--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E41DC1-5AFE-47EB-AC54-7C5FD3311ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AD54E1-7D3C-4E8A-8AE6-86C6BC0518C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="499">
   <si>
     <t>Event Name</t>
   </si>
@@ -287,6 +287,9 @@
     <t>Hartcliffe Nursery School</t>
   </si>
   <si>
+    <t>External</t>
+  </si>
+  <si>
     <t>NW Spotlight on Twos RP1-26-27</t>
   </si>
   <si>
@@ -296,144 +299,150 @@
     <t>Hosted by Hartcliffe Nursery School. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-october-2026/</t>
+  </si>
+  <si>
+    <t>The Terrific Twos Network is an opportunity for early years practitioners and leaders in Bristol to connect around a shared passion for working with two-year-olds. Whether experienced or new to the age group, and whether based in a setting, school or childminder provision, this is a chance to focus on this unique age group, visit other settings and gain peer support. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
+  </si>
+  <si>
+    <t>How Can a Playful Pedagogy Work Within a Home-Based Childcare Setting? With Michelle Malomo</t>
+  </si>
+  <si>
+    <t>PD PSED RP1-26-27</t>
+  </si>
+  <si>
+    <t>Presenter: Michelle Malamo. Can record.</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/how-can-a-playful-pedagogy-work-within-a-home-based-childcare-setting-michelle-malomo/</t>
+  </si>
+  <si>
+    <t>A webinar for childminders exploring playful, therapeutic practices that meet the needs of babies and young children through play, considering how different types of play, flexible play environments and intentional adult responses support children's development, wellbeing and learning. Participants will reflect on embedding playful pedagogy within home-based childcare settings and leave with practical strategies to implement immediately.</t>
+  </si>
+  <si>
+    <t>CPD Programme: Using Evidence to Strengthen Your Early Years Leadership - Session 1</t>
+  </si>
+  <si>
+    <t>9:00 am - 12:00 pm</t>
+  </si>
+  <si>
+    <t>St Pauls Nursery Community Room</t>
+  </si>
+  <si>
+    <t>Leadership</t>
+  </si>
+  <si>
+    <t>Presenters: Tom Colquhoun and Lucy Driver. Delivered in collaboration with the Somerset Research School.</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/cpd-programme-using-evidence-to-strengthen-your-early-years-leadership-2026/</t>
+  </si>
+  <si>
+    <t>A three-part face-to-face leadership programme delivered in collaboration with the Somerset Research School, for Headteachers, EYFS Leads, Nursery/Pre-School Managers, Room Leaders and EYFS Teachers. The programme supports those leading in the early years to engage with the growing body of educational research evidence and use it to make decisions about the 'best bets' for their school or setting.</t>
+  </si>
+  <si>
+    <t>Bristol Baby Practitioner Clusters - October 2026</t>
+  </si>
+  <si>
+    <t>6:15 pm - 7:45 pm</t>
+  </si>
+  <si>
+    <t>Partou Little Big Steps</t>
+  </si>
+  <si>
+    <t>NW Working with Babies RP1-26-27</t>
+  </si>
+  <si>
+    <t>Hosted by Partou Little Big Steps. Facilitators: Bev Roberts (Manager), Amber O'Connor (Under Two's Unit Leader).</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-october-2026/</t>
+  </si>
+  <si>
+    <t>Bristol's Baby Practitioner Networks have grown from six citywide meetings to nine locality-based clusters, with three meetings each in North, South and East &amp; Central Bristol, giving practitioners more opportunities to connect, share practice and be part of a supportive community focused on giving babies the best start in life. Free to attend and open to all — explore current themes in baby room practice, share ideas and celebrate great practice.</t>
+  </si>
+  <si>
+    <t>Mathematising the Day</t>
+  </si>
+  <si>
+    <t>Maths</t>
+  </si>
+  <si>
+    <t>PD Mathematics RP1-26-27</t>
+  </si>
+  <si>
+    <t>Presenter: Maeve Dorrian. Session can be recorded.</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/mathematising-the-day-october-2026/</t>
+  </si>
+  <si>
+    <t>Identify children's everyday mathematical experiences and plan for playful moments of mathematics throughout the day, exploring evidence-informed approaches that support children's understanding of mathematical skills and concepts through games, stories and mathematical vocabulary woven into everyday routines, interactions and provision.</t>
+  </si>
+  <si>
+    <t>Talking About Twos: Meaningful Two-Year Progress Checks</t>
+  </si>
+  <si>
+    <t>3:30 pm - 4:45 pm</t>
+  </si>
+  <si>
+    <t>Presenter: TBC</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/talking-about-twos-meaningful-two-year-progress-checks/</t>
+  </si>
+  <si>
+    <t>Explore how to make the two-year progress check a meaningful, child-centred process — celebrating children's strengths, identifying support needs, and working in partnership with families and other professionals to ensure the right support at the right time.</t>
+  </si>
+  <si>
+    <t>Live Panel Webinar: Inside the Baby Room: Insights from the Babies in Mind Project</t>
+  </si>
+  <si>
+    <t>7:00 pm - 8:00 pm</t>
+  </si>
+  <si>
+    <t>Working With Babies</t>
+  </si>
+  <si>
+    <t>Panellists: Professor Mona Sakr (Middlesex University), Rosie McCallum-Faraday (Local Authority Lead Teacher and Local Specialist Leader of Education for Birth to Threes, Bristol), and Cassie Holland (Birth to Three Local Specialist Leader, Bristol Early Years, and Birth to Three Network Lead for Bristol &amp; Beyond Stronger Practice Hub).</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/live-panel-webinar-inside-the-baby-room/</t>
+  </si>
+  <si>
+    <t>A panel discussion sharing findings from the Babies in Mind project, a Bristol-based exploration of baby room practice, alongside emerging national research from the Nuffield Foundation-funded Achieving High-Quality Provision in the Baby Room of English Nurseries study. The panel will explore what we are learning about baby room practice and consider how these findings can inform professional learning, leadership and future provision for babies.</t>
+  </si>
+  <si>
+    <t>Developing an Early Years Curriculum – Strengthening Early Years Teaching</t>
+  </si>
+  <si>
+    <t>9:30 am - 11:30 am</t>
+  </si>
+  <si>
+    <t>Presenter: Ali Carrington.</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/developing-an-early-years-curriculum-oct-26/</t>
+  </si>
+  <si>
+    <t>Develop an ambitious, inclusive Early Years curriculum that responds to the unique needs, experiences and cultural capital of your children, families and communities, drawing on Bristol's Early Years Curriculum Guidance to explore Intent, Implementation and Impact and how curriculum design, pedagogy, assessment and interactions work together to help children know more, remember more and do more over time.</t>
+  </si>
+  <si>
+    <t>Bristol Baby Practitioner Clusters - November 2026</t>
+  </si>
+  <si>
+    <t>4:30 pm - 6:00 pm</t>
+  </si>
+  <si>
+    <t>EveryFAMILY</t>
+  </si>
+  <si>
+    <t>Hosted by EveryFAMILY. Facilitator: Nic.</t>
+  </si>
+  <si>
     <t>https://calendar.bristolearlyyears.org.uk/</t>
   </si>
   <si>
-    <t>The Terrific Twos Network is an opportunity for early years practitioners and leaders in Bristol to connect around a shared passion for working with two-year-olds. Whether experienced or new to the age group, and whether based in a setting, school or childminder provision, this is a chance to focus on this unique age group, visit other settings and gain peer support. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
-  </si>
-  <si>
-    <t>External</t>
-  </si>
-  <si>
-    <t>PD PSED RP1-26-27</t>
-  </si>
-  <si>
-    <t>Presenter: Michelle Malamo. Can record.</t>
-  </si>
-  <si>
-    <t>A webinar for childminders exploring playful, therapeutic practices that meet the needs of babies and young children through play, considering how different types of play, flexible play environments and intentional adult responses support children's development, wellbeing and learning. Participants will reflect on embedding playful pedagogy within home-based childcare settings and leave with practical strategies to implement immediately.</t>
-  </si>
-  <si>
-    <t>CPD Programme: Using Evidence to Strengthen Your Early Years Leadership - Session 1</t>
-  </si>
-  <si>
-    <t>9:00 am - 12:00 pm</t>
-  </si>
-  <si>
-    <t>St Pauls Nursery Community Room</t>
-  </si>
-  <si>
-    <t>Leadership</t>
-  </si>
-  <si>
-    <t>Presenters: Tom Colquhoun and Lucy Driver. Delivered in collaboration with the Somerset Research School.</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/cpd-programme-using-evidence-to-strengthen-your-early-years-leadership-2026/</t>
-  </si>
-  <si>
-    <t>A three-part face-to-face leadership programme delivered in collaboration with the Somerset Research School, for Headteachers, EYFS Leads, Nursery/Pre-School Managers, Room Leaders and EYFS Teachers. The programme supports those leading in the early years to engage with the growing body of educational research evidence and use it to make decisions about the 'best bets' for their school or setting.</t>
-  </si>
-  <si>
-    <t>Bristol Baby Practitioner Clusters - October 2026</t>
-  </si>
-  <si>
-    <t>6:15 pm - 7:45 pm</t>
-  </si>
-  <si>
-    <t>Partou Little Big Steps</t>
-  </si>
-  <si>
-    <t>NW Working with Babies RP1-26-27</t>
-  </si>
-  <si>
-    <t>Hosted by Partou Little Big Steps. Facilitators: Bev Roberts (Manager), Amber O'Connor (Under Two's Unit Leader).</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-october-2026/</t>
-  </si>
-  <si>
-    <t>Bristol's Baby Practitioner Networks have grown from six citywide meetings to nine locality-based clusters, with three meetings each in North, South and East &amp; Central Bristol, giving practitioners more opportunities to connect, share practice and be part of a supportive community focused on giving babies the best start in life. Free to attend and open to all — explore current themes in baby room practice, share ideas and celebrate great practice.</t>
-  </si>
-  <si>
-    <t>Mathematising the Day</t>
-  </si>
-  <si>
-    <t>Maths</t>
-  </si>
-  <si>
-    <t>PD Mathematics RP1-26-27</t>
-  </si>
-  <si>
-    <t>Presenter: Maeve Dorrian. Session can be recorded.</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/mathematising-the-day-october-2026/</t>
-  </si>
-  <si>
-    <t>Identify children's everyday mathematical experiences and plan for playful moments of mathematics throughout the day, exploring evidence-informed approaches that support children's understanding of mathematical skills and concepts through games, stories and mathematical vocabulary woven into everyday routines, interactions and provision.</t>
-  </si>
-  <si>
-    <t>Talking About Twos: Meaningful Two-Year Progress Checks</t>
-  </si>
-  <si>
-    <t>3:30 pm - 4:45 pm</t>
-  </si>
-  <si>
-    <t>Presenter: TBC</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/talking-about-twos-meaningful-two-year-progress-checks/</t>
-  </si>
-  <si>
-    <t>Explore how to make the two-year progress check a meaningful, child-centred process — celebrating children's strengths, identifying support needs, and working in partnership with families and other professionals to ensure the right support at the right time.</t>
-  </si>
-  <si>
-    <t>Live Panel Webinar: Inside the Baby Room: Insights from the Babies in Mind Project</t>
-  </si>
-  <si>
-    <t>7:00 pm - 8:00 pm</t>
-  </si>
-  <si>
-    <t>Working With Babies</t>
-  </si>
-  <si>
-    <t>Panellists: Professor Mona Sakr (Middlesex University), Rosie McCallum-Faraday (Local Authority Lead Teacher and Local Specialist Leader of Education for Birth to Threes, Bristol), and Cassie Holland (Birth to Three Local Specialist Leader, Bristol Early Years, and Birth to Three Network Lead for Bristol &amp; Beyond Stronger Practice Hub).</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/live-panel-webinar-inside-the-baby-room/</t>
-  </si>
-  <si>
-    <t>A panel discussion sharing findings from the Babies in Mind project, a Bristol-based exploration of baby room practice, alongside emerging national research from the Nuffield Foundation-funded Achieving High-Quality Provision in the Baby Room of English Nurseries study. The panel will explore what we are learning about baby room practice and consider how these findings can inform professional learning, leadership and future provision for babies.</t>
-  </si>
-  <si>
-    <t>Developing an Early Years Curriculum – Strengthening Early Years Teaching</t>
-  </si>
-  <si>
-    <t>9:30 am - 11:30 am</t>
-  </si>
-  <si>
-    <t>Presenter: Ali Carrington.</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/developing-an-early-years-curriculum-oct-26/</t>
-  </si>
-  <si>
-    <t>Develop an ambitious, inclusive Early Years curriculum that responds to the unique needs, experiences and cultural capital of your children, families and communities, drawing on Bristol's Early Years Curriculum Guidance to explore Intent, Implementation and Impact and how curriculum design, pedagogy, assessment and interactions work together to help children know more, remember more and do more over time.</t>
-  </si>
-  <si>
-    <t>Bristol Baby Practitioner Clusters - November 2026</t>
-  </si>
-  <si>
-    <t>4:30 pm - 6:00 pm</t>
-  </si>
-  <si>
-    <t>EveryFAMILY</t>
-  </si>
-  <si>
-    <t>Hosted by EveryFAMILY. Facilitator: Nic.</t>
-  </si>
-  <si>
     <t>CPD Programme: Getting it Right for Twos - Session 1</t>
   </si>
   <si>
@@ -1187,6 +1196,9 @@
     <t>Talking About Babies: Listening to Babies</t>
   </si>
   <si>
+    <t>Presenters: Tracy Greenwood and Melanie Farman.</t>
+  </si>
+  <si>
     <t>https://beyth.co.uk/course/talking-about-babies-listening-to-babies/</t>
   </si>
   <si>
@@ -1298,7 +1310,7 @@
     <t>https://beyth.co.uk/course/send-network-working-in-partnership-with-parents/</t>
   </si>
   <si>
-    <t>Explore how to work in partnership with parents and carers of children with SEND in the early years, considering how trusting, collaborative relationships support children's communication, sensory processing, emotional regulation and developmental needs, with practical, inclusive strategies for building shared understanding between home and setting.</t>
+    <t>Positive relationships with parents are at the heart of good early years practice, but supporting families when a child has emerging or identified SEND can bring additional complexities. This reflective, practical session explores what meaningful partnership looks like in these situations — navigating different perspectives and sensitive conversations, and ensuring parents' knowledge of their child genuinely informs practice, assessment and planning.</t>
   </si>
   <si>
     <t>https://beyth.co.uk/course/open-study-day-at-st-pauls-nursery-may-27/</t>
@@ -1502,13 +1514,28 @@
     <t>Join Specialist Health Visitor Sarah Clarke to explore infant mental health and wellbeing and how it shapes babies' current and lifelong development, sharing ideas to support babies' mental health and development in early years settings — part of the Talking About... series of informal online networking sessions.</t>
   </si>
   <si>
-    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-october-2026/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/how-can-a-playful-pedagogy-work-within-a-home-based-childcare-setting-michelle-malomo/</t>
-  </si>
-  <si>
-    <t>How Can a Playful Pedagogy Work Within a Home-Based Childcare Setting? With Michelle Malomo</t>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-november-2026/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-december-2026/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-february-2027/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-march-2027/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-may-2027/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-june-2027/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-july-2027/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-august-2027/</t>
   </si>
 </sst>
 </file>
@@ -1553,7 +1580,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1586,12 +1613,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
@@ -1606,11 +1627,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1622,25 +1642,23 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2610,7 +2628,7 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="6" t="s">
         <v>78</v>
       </c>
       <c r="B10" s="7">
@@ -2623,14 +2641,14 @@
       <c r="D10" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="15" t="s">
-        <v>87</v>
+      <c r="G10" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H10" t="s">
         <v>25</v>
@@ -2645,31 +2663,31 @@
         <v>28</v>
       </c>
       <c r="L10" t="s">
+        <v>83</v>
+      </c>
+      <c r="M10" t="s">
+        <v>84</v>
+      </c>
+      <c r="N10" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="R10" t="s">
+        <v>87</v>
+      </c>
+      <c r="S10" t="s">
+        <v>80</v>
+      </c>
+      <c r="T10" t="s">
         <v>82</v>
-      </c>
-      <c r="M10" t="s">
-        <v>83</v>
-      </c>
-      <c r="N10" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" t="s">
-        <v>29</v>
-      </c>
-      <c r="P10" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>487</v>
-      </c>
-      <c r="R10" t="s">
-        <v>86</v>
-      </c>
-      <c r="S10" t="s">
-        <v>80</v>
-      </c>
-      <c r="T10" t="s">
-        <v>87</v>
       </c>
       <c r="U10" t="b">
         <f>FALSE()</f>
@@ -2678,7 +2696,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>489</v>
+        <v>88</v>
       </c>
       <c r="B11" s="7">
         <v>46315</v>
@@ -2709,7 +2727,7 @@
         <v>64</v>
       </c>
       <c r="K11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M11" t="s">
         <v>23</v>
@@ -2721,13 +2739,13 @@
         <v>30</v>
       </c>
       <c r="P11" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q11" s="16" t="s">
-        <v>488</v>
+        <v>90</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>91</v>
       </c>
       <c r="R11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -2742,7 +2760,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B12" s="7">
         <v>46315</v>
@@ -2752,13 +2770,13 @@
         <v>Tuesday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G12" s="2">
         <v>16</v>
@@ -2776,7 +2794,7 @@
         <v>28</v>
       </c>
       <c r="M12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N12" t="s">
         <v>30</v>
@@ -2785,13 +2803,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -2805,8 +2823,8 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>98</v>
+      <c r="A13" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="B13" s="7">
         <v>46316</v>
@@ -2816,16 +2834,16 @@
         <v>Wednesday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>87</v>
+        <v>102</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H13" t="s">
         <v>25</v>
@@ -2840,7 +2858,7 @@
         <v>28</v>
       </c>
       <c r="L13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M13" t="s">
         <v>75</v>
@@ -2852,19 +2870,19 @@
         <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="R13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S13" t="s">
         <v>80</v>
       </c>
       <c r="T13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U13" t="b">
         <f>FALSE()</f>
@@ -2873,7 +2891,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B14" s="7">
         <v>46316</v>
@@ -2886,7 +2904,7 @@
         <v>79</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -2904,10 +2922,10 @@
         <v>64</v>
       </c>
       <c r="K14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
@@ -2916,13 +2934,13 @@
         <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="R14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -2937,7 +2955,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B15" s="7">
         <v>46317</v>
@@ -2947,10 +2965,10 @@
         <v>Thursday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>38</v>
@@ -2968,13 +2986,13 @@
         <v>39</v>
       </c>
       <c r="K15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N15" t="s">
         <v>29</v>
@@ -2983,13 +3001,13 @@
         <v>30</v>
       </c>
       <c r="P15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -3004,7 +3022,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B16" s="7">
         <v>46317</v>
@@ -3014,10 +3032,10 @@
         <v>Thursday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>38</v>
@@ -3035,10 +3053,10 @@
         <v>64</v>
       </c>
       <c r="K16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -3047,13 +3065,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="R16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -3068,7 +3086,7 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B17" s="7">
         <v>46318</v>
@@ -3078,7 +3096,7 @@
         <v>Friday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>46</v>
@@ -3102,7 +3120,7 @@
         <v>28</v>
       </c>
       <c r="M17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
@@ -3111,13 +3129,13 @@
         <v>30</v>
       </c>
       <c r="P17" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="R17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -3131,8 +3149,8 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>127</v>
+      <c r="A18" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="B18" s="7">
         <v>46328</v>
@@ -3142,16 +3160,16 @@
         <v>Monday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E18" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>87</v>
+        <v>131</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H18" t="s">
         <v>25</v>
@@ -3166,7 +3184,7 @@
         <v>28</v>
       </c>
       <c r="L18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M18" t="s">
         <v>75</v>
@@ -3178,19 +3196,19 @@
         <v>29</v>
       </c>
       <c r="P18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>85</v>
+        <v>491</v>
       </c>
       <c r="R18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S18" t="s">
         <v>80</v>
       </c>
       <c r="T18" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U18" t="b">
         <f>FALSE()</f>
@@ -3199,7 +3217,7 @@
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B19" s="7">
         <v>46330</v>
@@ -3212,7 +3230,7 @@
         <v>79</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>38</v>
@@ -3230,10 +3248,10 @@
         <v>64</v>
       </c>
       <c r="K19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N19" t="s">
         <v>30</v>
@@ -3242,10 +3260,10 @@
         <v>30</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="R19" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -3260,7 +3278,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B20" s="7">
         <v>46331</v>
@@ -3303,10 +3321,10 @@
         <v>30</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="R20" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -3321,7 +3339,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B21" s="7">
         <v>46332</v>
@@ -3331,10 +3349,10 @@
         <v>Friday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>81</v>
@@ -3352,10 +3370,10 @@
         <v>27</v>
       </c>
       <c r="K21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
@@ -3364,13 +3382,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="R21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -3385,7 +3403,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B22" s="7">
         <v>46335</v>
@@ -3398,7 +3416,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>38</v>
@@ -3416,13 +3434,13 @@
         <v>39</v>
       </c>
       <c r="K22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L22" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="M22" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N22" t="s">
         <v>29</v>
@@ -3431,10 +3449,10 @@
         <v>30</v>
       </c>
       <c r="Q22" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="R22" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -3448,8 +3466,8 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>147</v>
+      <c r="A23" s="13" t="s">
+        <v>150</v>
       </c>
       <c r="B23" s="7">
         <v>46336</v>
@@ -3459,13 +3477,13 @@
         <v>Tuesday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G23" s="2">
         <v>16</v>
@@ -3483,7 +3501,7 @@
         <v>28</v>
       </c>
       <c r="M23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N23" t="s">
         <v>30</v>
@@ -3492,13 +3510,13 @@
         <v>29</v>
       </c>
       <c r="P23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -3513,7 +3531,7 @@
     </row>
     <row r="24" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B24" s="7">
         <v>46337</v>
@@ -3523,13 +3541,13 @@
         <v>Wednesday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G24" s="2">
         <v>16</v>
@@ -3547,7 +3565,7 @@
         <v>28</v>
       </c>
       <c r="M24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -3556,13 +3574,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -3577,7 +3595,7 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B25" s="7">
         <v>46338</v>
@@ -3587,7 +3605,7 @@
         <v>Thursday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>80</v>
@@ -3608,7 +3626,7 @@
         <v>28</v>
       </c>
       <c r="L25" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N25" t="s">
         <v>29</v>
@@ -3617,10 +3635,10 @@
         <v>30</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="R25" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="S25" t="s">
         <v>80</v>
@@ -3634,8 +3652,8 @@
       </c>
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>157</v>
+      <c r="A26" s="13" t="s">
+        <v>160</v>
       </c>
       <c r="B26" s="7">
         <v>46344</v>
@@ -3648,7 +3666,7 @@
         <v>79</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>38</v>
@@ -3666,10 +3684,10 @@
         <v>64</v>
       </c>
       <c r="K26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N26" t="s">
         <v>30</v>
@@ -3678,7 +3696,7 @@
         <v>29</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -3693,7 +3711,7 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B27" s="7">
         <v>46345</v>
@@ -3739,13 +3757,13 @@
         <v>30</v>
       </c>
       <c r="P27" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="R27" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -3760,7 +3778,7 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B28" s="7">
         <v>46351</v>
@@ -3773,7 +3791,7 @@
         <v>79</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>38</v>
@@ -3791,10 +3809,10 @@
         <v>64</v>
       </c>
       <c r="K28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M28" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N28" t="s">
         <v>29</v>
@@ -3803,13 +3821,13 @@
         <v>30</v>
       </c>
       <c r="P28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="R28" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="S28" t="s">
         <v>33</v>
@@ -3824,7 +3842,7 @@
     </row>
     <row r="29" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B29" s="7">
         <v>46352</v>
@@ -3855,7 +3873,7 @@
         <v>64</v>
       </c>
       <c r="K29" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M29" t="s">
         <v>37</v>
@@ -3867,10 +3885,10 @@
         <v>30</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="R29" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -3885,7 +3903,7 @@
     </row>
     <row r="30" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B30" s="7">
         <v>46352</v>
@@ -3934,10 +3952,10 @@
         <v>55</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="R30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -3968,18 +3986,17 @@
     <hyperlink ref="Q6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="Q8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="Q9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="Q14" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="Q18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="Q11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="Q14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="Q19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
     <hyperlink ref="Q21" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
     <hyperlink ref="Q23" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="Q25" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="Q26" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
     <hyperlink ref="Q28" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="Q11" r:id="rId15" xr:uid="{0C4392EE-38FB-4C24-9A4D-9185E1338FE4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId15"/>
   <tableParts count="1">
     <tablePart r:id="rId16"/>
   </tableParts>
@@ -4073,7 +4090,7 @@
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B2" s="7">
         <v>46357</v>
@@ -4095,19 +4112,19 @@
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>
@@ -4119,10 +4136,10 @@
         <v>30</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="S2" t="s">
         <v>33</v>
@@ -4136,8 +4153,8 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>181</v>
+      <c r="A3" s="13" t="s">
+        <v>184</v>
       </c>
       <c r="B3" s="7">
         <v>46357</v>
@@ -4147,31 +4164,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2">
         <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N3" t="s">
         <v>30</v>
@@ -4180,13 +4197,13 @@
         <v>29</v>
       </c>
       <c r="P3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -4200,8 +4217,8 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>183</v>
+      <c r="A4" s="15" t="s">
+        <v>186</v>
       </c>
       <c r="B4" s="7">
         <v>46357</v>
@@ -4211,31 +4228,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>87</v>
+        <v>95</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M4" t="s">
         <v>75</v>
@@ -4247,19 +4264,19 @@
         <v>29</v>
       </c>
       <c r="P4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="R4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S4" t="s">
         <v>80</v>
       </c>
       <c r="T4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U4" t="b">
         <f>FALSE()</f>
@@ -4268,7 +4285,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B5" s="7">
         <v>46358</v>
@@ -4290,19 +4307,19 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M5" t="s">
         <v>46</v>
@@ -4314,7 +4331,7 @@
         <v>30</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R5" t="s">
         <v>49</v>
@@ -4331,8 +4348,8 @@
       </c>
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>189</v>
+      <c r="A6" s="13" t="s">
+        <v>192</v>
       </c>
       <c r="B6" s="7">
         <v>46358</v>
@@ -4345,7 +4362,7 @@
         <v>79</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>38</v>
@@ -4354,19 +4371,19 @@
         <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N6" t="s">
         <v>30</v>
@@ -4375,7 +4392,7 @@
         <v>29</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -4390,7 +4407,7 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B7" s="7">
         <v>46358</v>
@@ -4400,31 +4417,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G7" s="2">
         <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
@@ -4433,10 +4450,10 @@
         <v>30</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="R7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -4451,7 +4468,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B8" s="7">
         <v>46360</v>
@@ -4461,10 +4478,10 @@
         <v>Friday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
@@ -4473,19 +4490,19 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="L8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M8" t="s">
         <v>75</v>
@@ -4497,13 +4514,13 @@
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="R8" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -4518,7 +4535,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B9" s="7">
         <v>46363</v>
@@ -4540,19 +4557,19 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M9" t="s">
         <v>37</v>
@@ -4564,10 +4581,10 @@
         <v>30</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="R9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -4582,7 +4599,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B10" s="7">
         <v>46364</v>
@@ -4595,7 +4612,7 @@
         <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>38</v>
@@ -4604,19 +4621,19 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K10" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="M10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
@@ -4625,13 +4642,13 @@
         <v>30</v>
       </c>
       <c r="P10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="R10" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -4645,8 +4662,8 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>212</v>
+      <c r="A11" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="B11" s="7">
         <v>46365</v>
@@ -4656,55 +4673,55 @@
         <v>Wednesday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E11" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G11" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I11" t="s">
+        <v>178</v>
+      </c>
+      <c r="J11" t="s">
+        <v>179</v>
+      </c>
+      <c r="K11" t="s">
+        <v>180</v>
+      </c>
+      <c r="L11" t="s">
+        <v>218</v>
+      </c>
+      <c r="M11" t="s">
+        <v>84</v>
+      </c>
+      <c r="N11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="R11" t="s">
         <v>87</v>
       </c>
-      <c r="H11" t="s">
-        <v>174</v>
-      </c>
-      <c r="I11" t="s">
-        <v>175</v>
-      </c>
-      <c r="J11" t="s">
-        <v>176</v>
-      </c>
-      <c r="K11" t="s">
-        <v>177</v>
-      </c>
-      <c r="L11" t="s">
-        <v>215</v>
-      </c>
-      <c r="M11" t="s">
-        <v>83</v>
-      </c>
-      <c r="N11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" t="s">
-        <v>29</v>
-      </c>
-      <c r="P11" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="R11" t="s">
-        <v>86</v>
-      </c>
       <c r="S11" t="s">
         <v>80</v>
       </c>
       <c r="T11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U11" t="b">
         <f>FALSE()</f>
@@ -4713,7 +4730,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B12" s="7">
         <v>46366</v>
@@ -4726,7 +4743,7 @@
         <v>36</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>38</v>
@@ -4735,22 +4752,22 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K12" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L12" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
@@ -4759,13 +4776,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="R12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -4780,7 +4797,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B13" s="7">
         <v>46394</v>
@@ -4802,19 +4819,19 @@
         <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
@@ -4823,13 +4840,13 @@
         <v>30</v>
       </c>
       <c r="P13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R13" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -4844,7 +4861,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B14" s="7">
         <v>46398</v>
@@ -4854,10 +4871,10 @@
         <v>Monday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -4866,19 +4883,19 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I14" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J14" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M14" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
@@ -4887,13 +4904,13 @@
         <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="R14" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -4908,7 +4925,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B15" s="7">
         <v>46400</v>
@@ -4918,10 +4935,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>38</v>
@@ -4930,19 +4947,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I15" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J15" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N15" t="s">
         <v>30</v>
@@ -4951,13 +4968,13 @@
         <v>30</v>
       </c>
       <c r="P15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="R15" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -4972,7 +4989,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B16" s="7">
         <v>46402</v>
@@ -4982,31 +4999,31 @@
         <v>Friday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I16" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J16" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="M16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -5015,13 +5032,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="R16" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -5036,7 +5053,7 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B17" s="7">
         <v>46405</v>
@@ -5046,28 +5063,28 @@
         <v>Monday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G17" s="2">
         <v>6</v>
       </c>
       <c r="H17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I17" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K17" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M17" t="s">
         <v>52</v>
@@ -5079,10 +5096,10 @@
         <v>30</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="R17" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -5097,7 +5114,7 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B18" s="7">
         <v>46407</v>
@@ -5107,28 +5124,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G18" s="2">
         <v>6</v>
       </c>
       <c r="H18" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I18" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J18" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K18" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M18" t="s">
         <v>52</v>
@@ -5140,10 +5157,10 @@
         <v>30</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="R18" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -5158,7 +5175,7 @@
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B19" s="7">
         <v>46407</v>
@@ -5180,19 +5197,19 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I19" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J19" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K19" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N19" t="s">
         <v>29</v>
@@ -5201,13 +5218,13 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="R19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -5222,7 +5239,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B20" s="7">
         <v>46408</v>
@@ -5235,7 +5252,7 @@
         <v>36</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>38</v>
@@ -5244,22 +5261,22 @@
         <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I20" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J20" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K20" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="L20" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M20" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N20" t="s">
         <v>29</v>
@@ -5268,10 +5285,10 @@
         <v>30</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="R20" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -5286,7 +5303,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B21" s="7">
         <v>46408</v>
@@ -5296,10 +5313,10 @@
         <v>Thursday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>38</v>
@@ -5308,19 +5325,19 @@
         <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J21" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K21" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M21" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
@@ -5329,13 +5346,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="R21" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -5350,7 +5367,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B22" s="7">
         <v>46414</v>
@@ -5372,19 +5389,19 @@
         <v>80</v>
       </c>
       <c r="H22" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I22" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J22" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M22" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N22" t="s">
         <v>30</v>
@@ -5393,13 +5410,13 @@
         <v>30</v>
       </c>
       <c r="P22" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q22" s="8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R22" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -5413,8 +5430,8 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>267</v>
+      <c r="A23" s="14" t="s">
+        <v>270</v>
       </c>
       <c r="B23" s="7">
         <v>46416</v>
@@ -5424,7 +5441,7 @@
         <v>Friday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>37</v>
@@ -5436,16 +5453,16 @@
         <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I23" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J23" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K23" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M23" t="s">
         <v>37</v>
@@ -5457,10 +5474,10 @@
         <v>30</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="R23" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -5475,7 +5492,7 @@
     </row>
     <row r="24" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B24" s="7">
         <v>46420</v>
@@ -5485,10 +5502,10 @@
         <v>Tuesday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>38</v>
@@ -5497,22 +5514,22 @@
         <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I24" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J24" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K24" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="L24" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -5521,13 +5538,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="R24" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -5542,7 +5559,7 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B25" s="7">
         <v>46420</v>
@@ -5552,28 +5569,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G25" s="2">
         <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I25" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J25" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K25" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s">
         <v>52</v>
@@ -5585,13 +5602,13 @@
         <v>30</v>
       </c>
       <c r="P25" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="R25" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -5606,7 +5623,7 @@
     </row>
     <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B26" s="7">
         <v>46420</v>
@@ -5628,16 +5645,16 @@
         <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I26" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J26" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K26" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M26" t="s">
         <v>23</v>
@@ -5649,13 +5666,13 @@
         <v>30</v>
       </c>
       <c r="P26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="R26" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -5670,7 +5687,7 @@
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B27" s="7">
         <v>46421</v>
@@ -5680,31 +5697,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G27" s="2">
         <v>12</v>
       </c>
       <c r="H27" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I27" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J27" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K27" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M27" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N27" t="s">
         <v>29</v>
@@ -5713,10 +5730,10 @@
         <v>30</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="R27" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -5731,7 +5748,7 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B28" s="7">
         <v>46421</v>
@@ -5753,19 +5770,19 @@
         <v>80</v>
       </c>
       <c r="H28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I28" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J28" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K28" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L28" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M28" t="s">
         <v>46</v>
@@ -5777,7 +5794,7 @@
         <v>30</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="R28" t="s">
         <v>49</v>
@@ -5795,7 +5812,7 @@
     </row>
     <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B29" s="7">
         <v>46422</v>
@@ -5805,28 +5822,28 @@
         <v>Thursday</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G29" s="2">
         <v>6</v>
       </c>
       <c r="H29" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I29" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J29" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K29" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M29" t="s">
         <v>52</v>
@@ -5838,13 +5855,13 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="R29" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -5859,7 +5876,7 @@
     </row>
     <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B30" s="7">
         <v>46422</v>
@@ -5869,10 +5886,10 @@
         <v>Thursday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>38</v>
@@ -5881,19 +5898,19 @@
         <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I30" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K30" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M30" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N30" t="s">
         <v>29</v>
@@ -5902,13 +5919,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="R30" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -5922,8 +5939,8 @@
       </c>
     </row>
     <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>292</v>
+      <c r="A31" s="14" t="s">
+        <v>295</v>
       </c>
       <c r="B31" s="7">
         <v>46423</v>
@@ -5933,7 +5950,7 @@
         <v>Friday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>37</v>
@@ -5945,16 +5962,16 @@
         <v>24</v>
       </c>
       <c r="H31" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I31" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J31" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K31" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M31" t="s">
         <v>37</v>
@@ -5966,10 +5983,10 @@
         <v>30</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="R31" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -5984,7 +6001,7 @@
     </row>
     <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B32" s="7">
         <v>46426</v>
@@ -6006,19 +6023,19 @@
         <v>80</v>
       </c>
       <c r="H32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I32" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J32" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K32" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L32" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M32" t="s">
         <v>37</v>
@@ -6030,10 +6047,10 @@
         <v>30</v>
       </c>
       <c r="Q32" s="8" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="R32" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -6048,7 +6065,7 @@
     </row>
     <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B33" s="7">
         <v>46427</v>
@@ -6070,19 +6087,19 @@
         <v>80</v>
       </c>
       <c r="H33" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I33" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J33" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K33" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N33" t="s">
         <v>29</v>
@@ -6091,13 +6108,13 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q33" s="8" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="R33" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="S33" t="s">
         <v>33</v>
@@ -6111,8 +6128,8 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>300</v>
+      <c r="A34" s="15" t="s">
+        <v>303</v>
       </c>
       <c r="B34" s="7">
         <v>46427</v>
@@ -6122,31 +6139,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E34" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>87</v>
+        <v>304</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H34" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I34" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J34" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K34" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L34" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M34" t="s">
         <v>75</v>
@@ -6158,19 +6175,19 @@
         <v>29</v>
       </c>
       <c r="P34" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q34" s="8" t="s">
-        <v>85</v>
+        <v>493</v>
       </c>
       <c r="R34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S34" t="s">
         <v>80</v>
       </c>
       <c r="T34" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U34" t="b">
         <f>FALSE()</f>
@@ -6178,8 +6195,8 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
-        <v>303</v>
+      <c r="A35" s="13" t="s">
+        <v>306</v>
       </c>
       <c r="B35" s="7">
         <v>46428</v>
@@ -6201,19 +6218,19 @@
         <v>80</v>
       </c>
       <c r="H35" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I35" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J35" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K35" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M35" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N35" t="s">
         <v>30</v>
@@ -6222,10 +6239,10 @@
         <v>29</v>
       </c>
       <c r="P35" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q35" s="8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="S35" t="s">
         <v>33</v>
@@ -6239,8 +6256,8 @@
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>304</v>
+      <c r="A36" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="B36" s="7">
         <v>46428</v>
@@ -6250,10 +6267,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>38</v>
@@ -6262,19 +6279,19 @@
         <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I36" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J36" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K36" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M36" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N36" t="s">
         <v>30</v>
@@ -6283,10 +6300,10 @@
         <v>29</v>
       </c>
       <c r="P36" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q36" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="S36" t="s">
         <v>33</v>
@@ -6300,8 +6317,8 @@
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>305</v>
+      <c r="A37" s="14" t="s">
+        <v>308</v>
       </c>
       <c r="B37" s="7">
         <v>46430</v>
@@ -6311,7 +6328,7 @@
         <v>Friday</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>37</v>
@@ -6323,16 +6340,16 @@
         <v>24</v>
       </c>
       <c r="H37" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I37" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J37" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K37" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M37" t="s">
         <v>37</v>
@@ -6344,10 +6361,10 @@
         <v>30</v>
       </c>
       <c r="Q37" s="8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="R37" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -6362,7 +6379,7 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B38" s="7">
         <v>46441</v>
@@ -6375,7 +6392,7 @@
         <v>36</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>38</v>
@@ -6384,22 +6401,22 @@
         <v>80</v>
       </c>
       <c r="H38" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I38" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J38" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K38" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L38" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M38" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N38" t="s">
         <v>29</v>
@@ -6408,13 +6425,13 @@
         <v>30</v>
       </c>
       <c r="P38" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q38" s="8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="R38" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S38" t="s">
         <v>33</v>
@@ -6428,8 +6445,8 @@
       </c>
     </row>
     <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>309</v>
+      <c r="A39" s="12" t="s">
+        <v>312</v>
       </c>
       <c r="B39" s="7">
         <v>46441</v>
@@ -6439,55 +6456,55 @@
         <v>Tuesday</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E39" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G39" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H39" t="s">
+        <v>177</v>
+      </c>
+      <c r="I39" t="s">
+        <v>178</v>
+      </c>
+      <c r="J39" t="s">
+        <v>179</v>
+      </c>
+      <c r="K39" t="s">
+        <v>180</v>
+      </c>
+      <c r="L39" t="s">
+        <v>218</v>
+      </c>
+      <c r="M39" t="s">
+        <v>84</v>
+      </c>
+      <c r="N39" t="s">
+        <v>29</v>
+      </c>
+      <c r="O39" t="s">
+        <v>29</v>
+      </c>
+      <c r="P39" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q39" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="R39" t="s">
         <v>87</v>
       </c>
-      <c r="H39" t="s">
-        <v>174</v>
-      </c>
-      <c r="I39" t="s">
-        <v>175</v>
-      </c>
-      <c r="J39" t="s">
-        <v>176</v>
-      </c>
-      <c r="K39" t="s">
-        <v>177</v>
-      </c>
-      <c r="L39" t="s">
-        <v>215</v>
-      </c>
-      <c r="M39" t="s">
-        <v>83</v>
-      </c>
-      <c r="N39" t="s">
-        <v>29</v>
-      </c>
-      <c r="O39" t="s">
-        <v>29</v>
-      </c>
-      <c r="P39" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q39" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="R39" t="s">
-        <v>86</v>
-      </c>
       <c r="S39" t="s">
         <v>80</v>
       </c>
       <c r="T39" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U39" t="b">
         <f>FALSE()</f>
@@ -6496,7 +6513,7 @@
     </row>
     <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B40" s="7">
         <v>46444</v>
@@ -6506,7 +6523,7 @@
         <v>Friday</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>23</v>
@@ -6518,19 +6535,19 @@
         <v>100</v>
       </c>
       <c r="H40" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I40" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J40" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K40" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L40" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -6542,10 +6559,10 @@
         <v>30</v>
       </c>
       <c r="Q40" s="8" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="R40" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="S40" t="s">
         <v>33</v>
@@ -6572,24 +6589,22 @@
   <hyperlinks>
     <hyperlink ref="Q2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="Q3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="Q4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="Q5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="Q6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="Q11" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="Q19" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="Q23" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="Q24" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="Q28" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="Q31" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="Q33" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="Q34" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="Q37" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="Q39" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="Q5" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="Q6" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="Q11" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="Q19" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="Q23" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="Q24" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="Q28" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="Q31" r:id="rId10" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="Q33" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="Q37" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="Q39" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId14"/>
   <tableParts count="1">
-    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6680,8 +6695,8 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>316</v>
+      <c r="A2" s="15" t="s">
+        <v>319</v>
       </c>
       <c r="B2" s="7">
         <v>46447</v>
@@ -6693,29 +6708,29 @@
       <c r="D2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>87</v>
+        <v>320</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M2" t="s">
         <v>75</v>
@@ -6727,19 +6742,19 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="R2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S2" t="s">
         <v>80</v>
       </c>
       <c r="T2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U2" t="b">
         <f>FALSE()</f>
@@ -6748,7 +6763,7 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B3" s="7">
         <v>46448</v>
@@ -6758,28 +6773,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2">
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M3" t="s">
         <v>52</v>
@@ -6791,10 +6806,10 @@
         <v>30</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="R3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -6809,7 +6824,7 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B4" s="7">
         <v>46449</v>
@@ -6819,10 +6834,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>38</v>
@@ -6831,19 +6846,19 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N4" t="s">
         <v>29</v>
@@ -6852,13 +6867,13 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="R4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -6873,7 +6888,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B5" s="7">
         <v>46450</v>
@@ -6895,19 +6910,19 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M5" t="s">
         <v>37</v>
@@ -6919,13 +6934,13 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="R5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -6940,7 +6955,7 @@
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B6" s="7">
         <v>46455</v>
@@ -6953,7 +6968,7 @@
         <v>79</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>38</v>
@@ -6962,19 +6977,19 @@
         <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I6" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J6" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s">
         <v>29</v>
@@ -6983,13 +6998,13 @@
         <v>30</v>
       </c>
       <c r="P6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="R6" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -7003,8 +7018,8 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>342</v>
+      <c r="A7" s="12" t="s">
+        <v>345</v>
       </c>
       <c r="B7" s="7">
         <v>46455</v>
@@ -7014,55 +7029,55 @@
         <v>Tuesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="E7" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" t="s">
+        <v>321</v>
+      </c>
+      <c r="I7" t="s">
+        <v>322</v>
+      </c>
+      <c r="J7" t="s">
+        <v>323</v>
+      </c>
+      <c r="K7" t="s">
+        <v>324</v>
+      </c>
+      <c r="L7" t="s">
+        <v>347</v>
+      </c>
+      <c r="M7" t="s">
+        <v>84</v>
+      </c>
+      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="R7" t="s">
         <v>87</v>
       </c>
-      <c r="H7" t="s">
-        <v>318</v>
-      </c>
-      <c r="I7" t="s">
-        <v>319</v>
-      </c>
-      <c r="J7" t="s">
-        <v>320</v>
-      </c>
-      <c r="K7" t="s">
-        <v>321</v>
-      </c>
-      <c r="L7" t="s">
-        <v>344</v>
-      </c>
-      <c r="M7" t="s">
-        <v>83</v>
-      </c>
-      <c r="N7" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P7" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="R7" t="s">
-        <v>86</v>
-      </c>
       <c r="S7" t="s">
         <v>80</v>
       </c>
       <c r="T7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U7" t="b">
         <f>FALSE()</f>
@@ -7070,8 +7085,8 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>346</v>
+      <c r="A8" s="13" t="s">
+        <v>349</v>
       </c>
       <c r="B8" s="7">
         <v>46456</v>
@@ -7081,10 +7096,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
@@ -7093,19 +7108,19 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -7114,10 +7129,10 @@
         <v>29</v>
       </c>
       <c r="P8" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -7132,7 +7147,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B9" s="7">
         <v>46456</v>
@@ -7154,19 +7169,19 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -7175,13 +7190,13 @@
         <v>30</v>
       </c>
       <c r="P9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="R9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -7196,7 +7211,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B10" s="7">
         <v>46457</v>
@@ -7218,16 +7233,16 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I10" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J10" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K10" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="M10" t="s">
         <v>37</v>
@@ -7239,10 +7254,10 @@
         <v>30</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="R10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -7257,7 +7272,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B11" s="7">
         <v>46462</v>
@@ -7270,7 +7285,7 @@
         <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>38</v>
@@ -7279,22 +7294,22 @@
         <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I11" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K11" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="M11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -7303,10 +7318,10 @@
         <v>30</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="R11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -7321,7 +7336,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B12" s="7">
         <v>46462</v>
@@ -7331,7 +7346,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>46</v>
@@ -7343,19 +7358,19 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K12" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M12" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
@@ -7364,13 +7379,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="R12" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -7385,7 +7400,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B13" s="7">
         <v>46463</v>
@@ -7407,19 +7422,19 @@
         <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I13" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J13" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L13" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M13" t="s">
         <v>52</v>
@@ -7434,10 +7449,10 @@
         <v>55</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="R13" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -7452,7 +7467,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B14" s="7">
         <v>46464</v>
@@ -7462,10 +7477,10 @@
         <v>Thursday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -7474,22 +7489,22 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I14" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J14" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K14" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L14" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
@@ -7498,10 +7513,10 @@
         <v>30</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="R14" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -7516,7 +7531,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B15" s="7">
         <v>46468</v>
@@ -7538,19 +7553,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I15" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J15" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L15" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M15" t="s">
         <v>37</v>
@@ -7562,10 +7577,10 @@
         <v>30</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="R15" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -7580,7 +7595,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B16" s="7">
         <v>46469</v>
@@ -7590,31 +7605,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I16" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J16" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K16" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -7623,13 +7638,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="R16" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -7644,7 +7659,7 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B17" s="7">
         <v>46470</v>
@@ -7666,19 +7681,19 @@
         <v>80</v>
       </c>
       <c r="H17" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I17" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J17" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K17" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L17" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M17" t="s">
         <v>46</v>
@@ -7690,7 +7705,7 @@
         <v>30</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="R17" t="s">
         <v>49</v>
@@ -7708,7 +7723,7 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B18" s="7">
         <v>46486</v>
@@ -7718,10 +7733,10 @@
         <v>Friday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>38</v>
@@ -7730,19 +7745,19 @@
         <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I18" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J18" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K18" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L18" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M18" t="s">
         <v>75</v>
@@ -7754,13 +7769,13 @@
         <v>30</v>
       </c>
       <c r="P18" t="s">
-        <v>113</v>
+        <v>385</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="R18" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -7775,7 +7790,7 @@
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B19" s="7">
         <v>46492</v>
@@ -7797,16 +7812,16 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I19" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J19" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K19" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M19" t="s">
         <v>37</v>
@@ -7818,13 +7833,13 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="R19" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -7839,7 +7854,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B20" s="7">
         <v>46496</v>
@@ -7849,7 +7864,7 @@
         <v>Monday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>23</v>
@@ -7861,19 +7876,19 @@
         <v>100</v>
       </c>
       <c r="H20" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I20" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J20" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K20" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L20" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="M20" t="s">
         <v>23</v>
@@ -7885,10 +7900,10 @@
         <v>30</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="R20" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -7903,7 +7918,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B21" s="7">
         <v>46500</v>
@@ -7913,31 +7928,31 @@
         <v>Friday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G21" s="2">
         <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I21" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J21" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K21" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
@@ -7946,13 +7961,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="R21" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -7967,7 +7982,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B22" s="7">
         <v>46505</v>
@@ -7977,28 +7992,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G22" s="2">
         <v>6</v>
       </c>
       <c r="H22" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I22" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J22" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K22" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M22" t="s">
         <v>52</v>
@@ -8010,10 +8025,10 @@
         <v>30</v>
       </c>
       <c r="Q22" s="8" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="R22" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -8027,8 +8042,8 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>398</v>
+      <c r="A23" s="13" t="s">
+        <v>402</v>
       </c>
       <c r="B23" s="7">
         <v>46506</v>
@@ -8050,16 +8065,16 @@
         <v>80</v>
       </c>
       <c r="H23" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I23" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J23" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K23" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M23" t="s">
         <v>37</v>
@@ -8071,13 +8086,13 @@
         <v>29</v>
       </c>
       <c r="P23" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="R23" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -8092,7 +8107,7 @@
     </row>
     <row r="24" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B24" s="7">
         <v>46507</v>
@@ -8102,7 +8117,7 @@
         <v>Friday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>46</v>
@@ -8114,19 +8129,19 @@
         <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I24" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J24" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K24" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -8135,13 +8150,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="R24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -8156,7 +8171,7 @@
     </row>
     <row r="25" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B25" s="7">
         <v>46512</v>
@@ -8166,10 +8181,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>38</v>
@@ -8178,22 +8193,22 @@
         <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I25" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J25" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K25" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L25" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M25" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N25" t="s">
         <v>29</v>
@@ -8202,10 +8217,10 @@
         <v>30</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="R25" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -8220,7 +8235,7 @@
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B26" s="7">
         <v>46512</v>
@@ -8242,19 +8257,19 @@
         <v>80</v>
       </c>
       <c r="H26" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I26" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J26" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K26" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L26" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M26" t="s">
         <v>46</v>
@@ -8266,7 +8281,7 @@
         <v>30</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="R26" t="s">
         <v>49</v>
@@ -8284,7 +8299,7 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B27" s="7">
         <v>46513</v>
@@ -8294,7 +8309,7 @@
         <v>Thursday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>37</v>
@@ -8306,16 +8321,16 @@
         <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I27" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J27" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K27" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M27" t="s">
         <v>37</v>
@@ -8327,10 +8342,10 @@
         <v>30</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="R27" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -8344,8 +8359,8 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>406</v>
+      <c r="A28" s="15" t="s">
+        <v>410</v>
       </c>
       <c r="B28" s="7">
         <v>46517</v>
@@ -8357,29 +8372,29 @@
       <c r="D28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>87</v>
+        <v>411</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H28" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I28" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J28" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K28" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L28" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M28" t="s">
         <v>75</v>
@@ -8391,19 +8406,19 @@
         <v>29</v>
       </c>
       <c r="P28" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>85</v>
+        <v>495</v>
       </c>
       <c r="R28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S28" t="s">
         <v>80</v>
       </c>
       <c r="T28" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U28" t="b">
         <f>FALSE()</f>
@@ -8412,7 +8427,7 @@
     </row>
     <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B29" s="7">
         <v>46518</v>
@@ -8425,7 +8440,7 @@
         <v>36</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>38</v>
@@ -8434,22 +8449,22 @@
         <v>80</v>
       </c>
       <c r="H29" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I29" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J29" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K29" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L29" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N29" t="s">
         <v>29</v>
@@ -8458,13 +8473,13 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="R29" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -8479,7 +8494,7 @@
     </row>
     <row r="30" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B30" s="7">
         <v>46519</v>
@@ -8489,10 +8504,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>38</v>
@@ -8501,19 +8516,19 @@
         <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I30" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J30" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K30" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
@@ -8522,13 +8537,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="R30" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -8543,7 +8558,7 @@
     </row>
     <row r="31" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B31" s="7">
         <v>46520</v>
@@ -8553,10 +8568,10 @@
         <v>Thursday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>38</v>
@@ -8565,19 +8580,19 @@
         <v>80</v>
       </c>
       <c r="H31" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I31" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J31" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K31" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N31" t="s">
         <v>30</v>
@@ -8586,10 +8601,10 @@
         <v>30</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="R31" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -8604,7 +8619,7 @@
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B32" s="7">
         <v>46525</v>
@@ -8626,19 +8641,19 @@
         <v>80</v>
       </c>
       <c r="H32" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I32" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J32" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K32" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L32" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M32" t="s">
         <v>52</v>
@@ -8653,10 +8668,10 @@
         <v>55</v>
       </c>
       <c r="Q32" s="8" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="R32" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -8671,7 +8686,7 @@
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B33" s="7">
         <v>46526</v>
@@ -8681,31 +8696,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G33" s="2">
         <v>16</v>
       </c>
       <c r="H33" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I33" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J33" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K33" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N33" t="s">
         <v>29</v>
@@ -8714,13 +8729,13 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q33" s="8" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="R33" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="S33" t="s">
         <v>33</v>
@@ -8734,8 +8749,8 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>421</v>
+      <c r="A34" s="13" t="s">
+        <v>425</v>
       </c>
       <c r="B34" s="7">
         <v>46527</v>
@@ -8757,16 +8772,16 @@
         <v>80</v>
       </c>
       <c r="H34" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I34" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J34" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K34" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M34" t="s">
         <v>37</v>
@@ -8778,13 +8793,13 @@
         <v>29</v>
       </c>
       <c r="P34" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Q34" s="8" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="R34" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="S34" t="s">
         <v>33</v>
@@ -8798,8 +8813,8 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>422</v>
+      <c r="A35" s="12" t="s">
+        <v>426</v>
       </c>
       <c r="B35" s="7">
         <v>46527</v>
@@ -8809,55 +8824,55 @@
         <v>Thursday</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E35" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="G35" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H35" t="s">
+        <v>321</v>
+      </c>
+      <c r="I35" t="s">
+        <v>322</v>
+      </c>
+      <c r="J35" t="s">
+        <v>323</v>
+      </c>
+      <c r="K35" t="s">
+        <v>324</v>
+      </c>
+      <c r="L35" t="s">
+        <v>347</v>
+      </c>
+      <c r="M35" t="s">
+        <v>84</v>
+      </c>
+      <c r="N35" t="s">
+        <v>29</v>
+      </c>
+      <c r="O35" t="s">
+        <v>29</v>
+      </c>
+      <c r="P35" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q35" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="R35" t="s">
         <v>87</v>
       </c>
-      <c r="H35" t="s">
-        <v>318</v>
-      </c>
-      <c r="I35" t="s">
-        <v>319</v>
-      </c>
-      <c r="J35" t="s">
-        <v>320</v>
-      </c>
-      <c r="K35" t="s">
-        <v>321</v>
-      </c>
-      <c r="L35" t="s">
-        <v>344</v>
-      </c>
-      <c r="M35" t="s">
-        <v>83</v>
-      </c>
-      <c r="N35" t="s">
-        <v>29</v>
-      </c>
-      <c r="O35" t="s">
-        <v>29</v>
-      </c>
-      <c r="P35" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q35" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="R35" t="s">
-        <v>86</v>
-      </c>
       <c r="S35" t="s">
         <v>80</v>
       </c>
       <c r="T35" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U35" t="b">
         <f>FALSE()</f>
@@ -8866,7 +8881,7 @@
     </row>
     <row r="36" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B36" s="7">
         <v>46533</v>
@@ -8876,31 +8891,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G36" s="2">
         <v>12</v>
       </c>
       <c r="H36" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I36" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J36" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K36" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M36" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N36" t="s">
         <v>29</v>
@@ -8909,10 +8924,10 @@
         <v>30</v>
       </c>
       <c r="Q36" s="8" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="R36" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S36" t="s">
         <v>33</v>
@@ -8926,8 +8941,8 @@
       </c>
     </row>
     <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>428</v>
+      <c r="A37" s="13" t="s">
+        <v>432</v>
       </c>
       <c r="B37" s="7">
         <v>46534</v>
@@ -8937,10 +8952,10 @@
         <v>Thursday</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>38</v>
@@ -8949,19 +8964,19 @@
         <v>80</v>
       </c>
       <c r="H37" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I37" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J37" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K37" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N37" t="s">
         <v>30</v>
@@ -8970,7 +8985,7 @@
         <v>29</v>
       </c>
       <c r="Q37" s="8" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -8995,20 +9010,18 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="Q2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="Q6" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="Q7" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="Q21" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="Q23" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="Q28" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
-    <hyperlink ref="Q34" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="Q35" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="Q37" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="Q6" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="Q7" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="Q21" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="Q23" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="Q34" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="Q35" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="Q37" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId8"/>
   <tableParts count="1">
-    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9099,8 +9112,8 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>429</v>
+      <c r="A2" s="15" t="s">
+        <v>433</v>
       </c>
       <c r="B2" s="7">
         <v>46546</v>
@@ -9110,31 +9123,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>87</v>
+        <v>434</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M2" t="s">
         <v>75</v>
@@ -9146,19 +9159,19 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>85</v>
+        <v>496</v>
       </c>
       <c r="R2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S2" t="s">
         <v>80</v>
       </c>
       <c r="T2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U2" t="b">
         <f>FALSE()</f>
@@ -9167,7 +9180,7 @@
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B3" s="7">
         <v>46547</v>
@@ -9177,10 +9190,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>38</v>
@@ -9189,22 +9202,22 @@
         <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K3" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="L3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="M3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N3" t="s">
         <v>29</v>
@@ -9213,13 +9226,13 @@
         <v>30</v>
       </c>
       <c r="P3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="R3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -9234,7 +9247,7 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B4" s="7">
         <v>46548</v>
@@ -9256,19 +9269,19 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L4" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="M4" t="s">
         <v>37</v>
@@ -9280,13 +9293,13 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="R4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -9301,7 +9314,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B5" s="7">
         <v>46552</v>
@@ -9311,7 +9324,7 @@
         <v>Monday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>46</v>
@@ -9323,19 +9336,19 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I5" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="K5" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N5" t="s">
         <v>29</v>
@@ -9344,13 +9357,13 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="R5" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -9365,7 +9378,7 @@
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B6" s="7">
         <v>46553</v>
@@ -9375,7 +9388,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
@@ -9387,19 +9400,19 @@
         <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I6" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J6" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K6" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L6" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
@@ -9411,10 +9424,10 @@
         <v>30</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="R6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -9428,8 +9441,8 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>453</v>
+      <c r="A7" s="13" t="s">
+        <v>457</v>
       </c>
       <c r="B7" s="7">
         <v>46554</v>
@@ -9439,10 +9452,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>38</v>
@@ -9451,19 +9464,19 @@
         <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I7" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J7" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="K7" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N7" t="s">
         <v>30</v>
@@ -9472,10 +9485,10 @@
         <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -9490,7 +9503,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B8" s="7">
         <v>46561</v>
@@ -9512,19 +9525,19 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I8" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J8" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="K8" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M8" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -9533,13 +9546,13 @@
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="R8" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -9554,7 +9567,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B9" s="7">
         <v>46562</v>
@@ -9567,7 +9580,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>38</v>
@@ -9576,22 +9589,22 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I9" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J9" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K9" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="L9" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="M9" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -9600,10 +9613,10 @@
         <v>30</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="R9" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -9618,7 +9631,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B10" s="7">
         <v>46568</v>
@@ -9640,19 +9653,19 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I10" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J10" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K10" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L10" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="M10" t="s">
         <v>46</v>
@@ -9664,7 +9677,7 @@
         <v>30</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="R10" t="s">
         <v>49</v>
@@ -9682,7 +9695,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B11" s="7">
         <v>46569</v>
@@ -9692,10 +9705,10 @@
         <v>Thursday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>38</v>
@@ -9704,22 +9717,22 @@
         <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I11" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J11" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K11" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="L11" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="M11" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -9728,10 +9741,10 @@
         <v>30</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="R11" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -9746,7 +9759,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B12" s="7">
         <v>46570</v>
@@ -9762,22 +9775,22 @@
         <v>63</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G12" s="2">
         <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I12" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J12" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="K12" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="M12" t="s">
         <v>63</v>
@@ -9789,13 +9802,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="R12" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -9809,8 +9822,8 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>470</v>
+      <c r="A13" s="15" t="s">
+        <v>474</v>
       </c>
       <c r="B13" s="7">
         <v>46574</v>
@@ -9822,29 +9835,29 @@
       <c r="D13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>87</v>
+        <v>475</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I13" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J13" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K13" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L13" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M13" t="s">
         <v>75</v>
@@ -9856,19 +9869,19 @@
         <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>85</v>
+        <v>497</v>
       </c>
       <c r="R13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S13" t="s">
         <v>80</v>
       </c>
       <c r="T13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U13" t="b">
         <f>FALSE()</f>
@@ -9876,8 +9889,8 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>473</v>
+      <c r="A14" s="13" t="s">
+        <v>477</v>
       </c>
       <c r="B14" s="7">
         <v>46575</v>
@@ -9899,19 +9912,19 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I14" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J14" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="K14" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M14" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N14" t="s">
         <v>30</v>
@@ -9920,10 +9933,10 @@
         <v>29</v>
       </c>
       <c r="P14" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -9937,8 +9950,8 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>474</v>
+      <c r="A15" s="13" t="s">
+        <v>478</v>
       </c>
       <c r="B15" s="7">
         <v>46575</v>
@@ -9948,10 +9961,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>38</v>
@@ -9960,19 +9973,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I15" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J15" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="K15" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M15" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N15" t="s">
         <v>30</v>
@@ -9981,10 +9994,10 @@
         <v>29</v>
       </c>
       <c r="P15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -9999,7 +10012,7 @@
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B16" s="7">
         <v>46576</v>
@@ -10021,19 +10034,19 @@
         <v>80</v>
       </c>
       <c r="H16" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I16" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J16" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="K16" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="M16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -10042,13 +10055,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="R16" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -10062,8 +10075,8 @@
       </c>
     </row>
     <row r="17" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>476</v>
+      <c r="A17" s="12" t="s">
+        <v>480</v>
       </c>
       <c r="B17" s="7">
         <v>46582</v>
@@ -10075,53 +10088,53 @@
       <c r="D17" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="G17" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" t="s">
+        <v>435</v>
+      </c>
+      <c r="I17" t="s">
+        <v>436</v>
+      </c>
+      <c r="J17" t="s">
+        <v>437</v>
+      </c>
+      <c r="K17" t="s">
+        <v>438</v>
+      </c>
+      <c r="L17" t="s">
+        <v>443</v>
+      </c>
+      <c r="M17" t="s">
+        <v>84</v>
+      </c>
+      <c r="N17" t="s">
+        <v>29</v>
+      </c>
+      <c r="O17" t="s">
+        <v>29</v>
+      </c>
+      <c r="P17" t="s">
+        <v>482</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="R17" t="s">
         <v>87</v>
       </c>
-      <c r="H17" t="s">
-        <v>431</v>
-      </c>
-      <c r="I17" t="s">
-        <v>432</v>
-      </c>
-      <c r="J17" t="s">
-        <v>433</v>
-      </c>
-      <c r="K17" t="s">
-        <v>434</v>
-      </c>
-      <c r="L17" t="s">
-        <v>439</v>
-      </c>
-      <c r="M17" t="s">
-        <v>83</v>
-      </c>
-      <c r="N17" t="s">
-        <v>29</v>
-      </c>
-      <c r="O17" t="s">
-        <v>29</v>
-      </c>
-      <c r="P17" t="s">
-        <v>478</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="R17" t="s">
-        <v>86</v>
-      </c>
       <c r="S17" t="s">
         <v>80</v>
       </c>
       <c r="T17" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U17" t="b">
         <f>FALSE()</f>
@@ -10129,8 +10142,8 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>479</v>
+      <c r="A18" s="13" t="s">
+        <v>483</v>
       </c>
       <c r="B18" s="7">
         <v>46589</v>
@@ -10152,19 +10165,19 @@
         <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I18" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J18" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="K18" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M18" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N18" t="s">
         <v>30</v>
@@ -10173,10 +10186,10 @@
         <v>29</v>
       </c>
       <c r="P18" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -10190,8 +10203,8 @@
       </c>
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>480</v>
+      <c r="A19" s="15" t="s">
+        <v>484</v>
       </c>
       <c r="B19" s="7">
         <v>46604</v>
@@ -10203,29 +10216,29 @@
       <c r="D19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>87</v>
+        <v>485</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="H19" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I19" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J19" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K19" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L19" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M19" t="s">
         <v>75</v>
@@ -10237,19 +10250,19 @@
         <v>29</v>
       </c>
       <c r="P19" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>85</v>
+        <v>498</v>
       </c>
       <c r="R19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S19" t="s">
         <v>80</v>
       </c>
       <c r="T19" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="U19" t="b">
         <f>FALSE()</f>
@@ -10258,7 +10271,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B20" s="7">
         <v>46612</v>
@@ -10268,10 +10281,10 @@
         <v>Friday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>38</v>
@@ -10280,19 +10293,19 @@
         <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I20" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J20" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K20" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="L20" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M20" t="s">
         <v>75</v>
@@ -10304,13 +10317,13 @@
         <v>30</v>
       </c>
       <c r="P20" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="R20" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -10335,16 +10348,13 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="Q2" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="Q9" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
-    <hyperlink ref="Q13" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
-    <hyperlink ref="Q17" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
-    <hyperlink ref="Q19" r:id="rId5" xr:uid="{00000000-0004-0000-0300-000004000000}"/>
+    <hyperlink ref="Q9" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="Q17" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AD54E1-7D3C-4E8A-8AE6-86C6BC0518C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A986EF-EB1F-44E6-A13B-6D75B4761BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="0" windowWidth="38610" windowHeight="20985" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19215" yWindow="240" windowWidth="38370" windowHeight="20505" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="503">
   <si>
     <t>Event Name</t>
   </si>
@@ -440,9 +440,6 @@
     <t>Hosted by EveryFAMILY. Facilitator: Nic.</t>
   </si>
   <si>
-    <t>https://calendar.bristolearlyyears.org.uk/</t>
-  </si>
-  <si>
     <t>CPD Programme: Getting it Right for Twos - Session 1</t>
   </si>
   <si>
@@ -1536,6 +1533,21 @@
   </si>
   <si>
     <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-august-2027/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-december-2026/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-february-2027/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-march-2027/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-may-2027/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-july-2027/</t>
   </si>
 </sst>
 </file>
@@ -1627,8 +1639,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1645,9 +1658,6 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1657,8 +1667,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3149,7 +3161,7 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>129</v>
       </c>
       <c r="B18" s="7">
@@ -3199,7 +3211,7 @@
         <v>132</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="R18" t="s">
         <v>106</v>
@@ -3217,7 +3229,7 @@
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B19" s="7">
         <v>46330</v>
@@ -3260,10 +3272,10 @@
         <v>30</v>
       </c>
       <c r="Q19" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="R19" t="s">
         <v>135</v>
-      </c>
-      <c r="R19" t="s">
-        <v>136</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -3278,7 +3290,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B20" s="7">
         <v>46331</v>
@@ -3321,10 +3333,10 @@
         <v>30</v>
       </c>
       <c r="Q20" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="R20" t="s">
         <v>138</v>
-      </c>
-      <c r="R20" t="s">
-        <v>139</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -3339,7 +3351,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B21" s="7">
         <v>46332</v>
@@ -3349,7 +3361,7 @@
         <v>Friday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>108</v>
@@ -3382,13 +3394,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q21" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Q21" s="8" t="s">
+      <c r="R21" t="s">
         <v>143</v>
-      </c>
-      <c r="R21" t="s">
-        <v>144</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -3403,7 +3415,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B22" s="7">
         <v>46335</v>
@@ -3416,7 +3428,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>38</v>
@@ -3437,37 +3449,37 @@
         <v>89</v>
       </c>
       <c r="L22" t="s">
+        <v>146</v>
+      </c>
+      <c r="M22" t="s">
+        <v>145</v>
+      </c>
+      <c r="N22" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q22" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="M22" t="s">
-        <v>146</v>
-      </c>
-      <c r="N22" t="s">
-        <v>29</v>
-      </c>
-      <c r="O22" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q22" s="8" t="s">
+      <c r="R22" t="s">
         <v>148</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
+        <v>33</v>
+      </c>
+      <c r="T22" t="s">
+        <v>34</v>
+      </c>
+      <c r="U22" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="S22" t="s">
-        <v>33</v>
-      </c>
-      <c r="T22" t="s">
-        <v>34</v>
-      </c>
-      <c r="U22" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>150</v>
       </c>
       <c r="B23" s="7">
         <v>46336</v>
@@ -3531,7 +3543,7 @@
     </row>
     <row r="24" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B24" s="7">
         <v>46337</v>
@@ -3541,7 +3553,7 @@
         <v>Wednesday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>46</v>
@@ -3574,13 +3586,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q24" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="Q24" s="8" t="s">
+      <c r="R24" t="s">
         <v>154</v>
-      </c>
-      <c r="R24" t="s">
-        <v>155</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -3595,7 +3607,7 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B25" s="7">
         <v>46338</v>
@@ -3605,7 +3617,7 @@
         <v>Thursday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>80</v>
@@ -3635,25 +3647,25 @@
         <v>30</v>
       </c>
       <c r="Q25" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="R25" t="s">
         <v>158</v>
       </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
+        <v>80</v>
+      </c>
+      <c r="T25" t="s">
+        <v>34</v>
+      </c>
+      <c r="U25" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
         <v>159</v>
-      </c>
-      <c r="S25" t="s">
-        <v>80</v>
-      </c>
-      <c r="T25" t="s">
-        <v>34</v>
-      </c>
-      <c r="U25" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>160</v>
       </c>
       <c r="B26" s="7">
         <v>46344</v>
@@ -3696,7 +3708,7 @@
         <v>29</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -3711,7 +3723,7 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B27" s="7">
         <v>46345</v>
@@ -3757,13 +3769,13 @@
         <v>30</v>
       </c>
       <c r="P27" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q27" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="Q27" s="8" t="s">
+      <c r="R27" t="s">
         <v>163</v>
-      </c>
-      <c r="R27" t="s">
-        <v>164</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -3778,7 +3790,7 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B28" s="7">
         <v>46351</v>
@@ -3791,7 +3803,7 @@
         <v>79</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>38</v>
@@ -3812,7 +3824,7 @@
         <v>89</v>
       </c>
       <c r="M28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N28" t="s">
         <v>29</v>
@@ -3821,13 +3833,13 @@
         <v>30</v>
       </c>
       <c r="P28" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q28" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="Q28" s="8" t="s">
+      <c r="R28" t="s">
         <v>167</v>
-      </c>
-      <c r="R28" t="s">
-        <v>168</v>
       </c>
       <c r="S28" t="s">
         <v>33</v>
@@ -3842,7 +3854,7 @@
     </row>
     <row r="29" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B29" s="7">
         <v>46352</v>
@@ -3873,7 +3885,7 @@
         <v>64</v>
       </c>
       <c r="K29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M29" t="s">
         <v>37</v>
@@ -3885,10 +3897,10 @@
         <v>30</v>
       </c>
       <c r="Q29" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="R29" t="s">
         <v>171</v>
-      </c>
-      <c r="R29" t="s">
-        <v>172</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -3903,7 +3915,7 @@
     </row>
     <row r="30" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B30" s="7">
         <v>46352</v>
@@ -3952,10 +3964,10 @@
         <v>55</v>
       </c>
       <c r="Q30" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="R30" t="s">
         <v>174</v>
-      </c>
-      <c r="R30" t="s">
-        <v>175</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -4090,7 +4102,7 @@
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B2" s="7">
         <v>46357</v>
@@ -4112,19 +4124,19 @@
         <v>100</v>
       </c>
       <c r="H2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2" t="s">
         <v>177</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>178</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>179</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>180</v>
-      </c>
-      <c r="L2" t="s">
-        <v>181</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>
@@ -4136,25 +4148,25 @@
         <v>30</v>
       </c>
       <c r="Q2" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="R2" t="s">
         <v>182</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T2" t="s">
+        <v>34</v>
+      </c>
+      <c r="U2" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>183</v>
-      </c>
-      <c r="S2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T2" t="s">
-        <v>34</v>
-      </c>
-      <c r="U2" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>184</v>
       </c>
       <c r="B3" s="7">
         <v>46357</v>
@@ -4176,16 +4188,16 @@
         <v>16</v>
       </c>
       <c r="H3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I3" t="s">
         <v>177</v>
       </c>
-      <c r="I3" t="s">
-        <v>178</v>
-      </c>
       <c r="J3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M3" t="s">
         <v>96</v>
@@ -4217,8 +4229,8 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>186</v>
+      <c r="A4" s="14" t="s">
+        <v>185</v>
       </c>
       <c r="B4" s="7">
         <v>46357</v>
@@ -4240,19 +4252,19 @@
         <v>82</v>
       </c>
       <c r="H4" t="s">
+        <v>176</v>
+      </c>
+      <c r="I4" t="s">
         <v>177</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>178</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>179</v>
       </c>
-      <c r="K4" t="s">
-        <v>180</v>
-      </c>
       <c r="L4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M4" t="s">
         <v>75</v>
@@ -4264,10 +4276,10 @@
         <v>29</v>
       </c>
       <c r="P4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="R4" t="s">
         <v>106</v>
@@ -4285,7 +4297,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B5" s="7">
         <v>46358</v>
@@ -4307,19 +4319,19 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
+        <v>176</v>
+      </c>
+      <c r="I5" t="s">
         <v>177</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>178</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>179</v>
       </c>
-      <c r="K5" t="s">
-        <v>180</v>
-      </c>
       <c r="L5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M5" t="s">
         <v>46</v>
@@ -4331,7 +4343,7 @@
         <v>30</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R5" t="s">
         <v>49</v>
@@ -4348,8 +4360,8 @@
       </c>
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>192</v>
+      <c r="A6" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="B6" s="7">
         <v>46358</v>
@@ -4371,16 +4383,16 @@
         <v>80</v>
       </c>
       <c r="H6" t="s">
+        <v>176</v>
+      </c>
+      <c r="I6" t="s">
         <v>177</v>
       </c>
-      <c r="I6" t="s">
-        <v>178</v>
-      </c>
       <c r="J6" t="s">
+        <v>192</v>
+      </c>
+      <c r="K6" t="s">
         <v>193</v>
-      </c>
-      <c r="K6" t="s">
-        <v>194</v>
       </c>
       <c r="M6" t="s">
         <v>84</v>
@@ -4392,7 +4404,7 @@
         <v>29</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -4407,7 +4419,7 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B7" s="7">
         <v>46358</v>
@@ -4417,31 +4429,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="G7" s="2">
         <v>12</v>
       </c>
       <c r="H7" t="s">
+        <v>176</v>
+      </c>
+      <c r="I7" t="s">
         <v>177</v>
       </c>
-      <c r="I7" t="s">
-        <v>178</v>
-      </c>
       <c r="J7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
@@ -4450,10 +4462,10 @@
         <v>30</v>
       </c>
       <c r="Q7" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="R7" t="s">
         <v>198</v>
-      </c>
-      <c r="R7" t="s">
-        <v>199</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -4468,7 +4480,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B8" s="7">
         <v>46360</v>
@@ -4478,7 +4490,7 @@
         <v>Friday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>120</v>
@@ -4490,19 +4502,19 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
+        <v>176</v>
+      </c>
+      <c r="I8" t="s">
         <v>177</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>178</v>
       </c>
-      <c r="J8" t="s">
-        <v>179</v>
-      </c>
       <c r="K8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M8" t="s">
         <v>75</v>
@@ -4517,10 +4529,10 @@
         <v>115</v>
       </c>
       <c r="Q8" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="R8" t="s">
         <v>202</v>
-      </c>
-      <c r="R8" t="s">
-        <v>203</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -4535,7 +4547,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B9" s="7">
         <v>46363</v>
@@ -4557,19 +4569,19 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I9" t="s">
         <v>177</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>178</v>
       </c>
-      <c r="J9" t="s">
-        <v>179</v>
-      </c>
       <c r="K9" t="s">
+        <v>204</v>
+      </c>
+      <c r="L9" t="s">
         <v>205</v>
-      </c>
-      <c r="L9" t="s">
-        <v>206</v>
       </c>
       <c r="M9" t="s">
         <v>37</v>
@@ -4581,10 +4593,10 @@
         <v>30</v>
       </c>
       <c r="Q9" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="R9" t="s">
         <v>207</v>
-      </c>
-      <c r="R9" t="s">
-        <v>208</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -4599,7 +4611,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B10" s="7">
         <v>46364</v>
@@ -4612,7 +4624,7 @@
         <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>38</v>
@@ -4621,49 +4633,49 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
+        <v>176</v>
+      </c>
+      <c r="I10" t="s">
         <v>177</v>
       </c>
-      <c r="I10" t="s">
-        <v>178</v>
-      </c>
       <c r="J10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K10" t="s">
+        <v>210</v>
+      </c>
+      <c r="M10" t="s">
+        <v>209</v>
+      </c>
+      <c r="N10" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" t="s">
         <v>211</v>
       </c>
-      <c r="M10" t="s">
-        <v>210</v>
-      </c>
-      <c r="N10" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" t="s">
-        <v>30</v>
-      </c>
-      <c r="P10" t="s">
+      <c r="Q10" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="Q10" s="8" t="s">
+      <c r="R10" t="s">
         <v>213</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
+        <v>33</v>
+      </c>
+      <c r="T10" t="s">
+        <v>34</v>
+      </c>
+      <c r="U10" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>214</v>
-      </c>
-      <c r="S10" t="s">
-        <v>33</v>
-      </c>
-      <c r="T10" t="s">
-        <v>34</v>
-      </c>
-      <c r="U10" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>215</v>
       </c>
       <c r="B11" s="7">
         <v>46365</v>
@@ -4673,31 +4685,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H11" t="s">
+        <v>176</v>
+      </c>
+      <c r="I11" t="s">
         <v>177</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>178</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>179</v>
       </c>
-      <c r="K11" t="s">
-        <v>180</v>
-      </c>
       <c r="L11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M11" t="s">
         <v>84</v>
@@ -4709,10 +4721,10 @@
         <v>29</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>133</v>
+        <v>498</v>
       </c>
       <c r="R11" t="s">
         <v>87</v>
@@ -4730,7 +4742,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B12" s="7">
         <v>46366</v>
@@ -4752,19 +4764,19 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
+        <v>176</v>
+      </c>
+      <c r="I12" t="s">
         <v>177</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>178</v>
       </c>
-      <c r="J12" t="s">
-        <v>179</v>
-      </c>
       <c r="K12" t="s">
+        <v>220</v>
+      </c>
+      <c r="L12" t="s">
         <v>221</v>
-      </c>
-      <c r="L12" t="s">
-        <v>222</v>
       </c>
       <c r="M12" t="s">
         <v>108</v>
@@ -4776,13 +4788,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q12" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="R12" t="s">
         <v>224</v>
-      </c>
-      <c r="R12" t="s">
-        <v>225</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -4797,7 +4809,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B13" s="7">
         <v>46394</v>
@@ -4819,16 +4831,16 @@
         <v>80</v>
       </c>
       <c r="H13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I13" t="s">
         <v>177</v>
       </c>
-      <c r="I13" t="s">
-        <v>178</v>
-      </c>
       <c r="J13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M13" t="s">
         <v>96</v>
@@ -4843,10 +4855,10 @@
         <v>126</v>
       </c>
       <c r="Q13" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="R13" t="s">
         <v>227</v>
-      </c>
-      <c r="R13" t="s">
-        <v>228</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -4861,7 +4873,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B14" s="7">
         <v>46398</v>
@@ -4871,10 +4883,10 @@
         <v>Monday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -4883,34 +4895,34 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
+        <v>176</v>
+      </c>
+      <c r="I14" t="s">
         <v>177</v>
       </c>
-      <c r="I14" t="s">
-        <v>178</v>
-      </c>
       <c r="J14" t="s">
+        <v>192</v>
+      </c>
+      <c r="K14" t="s">
         <v>193</v>
       </c>
-      <c r="K14" t="s">
-        <v>194</v>
-      </c>
       <c r="M14" t="s">
+        <v>229</v>
+      </c>
+      <c r="N14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" t="s">
+        <v>30</v>
+      </c>
+      <c r="P14" t="s">
         <v>230</v>
       </c>
-      <c r="N14" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" t="s">
-        <v>30</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="Q14" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="Q14" s="8" t="s">
+      <c r="R14" t="s">
         <v>232</v>
-      </c>
-      <c r="R14" t="s">
-        <v>233</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -4925,7 +4937,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B15" s="7">
         <v>46400</v>
@@ -4935,10 +4947,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>38</v>
@@ -4947,19 +4959,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
+        <v>176</v>
+      </c>
+      <c r="I15" t="s">
         <v>177</v>
       </c>
-      <c r="I15" t="s">
-        <v>178</v>
-      </c>
       <c r="J15" t="s">
+        <v>192</v>
+      </c>
+      <c r="K15" t="s">
         <v>193</v>
       </c>
-      <c r="K15" t="s">
-        <v>194</v>
-      </c>
       <c r="M15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N15" t="s">
         <v>30</v>
@@ -4968,13 +4980,13 @@
         <v>30</v>
       </c>
       <c r="P15" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q15" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="Q15" s="8" t="s">
+      <c r="R15" t="s">
         <v>237</v>
-      </c>
-      <c r="R15" t="s">
-        <v>238</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -4989,7 +5001,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B16" s="7">
         <v>46402</v>
@@ -4999,28 +5011,28 @@
         <v>Friday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>108</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
       </c>
       <c r="H16" t="s">
+        <v>176</v>
+      </c>
+      <c r="I16" t="s">
         <v>177</v>
       </c>
-      <c r="I16" t="s">
-        <v>178</v>
-      </c>
       <c r="J16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M16" t="s">
         <v>108</v>
@@ -5032,13 +5044,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q16" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="Q16" s="8" t="s">
+      <c r="R16" t="s">
         <v>242</v>
-      </c>
-      <c r="R16" t="s">
-        <v>243</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -5053,7 +5065,7 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B17" s="7">
         <v>46405</v>
@@ -5063,28 +5075,28 @@
         <v>Monday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G17" s="2">
         <v>6</v>
       </c>
       <c r="H17" t="s">
+        <v>176</v>
+      </c>
+      <c r="I17" t="s">
         <v>177</v>
       </c>
-      <c r="I17" t="s">
-        <v>178</v>
-      </c>
       <c r="J17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M17" t="s">
         <v>52</v>
@@ -5096,10 +5108,10 @@
         <v>30</v>
       </c>
       <c r="Q17" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="R17" t="s">
         <v>248</v>
-      </c>
-      <c r="R17" t="s">
-        <v>249</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -5114,7 +5126,7 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B18" s="7">
         <v>46407</v>
@@ -5124,28 +5136,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G18" s="2">
         <v>6</v>
       </c>
       <c r="H18" t="s">
+        <v>176</v>
+      </c>
+      <c r="I18" t="s">
         <v>177</v>
       </c>
-      <c r="I18" t="s">
-        <v>178</v>
-      </c>
       <c r="J18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M18" t="s">
         <v>52</v>
@@ -5157,10 +5169,10 @@
         <v>30</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -5175,7 +5187,7 @@
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B19" s="7">
         <v>46407</v>
@@ -5197,16 +5209,16 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
+        <v>176</v>
+      </c>
+      <c r="I19" t="s">
         <v>177</v>
       </c>
-      <c r="I19" t="s">
-        <v>178</v>
-      </c>
       <c r="J19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M19" t="s">
         <v>96</v>
@@ -5218,13 +5230,13 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q19" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="Q19" s="8" t="s">
+      <c r="R19" t="s">
         <v>254</v>
-      </c>
-      <c r="R19" t="s">
-        <v>255</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -5239,7 +5251,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B20" s="7">
         <v>46408</v>
@@ -5252,7 +5264,7 @@
         <v>36</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>38</v>
@@ -5261,34 +5273,34 @@
         <v>80</v>
       </c>
       <c r="H20" t="s">
+        <v>176</v>
+      </c>
+      <c r="I20" t="s">
         <v>177</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>178</v>
       </c>
-      <c r="J20" t="s">
-        <v>179</v>
-      </c>
       <c r="K20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L20" t="s">
+        <v>256</v>
+      </c>
+      <c r="M20" t="s">
+        <v>145</v>
+      </c>
+      <c r="N20" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q20" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="M20" t="s">
-        <v>146</v>
-      </c>
-      <c r="N20" t="s">
-        <v>29</v>
-      </c>
-      <c r="O20" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q20" s="8" t="s">
+      <c r="R20" t="s">
         <v>258</v>
-      </c>
-      <c r="R20" t="s">
-        <v>259</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -5303,7 +5315,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B21" s="7">
         <v>46408</v>
@@ -5316,7 +5328,7 @@
         <v>101</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>38</v>
@@ -5325,34 +5337,34 @@
         <v>80</v>
       </c>
       <c r="H21" t="s">
+        <v>176</v>
+      </c>
+      <c r="I21" t="s">
         <v>177</v>
       </c>
-      <c r="I21" t="s">
-        <v>178</v>
-      </c>
       <c r="J21" t="s">
+        <v>192</v>
+      </c>
+      <c r="K21" t="s">
         <v>193</v>
       </c>
-      <c r="K21" t="s">
-        <v>194</v>
-      </c>
       <c r="M21" t="s">
+        <v>260</v>
+      </c>
+      <c r="N21" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" t="s">
+        <v>30</v>
+      </c>
+      <c r="P21" t="s">
         <v>261</v>
       </c>
-      <c r="N21" t="s">
-        <v>29</v>
-      </c>
-      <c r="O21" t="s">
-        <v>30</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="Q21" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="Q21" s="8" t="s">
+      <c r="R21" t="s">
         <v>263</v>
-      </c>
-      <c r="R21" t="s">
-        <v>264</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -5367,7 +5379,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B22" s="7">
         <v>46414</v>
@@ -5389,49 +5401,49 @@
         <v>80</v>
       </c>
       <c r="H22" t="s">
+        <v>176</v>
+      </c>
+      <c r="I22" t="s">
         <v>177</v>
       </c>
-      <c r="I22" t="s">
-        <v>178</v>
-      </c>
       <c r="J22" t="s">
+        <v>192</v>
+      </c>
+      <c r="K22" t="s">
         <v>193</v>
       </c>
-      <c r="K22" t="s">
-        <v>194</v>
-      </c>
       <c r="M22" t="s">
+        <v>265</v>
+      </c>
+      <c r="N22" t="s">
+        <v>30</v>
+      </c>
+      <c r="O22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" t="s">
         <v>266</v>
       </c>
-      <c r="N22" t="s">
-        <v>30</v>
-      </c>
-      <c r="O22" t="s">
-        <v>30</v>
-      </c>
-      <c r="P22" t="s">
+      <c r="Q22" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="Q22" s="8" t="s">
+      <c r="R22" t="s">
         <v>268</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
+        <v>33</v>
+      </c>
+      <c r="T22" t="s">
+        <v>34</v>
+      </c>
+      <c r="U22" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>269</v>
-      </c>
-      <c r="S22" t="s">
-        <v>33</v>
-      </c>
-      <c r="T22" t="s">
-        <v>34</v>
-      </c>
-      <c r="U22" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>270</v>
       </c>
       <c r="B23" s="7">
         <v>46416</v>
@@ -5441,7 +5453,7 @@
         <v>Friday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>37</v>
@@ -5453,16 +5465,16 @@
         <v>24</v>
       </c>
       <c r="H23" t="s">
+        <v>176</v>
+      </c>
+      <c r="I23" t="s">
         <v>177</v>
       </c>
-      <c r="I23" t="s">
-        <v>178</v>
-      </c>
       <c r="J23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M23" t="s">
         <v>37</v>
@@ -5474,10 +5486,10 @@
         <v>30</v>
       </c>
       <c r="Q23" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="R23" t="s">
         <v>272</v>
-      </c>
-      <c r="R23" t="s">
-        <v>273</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -5492,7 +5504,7 @@
     </row>
     <row r="24" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" s="7">
         <v>46420</v>
@@ -5514,19 +5526,19 @@
         <v>80</v>
       </c>
       <c r="H24" t="s">
+        <v>176</v>
+      </c>
+      <c r="I24" t="s">
         <v>177</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>178</v>
       </c>
-      <c r="J24" t="s">
-        <v>179</v>
-      </c>
       <c r="K24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s">
         <v>84</v>
@@ -5541,10 +5553,10 @@
         <v>115</v>
       </c>
       <c r="Q24" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="R24" t="s">
         <v>275</v>
-      </c>
-      <c r="R24" t="s">
-        <v>276</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -5559,7 +5571,7 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B25" s="7">
         <v>46420</v>
@@ -5569,28 +5581,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G25" s="2">
         <v>6</v>
       </c>
       <c r="H25" t="s">
+        <v>176</v>
+      </c>
+      <c r="I25" t="s">
         <v>177</v>
       </c>
-      <c r="I25" t="s">
-        <v>178</v>
-      </c>
       <c r="J25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K25" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s">
         <v>52</v>
@@ -5602,13 +5614,13 @@
         <v>30</v>
       </c>
       <c r="P25" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q25" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="Q25" s="8" t="s">
+      <c r="R25" t="s">
         <v>280</v>
-      </c>
-      <c r="R25" t="s">
-        <v>281</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -5623,7 +5635,7 @@
     </row>
     <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B26" s="7">
         <v>46420</v>
@@ -5645,16 +5657,16 @@
         <v>40</v>
       </c>
       <c r="H26" t="s">
+        <v>176</v>
+      </c>
+      <c r="I26" t="s">
         <v>177</v>
       </c>
-      <c r="I26" t="s">
-        <v>178</v>
-      </c>
       <c r="J26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M26" t="s">
         <v>23</v>
@@ -5666,13 +5678,13 @@
         <v>30</v>
       </c>
       <c r="P26" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q26" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="Q26" s="8" t="s">
+      <c r="R26" t="s">
         <v>284</v>
-      </c>
-      <c r="R26" t="s">
-        <v>285</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -5687,7 +5699,7 @@
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B27" s="7">
         <v>46421</v>
@@ -5697,31 +5709,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="G27" s="2">
         <v>12</v>
       </c>
       <c r="H27" t="s">
+        <v>176</v>
+      </c>
+      <c r="I27" t="s">
         <v>177</v>
       </c>
-      <c r="I27" t="s">
-        <v>178</v>
-      </c>
       <c r="J27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N27" t="s">
         <v>29</v>
@@ -5730,10 +5742,10 @@
         <v>30</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -5748,7 +5760,7 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B28" s="7">
         <v>46421</v>
@@ -5770,19 +5782,19 @@
         <v>80</v>
       </c>
       <c r="H28" t="s">
+        <v>176</v>
+      </c>
+      <c r="I28" t="s">
         <v>177</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>178</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>179</v>
       </c>
-      <c r="K28" t="s">
-        <v>180</v>
-      </c>
       <c r="L28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M28" t="s">
         <v>46</v>
@@ -5794,7 +5806,7 @@
         <v>30</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R28" t="s">
         <v>49</v>
@@ -5812,7 +5824,7 @@
     </row>
     <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B29" s="7">
         <v>46422</v>
@@ -5822,28 +5834,28 @@
         <v>Thursday</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G29" s="2">
         <v>6</v>
       </c>
       <c r="H29" t="s">
+        <v>176</v>
+      </c>
+      <c r="I29" t="s">
         <v>177</v>
       </c>
-      <c r="I29" t="s">
-        <v>178</v>
-      </c>
       <c r="J29" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s">
         <v>52</v>
@@ -5855,13 +5867,13 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -5876,7 +5888,7 @@
     </row>
     <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B30" s="7">
         <v>46422</v>
@@ -5889,7 +5901,7 @@
         <v>101</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>38</v>
@@ -5898,49 +5910,49 @@
         <v>80</v>
       </c>
       <c r="H30" t="s">
+        <v>176</v>
+      </c>
+      <c r="I30" t="s">
         <v>177</v>
       </c>
-      <c r="I30" t="s">
-        <v>178</v>
-      </c>
       <c r="J30" t="s">
+        <v>192</v>
+      </c>
+      <c r="K30" t="s">
         <v>193</v>
       </c>
-      <c r="K30" t="s">
-        <v>194</v>
-      </c>
       <c r="M30" t="s">
+        <v>260</v>
+      </c>
+      <c r="N30" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30" t="s">
+        <v>30</v>
+      </c>
+      <c r="P30" t="s">
         <v>261</v>
       </c>
-      <c r="N30" t="s">
-        <v>29</v>
-      </c>
-      <c r="O30" t="s">
-        <v>30</v>
-      </c>
-      <c r="P30" t="s">
-        <v>262</v>
-      </c>
       <c r="Q30" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="R30" t="s">
         <v>293</v>
       </c>
-      <c r="R30" t="s">
+      <c r="S30" t="s">
+        <v>33</v>
+      </c>
+      <c r="T30" t="s">
+        <v>34</v>
+      </c>
+      <c r="U30" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>294</v>
-      </c>
-      <c r="S30" t="s">
-        <v>33</v>
-      </c>
-      <c r="T30" t="s">
-        <v>34</v>
-      </c>
-      <c r="U30" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>295</v>
       </c>
       <c r="B31" s="7">
         <v>46423</v>
@@ -5950,7 +5962,7 @@
         <v>Friday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>37</v>
@@ -5962,16 +5974,16 @@
         <v>24</v>
       </c>
       <c r="H31" t="s">
+        <v>176</v>
+      </c>
+      <c r="I31" t="s">
         <v>177</v>
       </c>
-      <c r="I31" t="s">
-        <v>178</v>
-      </c>
       <c r="J31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K31" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M31" t="s">
         <v>37</v>
@@ -5983,10 +5995,10 @@
         <v>30</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="R31" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -6001,7 +6013,7 @@
     </row>
     <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B32" s="7">
         <v>46426</v>
@@ -6023,19 +6035,19 @@
         <v>80</v>
       </c>
       <c r="H32" t="s">
+        <v>176</v>
+      </c>
+      <c r="I32" t="s">
         <v>177</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>178</v>
       </c>
-      <c r="J32" t="s">
-        <v>179</v>
-      </c>
       <c r="K32" t="s">
+        <v>204</v>
+      </c>
+      <c r="L32" t="s">
         <v>205</v>
-      </c>
-      <c r="L32" t="s">
-        <v>206</v>
       </c>
       <c r="M32" t="s">
         <v>37</v>
@@ -6047,10 +6059,10 @@
         <v>30</v>
       </c>
       <c r="Q32" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="R32" t="s">
         <v>298</v>
-      </c>
-      <c r="R32" t="s">
-        <v>299</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -6065,7 +6077,7 @@
     </row>
     <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B33" s="7">
         <v>46427</v>
@@ -6087,16 +6099,16 @@
         <v>80</v>
       </c>
       <c r="H33" t="s">
+        <v>176</v>
+      </c>
+      <c r="I33" t="s">
         <v>177</v>
       </c>
-      <c r="I33" t="s">
-        <v>178</v>
-      </c>
       <c r="J33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K33" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M33" t="s">
         <v>96</v>
@@ -6108,28 +6120,28 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q33" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="R33" t="s">
         <v>301</v>
       </c>
-      <c r="R33" t="s">
+      <c r="S33" t="s">
+        <v>33</v>
+      </c>
+      <c r="T33" t="s">
+        <v>34</v>
+      </c>
+      <c r="U33" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
         <v>302</v>
-      </c>
-      <c r="S33" t="s">
-        <v>33</v>
-      </c>
-      <c r="T33" t="s">
-        <v>34</v>
-      </c>
-      <c r="U33" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>303</v>
       </c>
       <c r="B34" s="7">
         <v>46427</v>
@@ -6145,25 +6157,25 @@
         <v>80</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H34" t="s">
+        <v>176</v>
+      </c>
+      <c r="I34" t="s">
         <v>177</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>178</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>179</v>
       </c>
-      <c r="K34" t="s">
-        <v>180</v>
-      </c>
       <c r="L34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M34" t="s">
         <v>75</v>
@@ -6175,10 +6187,10 @@
         <v>29</v>
       </c>
       <c r="P34" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q34" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="R34" t="s">
         <v>106</v>
@@ -6195,8 +6207,8 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>306</v>
+      <c r="A35" s="12" t="s">
+        <v>305</v>
       </c>
       <c r="B35" s="7">
         <v>46428</v>
@@ -6218,32 +6230,32 @@
         <v>80</v>
       </c>
       <c r="H35" t="s">
+        <v>176</v>
+      </c>
+      <c r="I35" t="s">
         <v>177</v>
       </c>
-      <c r="I35" t="s">
-        <v>178</v>
-      </c>
       <c r="J35" t="s">
+        <v>192</v>
+      </c>
+      <c r="K35" t="s">
         <v>193</v>
       </c>
-      <c r="K35" t="s">
-        <v>194</v>
-      </c>
       <c r="M35" t="s">
+        <v>265</v>
+      </c>
+      <c r="N35" t="s">
+        <v>30</v>
+      </c>
+      <c r="O35" t="s">
+        <v>29</v>
+      </c>
+      <c r="P35" t="s">
         <v>266</v>
       </c>
-      <c r="N35" t="s">
-        <v>30</v>
-      </c>
-      <c r="O35" t="s">
-        <v>29</v>
-      </c>
-      <c r="P35" t="s">
+      <c r="Q35" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="Q35" s="8" t="s">
-        <v>268</v>
-      </c>
       <c r="S35" t="s">
         <v>33</v>
       </c>
@@ -6256,8 +6268,8 @@
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
-        <v>307</v>
+      <c r="A36" s="12" t="s">
+        <v>306</v>
       </c>
       <c r="B36" s="7">
         <v>46428</v>
@@ -6267,10 +6279,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>38</v>
@@ -6279,19 +6291,19 @@
         <v>80</v>
       </c>
       <c r="H36" t="s">
+        <v>176</v>
+      </c>
+      <c r="I36" t="s">
         <v>177</v>
       </c>
-      <c r="I36" t="s">
-        <v>178</v>
-      </c>
       <c r="J36" t="s">
+        <v>192</v>
+      </c>
+      <c r="K36" t="s">
         <v>193</v>
       </c>
-      <c r="K36" t="s">
-        <v>194</v>
-      </c>
       <c r="M36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N36" t="s">
         <v>30</v>
@@ -6300,11 +6312,11 @@
         <v>29</v>
       </c>
       <c r="P36" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q36" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="Q36" s="8" t="s">
-        <v>237</v>
-      </c>
       <c r="S36" t="s">
         <v>33</v>
       </c>
@@ -6317,8 +6329,8 @@
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>308</v>
+      <c r="A37" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="B37" s="7">
         <v>46430</v>
@@ -6328,7 +6340,7 @@
         <v>Friday</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>37</v>
@@ -6340,16 +6352,16 @@
         <v>24</v>
       </c>
       <c r="H37" t="s">
+        <v>176</v>
+      </c>
+      <c r="I37" t="s">
         <v>177</v>
       </c>
-      <c r="I37" t="s">
-        <v>178</v>
-      </c>
       <c r="J37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K37" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M37" t="s">
         <v>37</v>
@@ -6361,10 +6373,10 @@
         <v>30</v>
       </c>
       <c r="Q37" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -6379,7 +6391,7 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B38" s="7">
         <v>46441</v>
@@ -6401,19 +6413,19 @@
         <v>80</v>
       </c>
       <c r="H38" t="s">
+        <v>176</v>
+      </c>
+      <c r="I38" t="s">
         <v>177</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>178</v>
       </c>
-      <c r="J38" t="s">
-        <v>179</v>
-      </c>
       <c r="K38" t="s">
+        <v>220</v>
+      </c>
+      <c r="L38" t="s">
         <v>221</v>
-      </c>
-      <c r="L38" t="s">
-        <v>222</v>
       </c>
       <c r="M38" t="s">
         <v>108</v>
@@ -6425,28 +6437,28 @@
         <v>30</v>
       </c>
       <c r="P38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q38" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="R38" t="s">
+        <v>224</v>
+      </c>
+      <c r="S38" t="s">
+        <v>33</v>
+      </c>
+      <c r="T38" t="s">
+        <v>34</v>
+      </c>
+      <c r="U38" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
         <v>311</v>
-      </c>
-      <c r="R38" t="s">
-        <v>225</v>
-      </c>
-      <c r="S38" t="s">
-        <v>33</v>
-      </c>
-      <c r="T38" t="s">
-        <v>34</v>
-      </c>
-      <c r="U38" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>312</v>
       </c>
       <c r="B39" s="7">
         <v>46441</v>
@@ -6456,31 +6468,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H39" t="s">
+        <v>176</v>
+      </c>
+      <c r="I39" t="s">
         <v>177</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>178</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>179</v>
       </c>
-      <c r="K39" t="s">
-        <v>180</v>
-      </c>
       <c r="L39" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M39" t="s">
         <v>84</v>
@@ -6492,10 +6504,10 @@
         <v>29</v>
       </c>
       <c r="P39" t="s">
-        <v>314</v>
-      </c>
-      <c r="Q39" s="8" t="s">
-        <v>133</v>
+        <v>313</v>
+      </c>
+      <c r="Q39" s="15" t="s">
+        <v>499</v>
       </c>
       <c r="R39" t="s">
         <v>87</v>
@@ -6513,7 +6525,7 @@
     </row>
     <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B40" s="7">
         <v>46444</v>
@@ -6523,7 +6535,7 @@
         <v>Friday</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>23</v>
@@ -6535,19 +6547,19 @@
         <v>100</v>
       </c>
       <c r="H40" t="s">
+        <v>176</v>
+      </c>
+      <c r="I40" t="s">
         <v>177</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>178</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>179</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>180</v>
-      </c>
-      <c r="L40" t="s">
-        <v>181</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -6559,10 +6571,10 @@
         <v>30</v>
       </c>
       <c r="Q40" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="R40" t="s">
         <v>317</v>
-      </c>
-      <c r="R40" t="s">
-        <v>318</v>
       </c>
       <c r="S40" t="s">
         <v>33</v>
@@ -6591,20 +6603,19 @@
     <hyperlink ref="Q3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="Q5" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
     <hyperlink ref="Q6" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="Q11" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="Q19" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="Q23" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="Q24" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="Q28" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="Q31" r:id="rId10" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="Q33" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="Q37" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="Q39" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="Q19" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="Q23" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="Q24" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="Q28" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="Q31" r:id="rId9" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="Q33" r:id="rId10" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="Q37" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="Q39" r:id="rId12" xr:uid="{C6A1392F-2DEE-417C-927C-B9C444D72EAE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId13"/>
   <tableParts count="1">
-    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId14"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6695,8 +6706,8 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>319</v>
+      <c r="A2" s="14" t="s">
+        <v>318</v>
       </c>
       <c r="B2" s="7">
         <v>46447</v>
@@ -6712,25 +6723,25 @@
         <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H2" t="s">
+        <v>320</v>
+      </c>
+      <c r="I2" t="s">
         <v>321</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>322</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>323</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>324</v>
-      </c>
-      <c r="L2" t="s">
-        <v>325</v>
       </c>
       <c r="M2" t="s">
         <v>75</v>
@@ -6742,10 +6753,10 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="R2" t="s">
         <v>106</v>
@@ -6763,7 +6774,7 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B3" s="7">
         <v>46448</v>
@@ -6773,7 +6784,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>52</v>
@@ -6785,16 +6796,16 @@
         <v>6</v>
       </c>
       <c r="H3" t="s">
+        <v>320</v>
+      </c>
+      <c r="I3" t="s">
         <v>321</v>
       </c>
-      <c r="I3" t="s">
-        <v>322</v>
-      </c>
       <c r="J3" t="s">
+        <v>327</v>
+      </c>
+      <c r="K3" t="s">
         <v>328</v>
-      </c>
-      <c r="K3" t="s">
-        <v>329</v>
       </c>
       <c r="M3" t="s">
         <v>52</v>
@@ -6806,10 +6817,10 @@
         <v>30</v>
       </c>
       <c r="Q3" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="R3" t="s">
         <v>330</v>
-      </c>
-      <c r="R3" t="s">
-        <v>331</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -6824,7 +6835,7 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B4" s="7">
         <v>46449</v>
@@ -6837,7 +6848,7 @@
         <v>101</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>38</v>
@@ -6846,34 +6857,34 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
+        <v>320</v>
+      </c>
+      <c r="I4" t="s">
         <v>321</v>
       </c>
-      <c r="I4" t="s">
-        <v>322</v>
-      </c>
       <c r="J4" t="s">
+        <v>332</v>
+      </c>
+      <c r="K4" t="s">
         <v>333</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
+        <v>260</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q4" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="M4" t="s">
-        <v>261</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" t="s">
         <v>335</v>
-      </c>
-      <c r="R4" t="s">
-        <v>336</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -6888,7 +6899,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B5" s="7">
         <v>46450</v>
@@ -6910,19 +6921,19 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
+        <v>320</v>
+      </c>
+      <c r="I5" t="s">
         <v>321</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>322</v>
       </c>
-      <c r="J5" t="s">
-        <v>323</v>
-      </c>
       <c r="K5" t="s">
+        <v>337</v>
+      </c>
+      <c r="L5" t="s">
         <v>338</v>
-      </c>
-      <c r="L5" t="s">
-        <v>339</v>
       </c>
       <c r="M5" t="s">
         <v>37</v>
@@ -6934,13 +6945,13 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="R5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -6955,7 +6966,7 @@
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B6" s="7">
         <v>46455</v>
@@ -6977,16 +6988,16 @@
         <v>80</v>
       </c>
       <c r="H6" t="s">
+        <v>320</v>
+      </c>
+      <c r="I6" t="s">
         <v>321</v>
       </c>
-      <c r="I6" t="s">
-        <v>322</v>
-      </c>
       <c r="J6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M6" t="s">
         <v>108</v>
@@ -6998,28 +7009,28 @@
         <v>30</v>
       </c>
       <c r="P6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q6" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="R6" t="s">
         <v>343</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
+        <v>33</v>
+      </c>
+      <c r="T6" t="s">
+        <v>34</v>
+      </c>
+      <c r="U6" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>344</v>
-      </c>
-      <c r="S6" t="s">
-        <v>33</v>
-      </c>
-      <c r="T6" t="s">
-        <v>34</v>
-      </c>
-      <c r="U6" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>345</v>
       </c>
       <c r="B7" s="7">
         <v>46455</v>
@@ -7029,7 +7040,7 @@
         <v>Tuesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>80</v>
@@ -7041,19 +7052,19 @@
         <v>82</v>
       </c>
       <c r="H7" t="s">
+        <v>320</v>
+      </c>
+      <c r="I7" t="s">
         <v>321</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>322</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>323</v>
       </c>
-      <c r="K7" t="s">
-        <v>324</v>
-      </c>
       <c r="L7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M7" t="s">
         <v>84</v>
@@ -7065,10 +7076,10 @@
         <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>133</v>
+        <v>347</v>
+      </c>
+      <c r="Q7" s="15" t="s">
+        <v>500</v>
       </c>
       <c r="R7" t="s">
         <v>87</v>
@@ -7085,8 +7096,8 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>349</v>
+      <c r="A8" s="12" t="s">
+        <v>348</v>
       </c>
       <c r="B8" s="7">
         <v>46456</v>
@@ -7096,10 +7107,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
@@ -7108,19 +7119,19 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
+        <v>320</v>
+      </c>
+      <c r="I8" t="s">
         <v>321</v>
       </c>
-      <c r="I8" t="s">
-        <v>322</v>
-      </c>
       <c r="J8" t="s">
+        <v>332</v>
+      </c>
+      <c r="K8" t="s">
         <v>333</v>
       </c>
-      <c r="K8" t="s">
-        <v>334</v>
-      </c>
       <c r="M8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -7129,10 +7140,10 @@
         <v>29</v>
       </c>
       <c r="P8" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q8" s="8" t="s">
         <v>236</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>237</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -7147,7 +7158,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B9" s="7">
         <v>46456</v>
@@ -7169,16 +7180,16 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
+        <v>320</v>
+      </c>
+      <c r="I9" t="s">
         <v>321</v>
       </c>
-      <c r="I9" t="s">
-        <v>322</v>
-      </c>
       <c r="J9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M9" t="s">
         <v>96</v>
@@ -7190,13 +7201,13 @@
         <v>30</v>
       </c>
       <c r="P9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q9" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="R9" t="s">
         <v>351</v>
-      </c>
-      <c r="R9" t="s">
-        <v>352</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -7211,7 +7222,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B10" s="7">
         <v>46457</v>
@@ -7233,16 +7244,16 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
+        <v>320</v>
+      </c>
+      <c r="I10" t="s">
         <v>321</v>
       </c>
-      <c r="I10" t="s">
-        <v>322</v>
-      </c>
       <c r="J10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="M10" t="s">
         <v>37</v>
@@ -7254,10 +7265,10 @@
         <v>30</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="R10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -7272,7 +7283,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B11" s="7">
         <v>46462</v>
@@ -7285,7 +7296,7 @@
         <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>38</v>
@@ -7294,34 +7305,34 @@
         <v>80</v>
       </c>
       <c r="H11" t="s">
+        <v>320</v>
+      </c>
+      <c r="I11" t="s">
         <v>321</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>322</v>
       </c>
-      <c r="J11" t="s">
-        <v>323</v>
-      </c>
       <c r="K11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L11" t="s">
+        <v>355</v>
+      </c>
+      <c r="M11" t="s">
+        <v>145</v>
+      </c>
+      <c r="N11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q11" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="M11" t="s">
-        <v>146</v>
-      </c>
-      <c r="N11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>357</v>
-      </c>
       <c r="R11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -7336,7 +7347,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B12" s="7">
         <v>46462</v>
@@ -7358,34 +7369,34 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
+        <v>320</v>
+      </c>
+      <c r="I12" t="s">
         <v>321</v>
       </c>
-      <c r="I12" t="s">
-        <v>322</v>
-      </c>
       <c r="J12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M12" t="s">
+        <v>358</v>
+      </c>
+      <c r="N12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q12" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="N12" t="s">
-        <v>29</v>
-      </c>
-      <c r="O12" t="s">
-        <v>30</v>
-      </c>
-      <c r="P12" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q12" s="8" t="s">
+      <c r="R12" t="s">
         <v>360</v>
-      </c>
-      <c r="R12" t="s">
-        <v>361</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -7400,7 +7411,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B13" s="7">
         <v>46463</v>
@@ -7422,19 +7433,19 @@
         <v>80</v>
       </c>
       <c r="H13" t="s">
+        <v>320</v>
+      </c>
+      <c r="I13" t="s">
         <v>321</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>322</v>
       </c>
-      <c r="J13" t="s">
-        <v>323</v>
-      </c>
       <c r="K13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M13" t="s">
         <v>52</v>
@@ -7449,10 +7460,10 @@
         <v>55</v>
       </c>
       <c r="Q13" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="R13" t="s">
         <v>364</v>
-      </c>
-      <c r="R13" t="s">
-        <v>365</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -7467,7 +7478,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B14" s="7">
         <v>46464</v>
@@ -7477,10 +7488,10 @@
         <v>Thursday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -7489,34 +7500,34 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
+        <v>320</v>
+      </c>
+      <c r="I14" t="s">
         <v>321</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>322</v>
       </c>
-      <c r="J14" t="s">
-        <v>323</v>
-      </c>
       <c r="K14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L14" t="s">
+        <v>367</v>
+      </c>
+      <c r="M14" t="s">
+        <v>260</v>
+      </c>
+      <c r="N14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="M14" t="s">
-        <v>261</v>
-      </c>
-      <c r="N14" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q14" s="8" t="s">
+      <c r="R14" t="s">
         <v>369</v>
-      </c>
-      <c r="R14" t="s">
-        <v>370</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -7531,7 +7542,7 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B15" s="7">
         <v>46468</v>
@@ -7553,19 +7564,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
+        <v>320</v>
+      </c>
+      <c r="I15" t="s">
         <v>321</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>322</v>
       </c>
-      <c r="J15" t="s">
-        <v>323</v>
-      </c>
       <c r="K15" t="s">
+        <v>337</v>
+      </c>
+      <c r="L15" t="s">
         <v>338</v>
-      </c>
-      <c r="L15" t="s">
-        <v>339</v>
       </c>
       <c r="M15" t="s">
         <v>37</v>
@@ -7577,10 +7588,10 @@
         <v>30</v>
       </c>
       <c r="Q15" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="R15" t="s">
         <v>372</v>
-      </c>
-      <c r="R15" t="s">
-        <v>373</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -7595,7 +7606,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B16" s="7">
         <v>46469</v>
@@ -7605,28 +7616,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>120</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
       </c>
       <c r="H16" t="s">
+        <v>320</v>
+      </c>
+      <c r="I16" t="s">
         <v>321</v>
       </c>
-      <c r="I16" t="s">
-        <v>322</v>
-      </c>
       <c r="J16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K16" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M16" t="s">
         <v>120</v>
@@ -7638,13 +7649,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q16" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="Q16" s="8" t="s">
+      <c r="R16" t="s">
         <v>379</v>
-      </c>
-      <c r="R16" t="s">
-        <v>380</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -7659,7 +7670,7 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B17" s="7">
         <v>46470</v>
@@ -7681,19 +7692,19 @@
         <v>80</v>
       </c>
       <c r="H17" t="s">
+        <v>320</v>
+      </c>
+      <c r="I17" t="s">
         <v>321</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>322</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>323</v>
       </c>
-      <c r="K17" t="s">
-        <v>324</v>
-      </c>
       <c r="L17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="M17" t="s">
         <v>46</v>
@@ -7705,7 +7716,7 @@
         <v>30</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R17" t="s">
         <v>49</v>
@@ -7723,7 +7734,7 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B18" s="7">
         <v>46486</v>
@@ -7733,7 +7744,7 @@
         <v>Friday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>120</v>
@@ -7745,19 +7756,19 @@
         <v>80</v>
       </c>
       <c r="H18" t="s">
+        <v>320</v>
+      </c>
+      <c r="I18" t="s">
         <v>321</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>322</v>
       </c>
-      <c r="J18" t="s">
-        <v>323</v>
-      </c>
       <c r="K18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M18" t="s">
         <v>75</v>
@@ -7769,13 +7780,13 @@
         <v>30</v>
       </c>
       <c r="P18" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q18" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="Q18" s="8" t="s">
+      <c r="R18" t="s">
         <v>386</v>
-      </c>
-      <c r="R18" t="s">
-        <v>387</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -7790,7 +7801,7 @@
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B19" s="7">
         <v>46492</v>
@@ -7812,16 +7823,16 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
+        <v>320</v>
+      </c>
+      <c r="I19" t="s">
         <v>321</v>
       </c>
-      <c r="I19" t="s">
-        <v>322</v>
-      </c>
       <c r="J19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M19" t="s">
         <v>37</v>
@@ -7833,13 +7844,13 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q19" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="Q19" s="8" t="s">
+      <c r="R19" t="s">
         <v>390</v>
-      </c>
-      <c r="R19" t="s">
-        <v>391</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -7854,7 +7865,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B20" s="7">
         <v>46496</v>
@@ -7876,19 +7887,19 @@
         <v>100</v>
       </c>
       <c r="H20" t="s">
+        <v>320</v>
+      </c>
+      <c r="I20" t="s">
         <v>321</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>322</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>323</v>
       </c>
-      <c r="K20" t="s">
-        <v>324</v>
-      </c>
       <c r="L20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M20" t="s">
         <v>23</v>
@@ -7900,10 +7911,10 @@
         <v>30</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="R20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -7918,7 +7929,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B21" s="7">
         <v>46500</v>
@@ -7928,7 +7939,7 @@
         <v>Friday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>108</v>
@@ -7940,16 +7951,16 @@
         <v>16</v>
       </c>
       <c r="H21" t="s">
+        <v>320</v>
+      </c>
+      <c r="I21" t="s">
         <v>321</v>
       </c>
-      <c r="I21" t="s">
-        <v>322</v>
-      </c>
       <c r="J21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M21" t="s">
         <v>108</v>
@@ -7961,13 +7972,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q21" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="Q21" s="8" t="s">
+      <c r="R21" t="s">
         <v>398</v>
-      </c>
-      <c r="R21" t="s">
-        <v>399</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -7982,7 +7993,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B22" s="7">
         <v>46505</v>
@@ -7992,7 +8003,7 @@
         <v>Wednesday</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>52</v>
@@ -8004,16 +8015,16 @@
         <v>6</v>
       </c>
       <c r="H22" t="s">
+        <v>320</v>
+      </c>
+      <c r="I22" t="s">
         <v>321</v>
       </c>
-      <c r="I22" t="s">
-        <v>322</v>
-      </c>
       <c r="J22" t="s">
+        <v>327</v>
+      </c>
+      <c r="K22" t="s">
         <v>328</v>
-      </c>
-      <c r="K22" t="s">
-        <v>329</v>
       </c>
       <c r="M22" t="s">
         <v>52</v>
@@ -8025,25 +8036,25 @@
         <v>30</v>
       </c>
       <c r="Q22" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="R22" t="s">
+        <v>330</v>
+      </c>
+      <c r="S22" t="s">
+        <v>33</v>
+      </c>
+      <c r="T22" t="s">
+        <v>34</v>
+      </c>
+      <c r="U22" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
         <v>401</v>
-      </c>
-      <c r="R22" t="s">
-        <v>331</v>
-      </c>
-      <c r="S22" t="s">
-        <v>33</v>
-      </c>
-      <c r="T22" t="s">
-        <v>34</v>
-      </c>
-      <c r="U22" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>402</v>
       </c>
       <c r="B23" s="7">
         <v>46506</v>
@@ -8065,16 +8076,16 @@
         <v>80</v>
       </c>
       <c r="H23" t="s">
+        <v>320</v>
+      </c>
+      <c r="I23" t="s">
         <v>321</v>
       </c>
-      <c r="I23" t="s">
-        <v>322</v>
-      </c>
       <c r="J23" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K23" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M23" t="s">
         <v>37</v>
@@ -8086,13 +8097,13 @@
         <v>29</v>
       </c>
       <c r="P23" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q23" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="Q23" s="8" t="s">
+      <c r="R23" t="s">
         <v>390</v>
-      </c>
-      <c r="R23" t="s">
-        <v>391</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -8129,16 +8140,16 @@
         <v>80</v>
       </c>
       <c r="H24" t="s">
+        <v>320</v>
+      </c>
+      <c r="I24" t="s">
         <v>321</v>
       </c>
-      <c r="I24" t="s">
-        <v>322</v>
-      </c>
       <c r="J24" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K24" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M24" t="s">
         <v>96</v>
@@ -8153,7 +8164,7 @@
         <v>126</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="R24" t="s">
         <v>128</v>
@@ -8171,7 +8182,7 @@
     </row>
     <row r="25" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B25" s="7">
         <v>46512</v>
@@ -8181,10 +8192,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>38</v>
@@ -8193,22 +8204,22 @@
         <v>80</v>
       </c>
       <c r="H25" t="s">
+        <v>320</v>
+      </c>
+      <c r="I25" t="s">
         <v>321</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>322</v>
       </c>
-      <c r="J25" t="s">
-        <v>323</v>
-      </c>
       <c r="K25" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L25" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M25" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N25" t="s">
         <v>29</v>
@@ -8217,10 +8228,10 @@
         <v>30</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="R25" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -8235,7 +8246,7 @@
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B26" s="7">
         <v>46512</v>
@@ -8257,19 +8268,19 @@
         <v>80</v>
       </c>
       <c r="H26" t="s">
+        <v>320</v>
+      </c>
+      <c r="I26" t="s">
         <v>321</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>322</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>323</v>
       </c>
-      <c r="K26" t="s">
-        <v>324</v>
-      </c>
       <c r="L26" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="M26" t="s">
         <v>46</v>
@@ -8281,7 +8292,7 @@
         <v>30</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="R26" t="s">
         <v>49</v>
@@ -8299,7 +8310,7 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B27" s="7">
         <v>46513</v>
@@ -8309,7 +8320,7 @@
         <v>Thursday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>37</v>
@@ -8321,16 +8332,16 @@
         <v>80</v>
       </c>
       <c r="H27" t="s">
+        <v>320</v>
+      </c>
+      <c r="I27" t="s">
         <v>321</v>
       </c>
-      <c r="I27" t="s">
-        <v>322</v>
-      </c>
       <c r="J27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K27" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M27" t="s">
         <v>37</v>
@@ -8342,25 +8353,25 @@
         <v>30</v>
       </c>
       <c r="Q27" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="R27" t="s">
+        <v>138</v>
+      </c>
+      <c r="S27" t="s">
+        <v>33</v>
+      </c>
+      <c r="T27" t="s">
+        <v>34</v>
+      </c>
+      <c r="U27" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
         <v>409</v>
-      </c>
-      <c r="R27" t="s">
-        <v>139</v>
-      </c>
-      <c r="S27" t="s">
-        <v>33</v>
-      </c>
-      <c r="T27" t="s">
-        <v>34</v>
-      </c>
-      <c r="U27" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
-        <v>410</v>
       </c>
       <c r="B28" s="7">
         <v>46517</v>
@@ -8376,25 +8387,25 @@
         <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H28" t="s">
+        <v>320</v>
+      </c>
+      <c r="I28" t="s">
         <v>321</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>322</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>323</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>324</v>
-      </c>
-      <c r="L28" t="s">
-        <v>325</v>
       </c>
       <c r="M28" t="s">
         <v>75</v>
@@ -8406,10 +8417,10 @@
         <v>29</v>
       </c>
       <c r="P28" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="R28" t="s">
         <v>106</v>
@@ -8427,7 +8438,7 @@
     </row>
     <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B29" s="7">
         <v>46518</v>
@@ -8449,19 +8460,19 @@
         <v>80</v>
       </c>
       <c r="H29" t="s">
+        <v>320</v>
+      </c>
+      <c r="I29" t="s">
         <v>321</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>322</v>
       </c>
-      <c r="J29" t="s">
-        <v>323</v>
-      </c>
       <c r="K29" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L29" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M29" t="s">
         <v>108</v>
@@ -8473,13 +8484,13 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="R29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -8494,7 +8505,7 @@
     </row>
     <row r="30" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B30" s="7">
         <v>46519</v>
@@ -8504,10 +8515,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>38</v>
@@ -8516,19 +8527,19 @@
         <v>80</v>
       </c>
       <c r="H30" t="s">
+        <v>320</v>
+      </c>
+      <c r="I30" t="s">
         <v>321</v>
       </c>
-      <c r="I30" t="s">
-        <v>322</v>
-      </c>
       <c r="J30" t="s">
+        <v>332</v>
+      </c>
+      <c r="K30" t="s">
         <v>333</v>
       </c>
-      <c r="K30" t="s">
-        <v>334</v>
-      </c>
       <c r="M30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
@@ -8537,13 +8548,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="R30" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -8558,7 +8569,7 @@
     </row>
     <row r="31" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B31" s="7">
         <v>46520</v>
@@ -8568,7 +8579,7 @@
         <v>Thursday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>84</v>
@@ -8580,16 +8591,16 @@
         <v>80</v>
       </c>
       <c r="H31" t="s">
+        <v>320</v>
+      </c>
+      <c r="I31" t="s">
         <v>321</v>
       </c>
-      <c r="I31" t="s">
-        <v>322</v>
-      </c>
       <c r="J31" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K31" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M31" t="s">
         <v>84</v>
@@ -8601,10 +8612,10 @@
         <v>30</v>
       </c>
       <c r="Q31" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="R31" t="s">
         <v>419</v>
-      </c>
-      <c r="R31" t="s">
-        <v>420</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -8619,7 +8630,7 @@
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B32" s="7">
         <v>46525</v>
@@ -8641,19 +8652,19 @@
         <v>80</v>
       </c>
       <c r="H32" t="s">
+        <v>320</v>
+      </c>
+      <c r="I32" t="s">
         <v>321</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>322</v>
       </c>
-      <c r="J32" t="s">
-        <v>323</v>
-      </c>
       <c r="K32" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L32" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M32" t="s">
         <v>52</v>
@@ -8668,10 +8679,10 @@
         <v>55</v>
       </c>
       <c r="Q32" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="R32" t="s">
         <v>422</v>
-      </c>
-      <c r="R32" t="s">
-        <v>423</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -8686,7 +8697,7 @@
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B33" s="7">
         <v>46526</v>
@@ -8696,7 +8707,7 @@
         <v>Wednesday</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>46</v>
@@ -8708,16 +8719,16 @@
         <v>16</v>
       </c>
       <c r="H33" t="s">
+        <v>320</v>
+      </c>
+      <c r="I33" t="s">
         <v>321</v>
       </c>
-      <c r="I33" t="s">
-        <v>322</v>
-      </c>
       <c r="J33" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M33" t="s">
         <v>96</v>
@@ -8729,28 +8740,28 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q33" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="R33" t="s">
+        <v>154</v>
+      </c>
+      <c r="S33" t="s">
+        <v>33</v>
+      </c>
+      <c r="T33" t="s">
+        <v>34</v>
+      </c>
+      <c r="U33" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
         <v>424</v>
-      </c>
-      <c r="R33" t="s">
-        <v>155</v>
-      </c>
-      <c r="S33" t="s">
-        <v>33</v>
-      </c>
-      <c r="T33" t="s">
-        <v>34</v>
-      </c>
-      <c r="U33" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
-        <v>425</v>
       </c>
       <c r="B34" s="7">
         <v>46527</v>
@@ -8772,16 +8783,16 @@
         <v>80</v>
       </c>
       <c r="H34" t="s">
+        <v>320</v>
+      </c>
+      <c r="I34" t="s">
         <v>321</v>
       </c>
-      <c r="I34" t="s">
-        <v>322</v>
-      </c>
       <c r="J34" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K34" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M34" t="s">
         <v>37</v>
@@ -8793,14 +8804,14 @@
         <v>29</v>
       </c>
       <c r="P34" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q34" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="Q34" s="8" t="s">
+      <c r="R34" t="s">
         <v>390</v>
       </c>
-      <c r="R34" t="s">
-        <v>391</v>
-      </c>
       <c r="S34" t="s">
         <v>33</v>
       </c>
@@ -8813,8 +8824,8 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>426</v>
+      <c r="A35" s="14" t="s">
+        <v>425</v>
       </c>
       <c r="B35" s="7">
         <v>46527</v>
@@ -8824,31 +8835,31 @@
         <v>Thursday</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H35" t="s">
+        <v>320</v>
+      </c>
+      <c r="I35" t="s">
         <v>321</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>322</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>323</v>
       </c>
-      <c r="K35" t="s">
-        <v>324</v>
-      </c>
       <c r="L35" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M35" t="s">
         <v>84</v>
@@ -8860,10 +8871,10 @@
         <v>29</v>
       </c>
       <c r="P35" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q35" s="8" t="s">
-        <v>133</v>
+        <v>501</v>
       </c>
       <c r="R35" t="s">
         <v>87</v>
@@ -8881,7 +8892,7 @@
     </row>
     <row r="36" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B36" s="7">
         <v>46533</v>
@@ -8891,31 +8902,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="G36" s="2">
         <v>12</v>
       </c>
       <c r="H36" t="s">
+        <v>320</v>
+      </c>
+      <c r="I36" t="s">
         <v>321</v>
       </c>
-      <c r="I36" t="s">
-        <v>322</v>
-      </c>
       <c r="J36" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K36" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N36" t="s">
         <v>29</v>
@@ -8924,25 +8935,25 @@
         <v>30</v>
       </c>
       <c r="Q36" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="R36" t="s">
+        <v>198</v>
+      </c>
+      <c r="S36" t="s">
+        <v>33</v>
+      </c>
+      <c r="T36" t="s">
+        <v>34</v>
+      </c>
+      <c r="U36" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
         <v>431</v>
-      </c>
-      <c r="R36" t="s">
-        <v>199</v>
-      </c>
-      <c r="S36" t="s">
-        <v>33</v>
-      </c>
-      <c r="T36" t="s">
-        <v>34</v>
-      </c>
-      <c r="U36" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>432</v>
       </c>
       <c r="B37" s="7">
         <v>46534</v>
@@ -8952,7 +8963,7 @@
         <v>Thursday</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>84</v>
@@ -8964,16 +8975,16 @@
         <v>80</v>
       </c>
       <c r="H37" t="s">
+        <v>320</v>
+      </c>
+      <c r="I37" t="s">
         <v>321</v>
       </c>
-      <c r="I37" t="s">
-        <v>322</v>
-      </c>
       <c r="J37" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M37" t="s">
         <v>84</v>
@@ -8985,7 +8996,7 @@
         <v>29</v>
       </c>
       <c r="Q37" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -9011,17 +9022,16 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="Q6" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="Q7" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="Q21" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="Q23" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="Q34" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="Q35" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="Q37" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="Q21" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="Q23" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="Q34" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="Q37" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="Q7" r:id="rId6" xr:uid="{F0AD118D-06F4-42C5-A9C0-E95F9538750E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId7"/>
   <tableParts count="1">
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9112,8 +9122,8 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>433</v>
+      <c r="A2" s="14" t="s">
+        <v>432</v>
       </c>
       <c r="B2" s="7">
         <v>46546</v>
@@ -9129,25 +9139,25 @@
         <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H2" t="s">
+        <v>434</v>
+      </c>
+      <c r="I2" t="s">
         <v>435</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>436</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>437</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>438</v>
-      </c>
-      <c r="L2" t="s">
-        <v>439</v>
       </c>
       <c r="M2" t="s">
         <v>75</v>
@@ -9159,10 +9169,10 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="R2" t="s">
         <v>106</v>
@@ -9180,7 +9190,7 @@
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B3" s="7">
         <v>46547</v>
@@ -9202,19 +9212,19 @@
         <v>80</v>
       </c>
       <c r="H3" t="s">
+        <v>434</v>
+      </c>
+      <c r="I3" t="s">
         <v>435</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>436</v>
       </c>
-      <c r="J3" t="s">
-        <v>437</v>
-      </c>
       <c r="K3" t="s">
+        <v>441</v>
+      </c>
+      <c r="L3" t="s">
         <v>442</v>
-      </c>
-      <c r="L3" t="s">
-        <v>443</v>
       </c>
       <c r="M3" t="s">
         <v>84</v>
@@ -9229,10 +9239,10 @@
         <v>115</v>
       </c>
       <c r="Q3" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="R3" t="s">
         <v>444</v>
-      </c>
-      <c r="R3" t="s">
-        <v>445</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -9247,7 +9257,7 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B4" s="7">
         <v>46548</v>
@@ -9269,19 +9279,19 @@
         <v>80</v>
       </c>
       <c r="H4" t="s">
+        <v>434</v>
+      </c>
+      <c r="I4" t="s">
         <v>435</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>436</v>
       </c>
-      <c r="J4" t="s">
-        <v>437</v>
-      </c>
       <c r="K4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L4" t="s">
         <v>447</v>
-      </c>
-      <c r="L4" t="s">
-        <v>448</v>
       </c>
       <c r="M4" t="s">
         <v>37</v>
@@ -9293,13 +9303,13 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -9314,7 +9324,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B5" s="7">
         <v>46552</v>
@@ -9324,7 +9334,7 @@
         <v>Monday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>46</v>
@@ -9336,16 +9346,16 @@
         <v>80</v>
       </c>
       <c r="H5" t="s">
+        <v>434</v>
+      </c>
+      <c r="I5" t="s">
         <v>435</v>
       </c>
-      <c r="I5" t="s">
-        <v>436</v>
-      </c>
       <c r="J5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M5" t="s">
         <v>96</v>
@@ -9357,13 +9367,13 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q5" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="R5" t="s">
         <v>452</v>
-      </c>
-      <c r="R5" t="s">
-        <v>453</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -9378,7 +9388,7 @@
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B6" s="7">
         <v>46553</v>
@@ -9400,19 +9410,19 @@
         <v>100</v>
       </c>
       <c r="H6" t="s">
+        <v>434</v>
+      </c>
+      <c r="I6" t="s">
         <v>435</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>436</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>437</v>
       </c>
-      <c r="K6" t="s">
-        <v>438</v>
-      </c>
       <c r="L6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
@@ -9424,25 +9434,25 @@
         <v>30</v>
       </c>
       <c r="Q6" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="R6" t="s">
+        <v>317</v>
+      </c>
+      <c r="S6" t="s">
+        <v>33</v>
+      </c>
+      <c r="T6" t="s">
+        <v>34</v>
+      </c>
+      <c r="U6" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>456</v>
-      </c>
-      <c r="R6" t="s">
-        <v>318</v>
-      </c>
-      <c r="S6" t="s">
-        <v>33</v>
-      </c>
-      <c r="T6" t="s">
-        <v>34</v>
-      </c>
-      <c r="U6" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>457</v>
       </c>
       <c r="B7" s="7">
         <v>46554</v>
@@ -9452,10 +9462,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>38</v>
@@ -9464,19 +9474,19 @@
         <v>80</v>
       </c>
       <c r="H7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I7" t="s">
         <v>435</v>
       </c>
-      <c r="I7" t="s">
-        <v>436</v>
-      </c>
       <c r="J7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N7" t="s">
         <v>30</v>
@@ -9485,10 +9495,10 @@
         <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -9503,7 +9513,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B8" s="7">
         <v>46561</v>
@@ -9525,34 +9535,34 @@
         <v>80</v>
       </c>
       <c r="H8" t="s">
+        <v>434</v>
+      </c>
+      <c r="I8" t="s">
         <v>435</v>
       </c>
-      <c r="I8" t="s">
-        <v>436</v>
-      </c>
       <c r="J8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M8" t="s">
+        <v>265</v>
+      </c>
+      <c r="N8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" t="s">
         <v>266</v>
       </c>
-      <c r="N8" t="s">
-        <v>30</v>
-      </c>
-      <c r="O8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P8" t="s">
-        <v>267</v>
-      </c>
       <c r="Q8" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="R8" t="s">
         <v>459</v>
-      </c>
-      <c r="R8" t="s">
-        <v>460</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -9567,7 +9577,7 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B9" s="7">
         <v>46562</v>
@@ -9580,7 +9590,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>38</v>
@@ -9589,34 +9599,34 @@
         <v>80</v>
       </c>
       <c r="H9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I9" t="s">
         <v>435</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>436</v>
       </c>
-      <c r="J9" t="s">
-        <v>437</v>
-      </c>
       <c r="K9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L9" t="s">
+        <v>461</v>
+      </c>
+      <c r="M9" t="s">
+        <v>145</v>
+      </c>
+      <c r="N9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="M9" t="s">
-        <v>146</v>
-      </c>
-      <c r="N9" t="s">
-        <v>29</v>
-      </c>
-      <c r="O9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>463</v>
-      </c>
       <c r="R9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -9631,7 +9641,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B10" s="7">
         <v>46568</v>
@@ -9653,19 +9663,19 @@
         <v>80</v>
       </c>
       <c r="H10" t="s">
+        <v>434</v>
+      </c>
+      <c r="I10" t="s">
         <v>435</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>436</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>437</v>
       </c>
-      <c r="K10" t="s">
-        <v>438</v>
-      </c>
       <c r="L10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M10" t="s">
         <v>46</v>
@@ -9677,7 +9687,7 @@
         <v>30</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="R10" t="s">
         <v>49</v>
@@ -9695,7 +9705,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B11" s="7">
         <v>46569</v>
@@ -9705,10 +9715,10 @@
         <v>Thursday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>38</v>
@@ -9717,34 +9727,34 @@
         <v>80</v>
       </c>
       <c r="H11" t="s">
+        <v>434</v>
+      </c>
+      <c r="I11" t="s">
         <v>435</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>436</v>
       </c>
-      <c r="J11" t="s">
-        <v>437</v>
-      </c>
       <c r="K11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L11" t="s">
+        <v>467</v>
+      </c>
+      <c r="M11" t="s">
+        <v>260</v>
+      </c>
+      <c r="N11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q11" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="M11" t="s">
-        <v>261</v>
-      </c>
-      <c r="N11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>469</v>
-      </c>
       <c r="R11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -9759,7 +9769,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B12" s="7">
         <v>46570</v>
@@ -9781,16 +9791,16 @@
         <v>16</v>
       </c>
       <c r="H12" t="s">
+        <v>434</v>
+      </c>
+      <c r="I12" t="s">
         <v>435</v>
       </c>
-      <c r="I12" t="s">
-        <v>436</v>
-      </c>
       <c r="J12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M12" t="s">
         <v>63</v>
@@ -9805,25 +9815,25 @@
         <v>126</v>
       </c>
       <c r="Q12" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="R12" t="s">
         <v>472</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
+        <v>33</v>
+      </c>
+      <c r="T12" t="s">
+        <v>34</v>
+      </c>
+      <c r="U12" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>473</v>
-      </c>
-      <c r="S12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T12" t="s">
-        <v>34</v>
-      </c>
-      <c r="U12" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>474</v>
       </c>
       <c r="B13" s="7">
         <v>46574</v>
@@ -9839,25 +9849,25 @@
         <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H13" t="s">
+        <v>434</v>
+      </c>
+      <c r="I13" t="s">
         <v>435</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>436</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>437</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>438</v>
-      </c>
-      <c r="L13" t="s">
-        <v>439</v>
       </c>
       <c r="M13" t="s">
         <v>75</v>
@@ -9869,10 +9879,10 @@
         <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="R13" t="s">
         <v>106</v>
@@ -9889,8 +9899,8 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>477</v>
+      <c r="A14" s="12" t="s">
+        <v>476</v>
       </c>
       <c r="B14" s="7">
         <v>46575</v>
@@ -9912,31 +9922,31 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
+        <v>434</v>
+      </c>
+      <c r="I14" t="s">
         <v>435</v>
       </c>
-      <c r="I14" t="s">
-        <v>436</v>
-      </c>
       <c r="J14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M14" t="s">
+        <v>265</v>
+      </c>
+      <c r="N14" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" t="s">
+        <v>29</v>
+      </c>
+      <c r="P14" t="s">
         <v>266</v>
       </c>
-      <c r="N14" t="s">
-        <v>30</v>
-      </c>
-      <c r="O14" t="s">
-        <v>29</v>
-      </c>
-      <c r="P14" t="s">
-        <v>267</v>
-      </c>
       <c r="Q14" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -9950,8 +9960,8 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>478</v>
+      <c r="A15" s="12" t="s">
+        <v>477</v>
       </c>
       <c r="B15" s="7">
         <v>46575</v>
@@ -9961,10 +9971,10 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>38</v>
@@ -9973,19 +9983,19 @@
         <v>80</v>
       </c>
       <c r="H15" t="s">
+        <v>434</v>
+      </c>
+      <c r="I15" t="s">
         <v>435</v>
       </c>
-      <c r="I15" t="s">
-        <v>436</v>
-      </c>
       <c r="J15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N15" t="s">
         <v>30</v>
@@ -9994,10 +10004,10 @@
         <v>29</v>
       </c>
       <c r="P15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -10012,7 +10022,7 @@
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B16" s="7">
         <v>46576</v>
@@ -10034,16 +10044,16 @@
         <v>80</v>
       </c>
       <c r="H16" t="s">
+        <v>434</v>
+      </c>
+      <c r="I16" t="s">
         <v>435</v>
       </c>
-      <c r="I16" t="s">
-        <v>436</v>
-      </c>
       <c r="J16" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K16" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M16" t="s">
         <v>96</v>
@@ -10058,25 +10068,25 @@
         <v>126</v>
       </c>
       <c r="Q16" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="R16" t="s">
+        <v>227</v>
+      </c>
+      <c r="S16" t="s">
+        <v>33</v>
+      </c>
+      <c r="T16" t="s">
+        <v>34</v>
+      </c>
+      <c r="U16" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>479</v>
-      </c>
-      <c r="R16" t="s">
-        <v>228</v>
-      </c>
-      <c r="S16" t="s">
-        <v>33</v>
-      </c>
-      <c r="T16" t="s">
-        <v>34</v>
-      </c>
-      <c r="U16" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>480</v>
       </c>
       <c r="B17" s="7">
         <v>46582</v>
@@ -10092,25 +10102,25 @@
         <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H17" t="s">
+        <v>434</v>
+      </c>
+      <c r="I17" t="s">
         <v>435</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>436</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>437</v>
       </c>
-      <c r="K17" t="s">
-        <v>438</v>
-      </c>
       <c r="L17" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M17" t="s">
         <v>84</v>
@@ -10122,10 +10132,10 @@
         <v>29</v>
       </c>
       <c r="P17" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>133</v>
+        <v>502</v>
       </c>
       <c r="R17" t="s">
         <v>87</v>
@@ -10142,8 +10152,8 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>483</v>
+      <c r="A18" s="12" t="s">
+        <v>482</v>
       </c>
       <c r="B18" s="7">
         <v>46589</v>
@@ -10165,31 +10175,31 @@
         <v>80</v>
       </c>
       <c r="H18" t="s">
+        <v>434</v>
+      </c>
+      <c r="I18" t="s">
         <v>435</v>
       </c>
-      <c r="I18" t="s">
-        <v>436</v>
-      </c>
       <c r="J18" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K18" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M18" t="s">
+        <v>265</v>
+      </c>
+      <c r="N18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" t="s">
+        <v>29</v>
+      </c>
+      <c r="P18" t="s">
         <v>266</v>
       </c>
-      <c r="N18" t="s">
-        <v>30</v>
-      </c>
-      <c r="O18" t="s">
-        <v>29</v>
-      </c>
-      <c r="P18" t="s">
-        <v>267</v>
-      </c>
       <c r="Q18" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -10203,8 +10213,8 @@
       </c>
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
-        <v>484</v>
+      <c r="A19" s="14" t="s">
+        <v>483</v>
       </c>
       <c r="B19" s="7">
         <v>46604</v>
@@ -10220,25 +10230,25 @@
         <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>82</v>
       </c>
       <c r="H19" t="s">
+        <v>434</v>
+      </c>
+      <c r="I19" t="s">
         <v>435</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>436</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>437</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>438</v>
-      </c>
-      <c r="L19" t="s">
-        <v>439</v>
       </c>
       <c r="M19" t="s">
         <v>75</v>
@@ -10250,10 +10260,10 @@
         <v>29</v>
       </c>
       <c r="P19" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="R19" t="s">
         <v>106</v>
@@ -10271,7 +10281,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B20" s="7">
         <v>46612</v>
@@ -10281,7 +10291,7 @@
         <v>Friday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>120</v>
@@ -10293,19 +10303,19 @@
         <v>80</v>
       </c>
       <c r="H20" t="s">
+        <v>434</v>
+      </c>
+      <c r="I20" t="s">
         <v>435</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>436</v>
       </c>
-      <c r="J20" t="s">
-        <v>437</v>
-      </c>
       <c r="K20" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L20" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M20" t="s">
         <v>75</v>
@@ -10317,13 +10327,13 @@
         <v>30</v>
       </c>
       <c r="P20" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q20" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="Q20" s="8" t="s">
+      <c r="R20" t="s">
         <v>489</v>
-      </c>
-      <c r="R20" t="s">
-        <v>490</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -10349,12 +10359,11 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="Q9" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
-    <hyperlink ref="Q17" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A986EF-EB1F-44E6-A13B-6D75B4761BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF840E23-F1CB-443D-8F45-2E4912C31557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19215" yWindow="240" windowWidth="38370" windowHeight="20505" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="516">
   <si>
     <t>Event Name</t>
   </si>
@@ -146,6 +146,36 @@
     <t>Website</t>
   </si>
   <si>
+    <t>Bristol EDI Network Sessions - It Starts With Us</t>
+  </si>
+  <si>
+    <t>9:00 am - 12:00 pm</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>External</t>
+  </si>
+  <si>
+    <t>AT Network RP1-26-27</t>
+  </si>
+  <si>
+    <t>NW Equality, Diversity and Inclusion RP1-26-27</t>
+  </si>
+  <si>
+    <t>EDI</t>
+  </si>
+  <si>
+    <t>Facilitated by Simone and Elaine. Session 1 of 6 in Bristol Early Years' Equality, Diversity and Inclusion CPD programme (sessions can be attended individually).</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-edi-network-sessions-it-starts-with-us/</t>
+  </si>
+  <si>
+    <t>A reflective session inviting early years educators to pause and consider equality, diversity and inclusion in their own practice. In a supportive space, participants explore how their values, experiences and biases shape their work with children and families, and consider what equitable practice looks like in action.</t>
+  </si>
+  <si>
     <t>Using Visuals to Support Speech, Language and Communication (SALT Network Session)</t>
   </si>
   <si>
@@ -158,9 +188,6 @@
     <t>Online</t>
   </si>
   <si>
-    <t>AT Network RP1-26-27</t>
-  </si>
-  <si>
     <t>PD Communication and Language RP1-26-27</t>
   </si>
   <si>
@@ -281,15 +308,9 @@
     <t>4:00 pm - 6:00 pm</t>
   </si>
   <si>
-    <t>Local</t>
-  </si>
-  <si>
     <t>Hartcliffe Nursery School</t>
   </si>
   <si>
-    <t>External</t>
-  </si>
-  <si>
     <t>NW Spotlight on Twos RP1-26-27</t>
   </si>
   <si>
@@ -305,6 +326,18 @@
     <t>The Terrific Twos Network is an opportunity for early years practitioners and leaders in Bristol to connect around a shared passion for working with two-year-olds. Whether experienced or new to the age group, and whether based in a setting, school or childminder provision, this is a chance to focus on this unique age group, visit other settings and gain peer support. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
   </si>
   <si>
+    <t>Bristol EDI Network Sessions - Inclusive Environments</t>
+  </si>
+  <si>
+    <t>Facilitated by Simone and Beth. Session 2 of 6 in Bristol Early Years' Equality, Diversity and Inclusion CPD programme (sessions can be attended individually).</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-edi-network-sessions-inclusive-environments/</t>
+  </si>
+  <si>
+    <t>A practical, reflective session exploring how physical, emotional and relational environments communicate messages about identity, belonging and inclusion. Participants examine how their own values and assumptions shape the spaces children encounter, and leave with renewed confidence to embed authentic representation into everyday practice.</t>
+  </si>
+  <si>
     <t>How Can a Playful Pedagogy Work Within a Home-Based Childcare Setting? With Michelle Malomo</t>
   </si>
   <si>
@@ -323,9 +356,6 @@
     <t>CPD Programme: Using Evidence to Strengthen Your Early Years Leadership - Session 1</t>
   </si>
   <si>
-    <t>9:00 am - 12:00 pm</t>
-  </si>
-  <si>
     <t>St Pauls Nursery Community Room</t>
   </si>
   <si>
@@ -440,6 +470,9 @@
     <t>Hosted by EveryFAMILY. Facilitator: Nic.</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-november-2026/</t>
+  </si>
+  <si>
     <t>CPD Programme: Getting it Right for Twos - Session 1</t>
   </si>
   <si>
@@ -566,6 +599,18 @@
     <t>Explore behaviour through a neurodevelopmental and relational lens, looking beyond behaviour itself to consider what children may be communicating, and understand the links between behaviour, communication, sensory processing, emotional regulation and developmental differences, with practical, inclusive strategies to support children's wellbeing and engagement.</t>
   </si>
   <si>
+    <t>Bristol EDI Network Sessions - Inclusive Curriculum</t>
+  </si>
+  <si>
+    <t>Facilitated by Simone and Elizabeth. Session 3 of 6 in Bristol Early Years' Equality, Diversity and Inclusion CPD programme (sessions can be attended individually).</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/bristol-edi-network-sessions-inclusive-curriculum/</t>
+  </si>
+  <si>
+    <t>A session introducing practical ways to diversify and decolonise the early years curriculum. Participants explore strategies for embedding diverse voices, experiences and knowledge systems into everyday learning, moving beyond tokenism toward authentic representation.</t>
+  </si>
+  <si>
     <t>Childminder Network: Leading a Team</t>
   </si>
   <si>
@@ -605,6 +650,9 @@
     <t>Hosted by St Paul's Nursery School &amp; Children's Centre. Facilitators: Robin Taylor (Executive Head), Tiff Henley (Birth to Two's Lead).</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-december-2026/</t>
+  </si>
+  <si>
     <t>Leadership Matters Network (December 2026)</t>
   </si>
   <si>
@@ -698,6 +746,9 @@
     <t>Hosted by Red Bus Coombe Dingle. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-december-2026/</t>
+  </si>
+  <si>
     <t>Maths Network - December 2026</t>
   </si>
   <si>
@@ -821,9 +872,6 @@
     <t>EDI: It Starts With Us - Reflection on Bias and Positionality</t>
   </si>
   <si>
-    <t>EDI</t>
-  </si>
-  <si>
     <t>Trainers: Local EDI Specialist leaders. One of a 3-part EDI CPD series — can book individually, but booking all 3 is recommended.</t>
   </si>
   <si>
@@ -956,6 +1004,9 @@
     <t>Hosted by BS3 The Chessel Centre. Facilitator: Hayley Smith (Manager).</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-february-2027/</t>
+  </si>
+  <si>
     <t>Tuning in to Babies CPD Programme - Session 2</t>
   </si>
   <si>
@@ -983,6 +1034,9 @@
     <t>Hosted by Snapdragons Horfield. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-february-2027/</t>
+  </si>
+  <si>
     <t>Childminder Network - February 2027</t>
   </si>
   <si>
@@ -1019,6 +1073,9 @@
     <t>Hosted by Jack and Jill.</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-march-2027/</t>
+  </si>
+  <si>
     <t>SEND Immersion Day at St. Paul’s Nursery School - March 2027</t>
   </si>
   <si>
@@ -1085,6 +1142,9 @@
     <t>Hosted by St Pauls Nursery School. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-march-2027/</t>
+  </si>
+  <si>
     <t>Behaviour CPD Programme (Jan, Feb, March 2027) - Session 3</t>
   </si>
   <si>
@@ -1277,6 +1337,9 @@
     <t>Hosted by Millie's Garden. Facilitator: Millie Colwey (Lead).</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-may-2027/</t>
+  </si>
+  <si>
     <t>Maths Network - May 2027</t>
   </si>
   <si>
@@ -1328,6 +1391,9 @@
     <t>Hosted by Windmill Hill City Farm. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-may-2027/</t>
+  </si>
+  <si>
     <t>Trauma Informed Practice Study Morning at Knowle West Nursery - May 2027</t>
   </si>
   <si>
@@ -1361,6 +1427,9 @@
     <t>Hosted by Mama Bears Totterdown. Facilitators: Justyna Van der Laan O'Donnell (Manager), Kayleigh (Treasure Room Lead).</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-june-2027/</t>
+  </si>
+  <si>
     <t>Talking About Twos: Behaviour: Regulate, Relate and Reason</t>
   </si>
   <si>
@@ -1469,6 +1538,9 @@
     <t>Hosted by Woodland House Nursery. Facilitators: Nicola (Baby Room Lead), Cristina (Deputy), Mitch &amp; Emma (Managers).</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-july-2027/</t>
+  </si>
+  <si>
     <t>Getting It Right for Babies CPD Programme - Session 2</t>
   </si>
   <si>
@@ -1487,6 +1559,9 @@
     <t>Hosted by The Limes Nursery School. Facilitated by local specialist leaders for birth to three years, Millie Colwey and Megan Day.</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-july-2027/</t>
+  </si>
+  <si>
     <t>Getting It Right for Babies CPD Programme - Session 3</t>
   </si>
   <si>
@@ -1499,6 +1574,9 @@
     <t>Hosted by Raised in Bristol at Felix Road Adventure Playground. Facilitator: Lisa H. Hathaway (Manager).</t>
   </si>
   <si>
+    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-august-2027/</t>
+  </si>
+  <si>
     <t>Talking About Babies: Mental Health and Wellbeing with Sarah Clarke</t>
   </si>
   <si>
@@ -1509,45 +1587,6 @@
   </si>
   <si>
     <t>Join Specialist Health Visitor Sarah Clarke to explore infant mental health and wellbeing and how it shapes babies' current and lifelong development, sharing ideas to support babies' mental health and development in early years settings — part of the Talking About... series of informal online networking sessions.</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-november-2026/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-december-2026/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-february-2027/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-march-2027/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-may-2027/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-june-2027/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-july-2027/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-baby-practitioner-clusters-august-2027/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-december-2026/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-february-2027/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-march-2027/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-may-2027/</t>
-  </si>
-  <si>
-    <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-july-2027/</t>
   </si>
 </sst>
 </file>
@@ -1577,13 +1616,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -1591,8 +1623,15 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1629,6 +1668,12 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1641,9 +1686,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1655,19 +1700,25 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1755,8 +1806,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TableRP12627" displayName="TableRP12627" ref="A1:U30" totalsRowShown="0">
-  <autoFilter ref="A1:U30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TableRP12627" displayName="TableRP12627" ref="A1:U33" totalsRowShown="0">
+  <autoFilter ref="A1:U33" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Event Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Activity Date"/>
@@ -2050,7 +2101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.85546875" customWidth="1"/>
@@ -2141,7 +2192,7 @@
         <v>46288</v>
       </c>
       <c r="C2" s="1" t="str">
-        <f t="shared" ref="C2:C30" si="0">IF(B2="","",TEXT(B2,"dddd"))</f>
+        <f t="shared" ref="C2:C33" si="0">IF(B2="","",TEXT(B2,"dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -2195,27 +2246,27 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="16" t="s">
         <v>35</v>
       </c>
       <c r="B3" s="7">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Monday</v>
+        <v>Friday</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="19" t="s">
         <v>38</v>
-      </c>
-      <c r="G3" s="2">
-        <v>80</v>
       </c>
       <c r="H3" t="s">
         <v>25</v>
@@ -2227,31 +2278,34 @@
         <v>39</v>
       </c>
       <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
         <v>40</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>41</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="R3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" t="s">
         <v>37</v>
       </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="R3" t="s">
-        <v>43</v>
-      </c>
-      <c r="S3" t="s">
-        <v>33</v>
-      </c>
       <c r="T3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U3" t="b">
         <f>FALSE()</f>
@@ -2260,23 +2314,23 @@
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="7">
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="C4" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Monday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G4" s="2">
         <v>80</v>
@@ -2291,14 +2345,14 @@
         <v>39</v>
       </c>
       <c r="K4" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="L4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4" t="s">
         <v>47</v>
       </c>
-      <c r="M4" t="s">
-        <v>46</v>
-      </c>
       <c r="N4" t="s">
         <v>29</v>
       </c>
@@ -2306,10 +2360,10 @@
         <v>30</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="R4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -2324,7 +2378,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B5" s="7">
         <v>46302</v>
@@ -2334,13 +2388,13 @@
         <v>Wednesday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2">
         <v>80</v>
@@ -2355,13 +2409,13 @@
         <v>39</v>
       </c>
       <c r="K5" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N5" t="s">
         <v>29</v>
@@ -2369,14 +2423,11 @@
       <c r="O5" t="s">
         <v>30</v>
       </c>
-      <c r="P5" t="s">
-        <v>55</v>
-      </c>
       <c r="Q5" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -2391,26 +2442,26 @@
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="7">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="C6" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G6" s="2">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
         <v>25</v>
@@ -2419,13 +2470,16 @@
         <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K6" t="s">
-        <v>28</v>
+        <v>62</v>
+      </c>
+      <c r="L6" t="s">
+        <v>63</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="N6" t="s">
         <v>29</v>
@@ -2433,11 +2487,14 @@
       <c r="O6" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" s="8" t="s">
-        <v>60</v>
+      <c r="P6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="R6" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -2452,26 +2509,26 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B7" s="7">
-        <v>46307</v>
+        <v>46303</v>
       </c>
       <c r="C7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Monday</v>
+        <v>Thursday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
         <v>25</v>
@@ -2480,13 +2537,13 @@
         <v>26</v>
       </c>
       <c r="J7" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="K7" t="s">
         <v>28</v>
       </c>
       <c r="M7" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
@@ -2494,14 +2551,11 @@
       <c r="O7" t="s">
         <v>30</v>
       </c>
-      <c r="P7" t="s">
-        <v>65</v>
-      </c>
       <c r="Q7" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="R7" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -2516,26 +2570,26 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B8" s="7">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="C8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Tuesday</v>
+        <v>Monday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s">
         <v>25</v>
@@ -2544,16 +2598,13 @@
         <v>26</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s">
         <v>28</v>
       </c>
-      <c r="L8" t="s">
-        <v>70</v>
-      </c>
       <c r="M8" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="N8" t="s">
         <v>29</v>
@@ -2561,11 +2612,14 @@
       <c r="O8" t="s">
         <v>30</v>
       </c>
-      <c r="Q8" s="8" t="s">
-        <v>71</v>
+      <c r="P8" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="R8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -2580,26 +2634,26 @@
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B9" s="7">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="C9" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G9" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H9" t="s">
         <v>25</v>
@@ -2608,13 +2662,16 @@
         <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="K9" t="s">
         <v>28</v>
       </c>
+      <c r="L9" t="s">
+        <v>79</v>
+      </c>
       <c r="M9" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -2623,10 +2680,10 @@
         <v>30</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="R9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -2641,7 +2698,7 @@
     </row>
     <row r="10" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B10" s="7">
         <v>46309</v>
@@ -2651,16 +2708,16 @@
         <v>Wednesday</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="21">
         <v>80</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>82</v>
       </c>
       <c r="H10" t="s">
         <v>25</v>
@@ -2669,14 +2726,11 @@
         <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s">
         <v>28</v>
       </c>
-      <c r="L10" t="s">
-        <v>83</v>
-      </c>
       <c r="M10" t="s">
         <v>84</v>
       </c>
@@ -2684,22 +2738,19 @@
         <v>29</v>
       </c>
       <c r="O10" t="s">
-        <v>29</v>
-      </c>
-      <c r="P10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="Q10" s="8" t="s">
+      <c r="R10" t="s">
         <v>86</v>
       </c>
-      <c r="R10" t="s">
-        <v>87</v>
-      </c>
       <c r="S10" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="T10" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="U10" t="b">
         <f>FALSE()</f>
@@ -2708,26 +2759,26 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="7">
+        <v>46309</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="7">
-        <v>46315</v>
-      </c>
-      <c r="C11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Tuesday</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>23</v>
+      <c r="E11" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="G11" s="2">
-        <v>80</v>
       </c>
       <c r="H11" t="s">
         <v>25</v>
@@ -2736,34 +2787,37 @@
         <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="K11" t="s">
-        <v>89</v>
+        <v>28</v>
+      </c>
+      <c r="L11" t="s">
+        <v>90</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
       </c>
       <c r="O11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P11" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q11" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>93</v>
       </c>
       <c r="R11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="S11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U11" t="b">
         <f>FALSE()</f>
@@ -2771,27 +2825,27 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>93</v>
+      <c r="A12" s="16" t="s">
+        <v>95</v>
       </c>
       <c r="B12" s="7">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="C12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Tuesday</v>
+        <v>Friday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G12" s="2">
-        <v>16</v>
+        <v>36</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>38</v>
       </c>
       <c r="H12" t="s">
         <v>25</v>
@@ -2800,34 +2854,37 @@
         <v>26</v>
       </c>
       <c r="J12" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K12" t="s">
         <v>28</v>
       </c>
+      <c r="L12" t="s">
+        <v>40</v>
+      </c>
       <c r="M12" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" t="s">
         <v>96</v>
       </c>
-      <c r="N12" t="s">
-        <v>30</v>
-      </c>
-      <c r="O12" t="s">
-        <v>30</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="Q12" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="R12" t="s">
         <v>98</v>
       </c>
-      <c r="R12" t="s">
-        <v>99</v>
-      </c>
       <c r="S12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U12" t="b">
         <f>FALSE()</f>
@@ -2836,26 +2893,26 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" s="7">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C13" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="21">
         <v>80</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>82</v>
       </c>
       <c r="H13" t="s">
         <v>25</v>
@@ -2864,37 +2921,34 @@
         <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="K13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" t="s">
+        <v>29</v>
+      </c>
+      <c r="O13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P13" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="R13" t="s">
         <v>103</v>
       </c>
-      <c r="M13" t="s">
-        <v>75</v>
-      </c>
-      <c r="N13" t="s">
-        <v>29</v>
-      </c>
-      <c r="O13" t="s">
-        <v>29</v>
-      </c>
-      <c r="P13" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="R13" t="s">
-        <v>106</v>
-      </c>
       <c r="S13" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="T13" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="U13" t="b">
         <f>FALSE()</f>
@@ -2903,26 +2957,26 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B14" s="7">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="C14" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="G14" s="2">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
         <v>25</v>
@@ -2931,28 +2985,28 @@
         <v>26</v>
       </c>
       <c r="J14" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="K14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" t="s">
+        <v>106</v>
+      </c>
+      <c r="N14" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" t="s">
+        <v>30</v>
+      </c>
+      <c r="P14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q14" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="R14" t="s">
         <v>109</v>
-      </c>
-      <c r="M14" t="s">
-        <v>108</v>
-      </c>
-      <c r="N14" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" t="s">
-        <v>30</v>
-      </c>
-      <c r="P14" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="R14" t="s">
-        <v>112</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -2967,26 +3021,26 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B15" s="7">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="C15" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>84</v>
+        <v>111</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="G15" s="2">
-        <v>80</v>
       </c>
       <c r="H15" t="s">
         <v>25</v>
@@ -2998,10 +3052,10 @@
         <v>39</v>
       </c>
       <c r="K15" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="L15" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="M15" t="s">
         <v>84</v>
@@ -3010,22 +3064,22 @@
         <v>29</v>
       </c>
       <c r="O15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P15" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q15" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="Q15" s="8" t="s">
+      <c r="R15" t="s">
         <v>116</v>
       </c>
-      <c r="R15" t="s">
-        <v>117</v>
-      </c>
       <c r="S15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U15" t="b">
         <f>FALSE()</f>
@@ -3034,26 +3088,26 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46316</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B16" s="7">
-        <v>46317</v>
-      </c>
-      <c r="C16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Thursday</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G16" s="2">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s">
         <v>25</v>
@@ -3062,28 +3116,28 @@
         <v>26</v>
       </c>
       <c r="J16" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K16" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="M16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N16" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16" t="s">
+        <v>30</v>
+      </c>
+      <c r="P16" t="s">
         <v>120</v>
       </c>
-      <c r="N16" t="s">
-        <v>29</v>
-      </c>
-      <c r="O16" t="s">
-        <v>30</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="Q16" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Q16" s="8" t="s">
+      <c r="R16" t="s">
         <v>122</v>
-      </c>
-      <c r="R16" t="s">
-        <v>123</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -3098,23 +3152,23 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46317</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Thursday</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="7">
-        <v>46318</v>
-      </c>
-      <c r="C17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Friday</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G17" s="2">
         <v>80</v>
@@ -3126,13 +3180,16 @@
         <v>26</v>
       </c>
       <c r="J17" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="K17" t="s">
-        <v>28</v>
+        <v>100</v>
+      </c>
+      <c r="L17" t="s">
+        <v>90</v>
       </c>
       <c r="M17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
@@ -3141,13 +3198,13 @@
         <v>30</v>
       </c>
       <c r="P17" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q17" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="Q17" s="8" t="s">
+      <c r="R17" t="s">
         <v>127</v>
-      </c>
-      <c r="R17" t="s">
-        <v>128</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -3161,27 +3218,27 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="7">
+        <v>46317</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Thursday</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="7">
-        <v>46328</v>
-      </c>
-      <c r="C18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Monday</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>82</v>
+      <c r="F18" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="21">
+        <v>500</v>
       </c>
       <c r="H18" t="s">
         <v>25</v>
@@ -3190,37 +3247,34 @@
         <v>26</v>
       </c>
       <c r="J18" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="K18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="N18" t="s">
         <v>29</v>
       </c>
       <c r="O18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P18" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q18" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="Q18" s="8" t="s">
-        <v>490</v>
-      </c>
       <c r="R18" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="S18" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="T18" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="U18" t="b">
         <f>FALSE()</f>
@@ -3229,23 +3283,23 @@
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="7">
-        <v>46330</v>
+        <v>46318</v>
       </c>
       <c r="C19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Friday</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G19" s="2">
         <v>80</v>
@@ -3257,25 +3311,28 @@
         <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K19" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="M19" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="N19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O19" t="s">
         <v>30</v>
       </c>
-      <c r="Q19" s="8" t="s">
-        <v>134</v>
+      <c r="P19" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>137</v>
       </c>
       <c r="R19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -3290,26 +3347,26 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B20" s="7">
-        <v>46331</v>
+        <v>46328</v>
       </c>
       <c r="C20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Monday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>37</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G20" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="G20" s="2">
-        <v>80</v>
       </c>
       <c r="H20" t="s">
         <v>25</v>
@@ -3318,31 +3375,37 @@
         <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="K20" t="s">
-        <v>40</v>
+        <v>28</v>
+      </c>
+      <c r="L20" t="s">
+        <v>113</v>
       </c>
       <c r="M20" t="s">
+        <v>84</v>
+      </c>
+      <c r="N20" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20" t="s">
+        <v>29</v>
+      </c>
+      <c r="P20" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q20" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="R20" t="s">
+        <v>116</v>
+      </c>
+      <c r="S20" t="s">
         <v>37</v>
       </c>
-      <c r="N20" t="s">
-        <v>29</v>
-      </c>
-      <c r="O20" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="R20" t="s">
-        <v>138</v>
-      </c>
-      <c r="S20" t="s">
-        <v>33</v>
-      </c>
       <c r="T20" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U20" t="b">
         <f>FALSE()</f>
@@ -3351,26 +3414,26 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B21" s="7">
-        <v>46332</v>
+        <v>46330</v>
       </c>
       <c r="C21" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Friday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="G21" s="2">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
         <v>25</v>
@@ -3379,28 +3442,25 @@
         <v>26</v>
       </c>
       <c r="J21" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="K21" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="M21" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="N21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O21" t="s">
         <v>30</v>
       </c>
-      <c r="P21" t="s">
-        <v>141</v>
-      </c>
       <c r="Q21" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="R21" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -3415,23 +3475,23 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B22" s="7">
-        <v>46335</v>
+        <v>46331</v>
       </c>
       <c r="C22" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Monday</v>
+        <v>Thursday</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>145</v>
+        <v>47</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G22" s="2">
         <v>80</v>
@@ -3443,16 +3503,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="K22" t="s">
-        <v>89</v>
-      </c>
-      <c r="L22" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="M22" t="s">
-        <v>145</v>
+        <v>47</v>
       </c>
       <c r="N22" t="s">
         <v>29</v>
@@ -3460,11 +3517,11 @@
       <c r="O22" t="s">
         <v>30</v>
       </c>
-      <c r="Q22" s="8" t="s">
-        <v>147</v>
+      <c r="Q22" s="10" t="s">
+        <v>148</v>
       </c>
       <c r="R22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -3478,27 +3535,27 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>149</v>
+      <c r="A23" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="B23" s="7">
-        <v>46336</v>
+        <v>46332</v>
       </c>
       <c r="C23" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Tuesday</v>
+        <v>Friday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H23" t="s">
         <v>25</v>
@@ -3510,25 +3567,25 @@
         <v>27</v>
       </c>
       <c r="K23" t="s">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="M23" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="N23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P23" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="R23" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -3543,26 +3600,26 @@
     </row>
     <row r="24" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B24" s="7">
-        <v>46337</v>
+        <v>46335</v>
       </c>
       <c r="C24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Monday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>151</v>
+        <v>46</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>46</v>
+        <v>156</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="G24" s="2">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s">
         <v>25</v>
@@ -3571,13 +3628,16 @@
         <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K24" t="s">
-        <v>28</v>
+        <v>100</v>
+      </c>
+      <c r="L24" t="s">
+        <v>157</v>
       </c>
       <c r="M24" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -3585,14 +3645,11 @@
       <c r="O24" t="s">
         <v>30</v>
       </c>
-      <c r="P24" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>153</v>
+      <c r="Q24" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="R24" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -3606,24 +3663,27 @@
       </c>
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>155</v>
+      <c r="A25" s="13" t="s">
+        <v>160</v>
       </c>
       <c r="B25" s="7">
-        <v>46338</v>
+        <v>46336</v>
       </c>
       <c r="C25" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Tuesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>80</v>
+        <v>55</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="G25" s="2">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="H25" t="s">
         <v>25</v>
@@ -3632,28 +3692,31 @@
         <v>26</v>
       </c>
       <c r="J25" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="K25" t="s">
         <v>28</v>
       </c>
-      <c r="L25" t="s">
-        <v>103</v>
+      <c r="M25" t="s">
+        <v>106</v>
       </c>
       <c r="N25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O25" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="P25" t="s">
+        <v>107</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="R25" t="s">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="S25" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="T25" t="s">
         <v>34</v>
@@ -3664,27 +3727,27 @@
       </c>
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>159</v>
+      <c r="A26" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="B26" s="7">
-        <v>46344</v>
+        <v>46337</v>
       </c>
       <c r="C26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Wednesday</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="G26" s="2">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="H26" t="s">
         <v>25</v>
@@ -3693,22 +3756,28 @@
         <v>26</v>
       </c>
       <c r="J26" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="K26" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="M26" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="N26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O26" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q26" s="8" t="s">
-        <v>134</v>
+        <v>30</v>
+      </c>
+      <c r="P26" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q26" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="R26" t="s">
+        <v>165</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -3723,26 +3792,23 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B27" s="7">
-        <v>46345</v>
+        <v>46338</v>
       </c>
       <c r="C27" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Thursday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>36</v>
+        <v>167</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="G27" s="2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H27" t="s">
         <v>25</v>
@@ -3754,32 +3820,26 @@
         <v>39</v>
       </c>
       <c r="K27" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="L27" t="s">
-        <v>41</v>
-      </c>
-      <c r="M27" t="s">
+        <v>113</v>
+      </c>
+      <c r="N27" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="R27" t="s">
+        <v>169</v>
+      </c>
+      <c r="S27" t="s">
         <v>37</v>
       </c>
-      <c r="N27" t="s">
-        <v>29</v>
-      </c>
-      <c r="O27" t="s">
-        <v>30</v>
-      </c>
-      <c r="P27" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q27" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="R27" t="s">
-        <v>163</v>
-      </c>
-      <c r="S27" t="s">
-        <v>33</v>
-      </c>
       <c r="T27" t="s">
         <v>34</v>
       </c>
@@ -3789,24 +3849,24 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>164</v>
+      <c r="A28" s="13" t="s">
+        <v>170</v>
       </c>
       <c r="B28" s="7">
-        <v>46351</v>
+        <v>46344</v>
       </c>
       <c r="C28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Wednesday</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G28" s="2">
         <v>80</v>
@@ -3818,28 +3878,22 @@
         <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K28" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="M28" t="s">
+        <v>91</v>
+      </c>
+      <c r="N28" t="s">
+        <v>30</v>
+      </c>
+      <c r="O28" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q28" s="8" t="s">
         <v>145</v>
-      </c>
-      <c r="N28" t="s">
-        <v>29</v>
-      </c>
-      <c r="O28" t="s">
-        <v>30</v>
-      </c>
-      <c r="P28" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q28" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="R28" t="s">
-        <v>167</v>
       </c>
       <c r="S28" t="s">
         <v>33</v>
@@ -3854,23 +3908,23 @@
     </row>
     <row r="29" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B29" s="7">
-        <v>46352</v>
+        <v>46345</v>
       </c>
       <c r="C29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Thursday</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G29" s="2">
         <v>80</v>
@@ -3882,13 +3936,16 @@
         <v>26</v>
       </c>
       <c r="J29" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="K29" t="s">
-        <v>169</v>
+        <v>49</v>
+      </c>
+      <c r="L29" t="s">
+        <v>50</v>
       </c>
       <c r="M29" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N29" t="s">
         <v>29</v>
@@ -3896,11 +3953,14 @@
       <c r="O29" t="s">
         <v>30</v>
       </c>
-      <c r="Q29" s="8" t="s">
-        <v>170</v>
+      <c r="P29" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q29" s="10" t="s">
+        <v>173</v>
       </c>
       <c r="R29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -3915,23 +3975,23 @@
     </row>
     <row r="30" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B30" s="7">
-        <v>46352</v>
+        <v>46351</v>
       </c>
       <c r="C30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G30" s="2">
         <v>80</v>
@@ -3943,16 +4003,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="K30" t="s">
-        <v>53</v>
-      </c>
-      <c r="L30" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="M30" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="N30" t="s">
         <v>29</v>
@@ -3961,13 +4018,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>55</v>
+        <v>176</v>
       </c>
       <c r="Q30" s="8" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="R30" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -3980,13 +4037,208 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46352</v>
+      </c>
+      <c r="C31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Thursday</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31" s="2">
+        <v>80</v>
+      </c>
+      <c r="H31" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31" t="s">
+        <v>73</v>
+      </c>
+      <c r="K31" t="s">
+        <v>180</v>
+      </c>
+      <c r="M31" t="s">
+        <v>47</v>
+      </c>
+      <c r="N31" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q31" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="R31" t="s">
+        <v>182</v>
+      </c>
+      <c r="S31" t="s">
+        <v>33</v>
+      </c>
+      <c r="T31" t="s">
+        <v>34</v>
+      </c>
+      <c r="U31" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46352</v>
+      </c>
+      <c r="C32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Thursday</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="2">
+        <v>80</v>
+      </c>
+      <c r="H32" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32" t="s">
+        <v>39</v>
+      </c>
+      <c r="K32" t="s">
+        <v>62</v>
+      </c>
+      <c r="L32" t="s">
+        <v>63</v>
+      </c>
+      <c r="M32" t="s">
+        <v>61</v>
+      </c>
+      <c r="N32" t="s">
+        <v>29</v>
+      </c>
+      <c r="O32" t="s">
+        <v>30</v>
+      </c>
+      <c r="P32" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>184</v>
+      </c>
+      <c r="R32" t="s">
+        <v>185</v>
+      </c>
+      <c r="S32" t="s">
+        <v>33</v>
+      </c>
+      <c r="T32" t="s">
+        <v>34</v>
+      </c>
+      <c r="U32" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46353</v>
+      </c>
+      <c r="C33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Friday</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I33" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K33" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" t="s">
+        <v>40</v>
+      </c>
+      <c r="M33" t="s">
+        <v>41</v>
+      </c>
+      <c r="N33" t="s">
+        <v>29</v>
+      </c>
+      <c r="O33" t="s">
+        <v>29</v>
+      </c>
+      <c r="P33" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q33" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="R33" t="s">
+        <v>189</v>
+      </c>
+      <c r="S33" t="s">
+        <v>37</v>
+      </c>
+      <c r="T33" t="s">
+        <v>38</v>
+      </c>
+      <c r="U33" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="S2:S30" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="S2:S33" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Regional,Local"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T2:T30" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="T2:T33" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Website,External"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3995,22 +4247,25 @@
     <hyperlink ref="Q2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="Q3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="Q4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="Q6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="Q8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="Q5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="Q7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="Q9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="Q11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="Q14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="Q19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="Q21" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="Q23" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="Q25" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="Q26" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="Q28" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="Q10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="Q12" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="Q13" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="Q16" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="Q21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="Q23" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="Q25" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="Q27" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="Q28" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="Q30" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="Q33" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId15"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId18"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4102,9 +4357,9 @@
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="B2" s="7">
+        <v>190</v>
+      </c>
+      <c r="B2" s="1">
         <v>46357</v>
       </c>
       <c r="C2" s="1" t="str">
@@ -4112,31 +4367,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G2" s="2">
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J2" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="L2" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>
@@ -4147,11 +4402,11 @@
       <c r="O2" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="8" t="s">
-        <v>181</v>
+      <c r="Q2" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="R2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="S2" t="s">
         <v>33</v>
@@ -4165,10 +4420,10 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="A3" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="1">
         <v>46357</v>
       </c>
       <c r="C3" s="1" t="str">
@@ -4176,31 +4431,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G3" s="2">
         <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J3" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="M3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="N3" t="s">
         <v>30</v>
@@ -4209,13 +4464,13 @@
         <v>29</v>
       </c>
       <c r="P3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>98</v>
+        <v>107</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>108</v>
       </c>
       <c r="R3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -4229,10 +4484,10 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" s="7">
+      <c r="A4" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" s="1">
         <v>46357</v>
       </c>
       <c r="C4" s="1" t="str">
@@ -4240,34 +4495,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>80</v>
+        <v>140</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>82</v>
+        <v>105</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I4" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J4" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="L4" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="M4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N4" t="s">
         <v>29</v>
@@ -4276,19 +4531,19 @@
         <v>29</v>
       </c>
       <c r="P4" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>491</v>
+        <v>202</v>
+      </c>
+      <c r="Q4" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="R4" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="S4" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T4" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="U4" t="b">
         <f>FALSE()</f>
@@ -4297,9 +4552,9 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B5" s="7">
+        <v>204</v>
+      </c>
+      <c r="B5" s="1">
         <v>46358</v>
       </c>
       <c r="C5" s="1" t="str">
@@ -4307,34 +4562,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2">
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I5" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J5" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K5" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="L5" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="M5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="N5" t="s">
         <v>29</v>
@@ -4342,11 +4597,11 @@
       <c r="O5" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="8" t="s">
-        <v>190</v>
+      <c r="Q5" s="10" t="s">
+        <v>206</v>
       </c>
       <c r="R5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -4360,10 +4615,10 @@
       </c>
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B6" s="7">
+      <c r="A6" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="1">
         <v>46358</v>
       </c>
       <c r="C6" s="1" t="str">
@@ -4371,31 +4626,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G6" s="2">
         <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I6" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J6" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K6" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="M6" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N6" t="s">
         <v>30</v>
@@ -4403,8 +4658,8 @@
       <c r="O6" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="8" t="s">
-        <v>134</v>
+      <c r="Q6" s="10" t="s">
+        <v>145</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -4419,9 +4674,9 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B7" s="7">
+        <v>210</v>
+      </c>
+      <c r="B7" s="1">
         <v>46358</v>
       </c>
       <c r="C7" s="1" t="str">
@@ -4429,31 +4684,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="G7" s="2">
         <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I7" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J7" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K7" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="M7" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
@@ -4461,11 +4716,11 @@
       <c r="O7" t="s">
         <v>30</v>
       </c>
-      <c r="Q7" s="8" t="s">
-        <v>197</v>
+      <c r="Q7" s="10" t="s">
+        <v>213</v>
       </c>
       <c r="R7" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -4480,9 +4735,9 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B8" s="7">
+        <v>215</v>
+      </c>
+      <c r="B8" s="1">
         <v>46360</v>
       </c>
       <c r="C8" s="1" t="str">
@@ -4490,34 +4745,34 @@
         <v>Friday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2">
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I8" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J8" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K8" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="L8" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="M8" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N8" t="s">
         <v>29</v>
@@ -4526,13 +4781,13 @@
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>201</v>
+        <v>125</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>217</v>
       </c>
       <c r="R8" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -4547,9 +4802,9 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B9" s="7">
+        <v>219</v>
+      </c>
+      <c r="B9" s="1">
         <v>46363</v>
       </c>
       <c r="C9" s="1" t="str">
@@ -4557,34 +4812,34 @@
         <v>Monday</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G9" s="2">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I9" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J9" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K9" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="L9" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="M9" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -4592,11 +4847,11 @@
       <c r="O9" t="s">
         <v>30</v>
       </c>
-      <c r="Q9" s="8" t="s">
-        <v>206</v>
+      <c r="Q9" s="10" t="s">
+        <v>222</v>
       </c>
       <c r="R9" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -4611,9 +4866,9 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="B10" s="7">
+        <v>224</v>
+      </c>
+      <c r="B10" s="1">
         <v>46364</v>
       </c>
       <c r="C10" s="1" t="str">
@@ -4621,31 +4876,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G10" s="2">
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I10" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J10" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K10" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="M10" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
@@ -4654,13 +4909,13 @@
         <v>30</v>
       </c>
       <c r="P10" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>212</v>
+        <v>227</v>
+      </c>
+      <c r="Q10" s="10" t="s">
+        <v>228</v>
       </c>
       <c r="R10" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -4674,10 +4929,10 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="B11" s="7">
+      <c r="A11" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B11" s="1">
         <v>46365</v>
       </c>
       <c r="C11" s="1" t="str">
@@ -4685,34 +4940,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>80</v>
+        <v>231</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>82</v>
+        <v>232</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I11" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J11" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K11" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="L11" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="M11" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -4721,19 +4976,19 @@
         <v>29</v>
       </c>
       <c r="P11" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>498</v>
+        <v>234</v>
+      </c>
+      <c r="Q11" s="10" t="s">
+        <v>235</v>
       </c>
       <c r="R11" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="S11" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T11" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="U11" t="b">
         <f>FALSE()</f>
@@ -4742,9 +4997,9 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B12" s="7">
+        <v>236</v>
+      </c>
+      <c r="B12" s="1">
         <v>46366</v>
       </c>
       <c r="C12" s="1" t="str">
@@ -4752,34 +5007,34 @@
         <v>Thursday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G12" s="2">
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I12" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J12" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K12" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="L12" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="M12" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
@@ -4788,13 +5043,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>223</v>
+        <v>239</v>
+      </c>
+      <c r="Q12" s="10" t="s">
+        <v>240</v>
       </c>
       <c r="R12" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -4809,9 +5064,9 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B13" s="7">
+        <v>242</v>
+      </c>
+      <c r="B13" s="1">
         <v>46394</v>
       </c>
       <c r="C13" s="1" t="str">
@@ -4819,31 +5074,31 @@
         <v>Thursday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G13" s="2">
         <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I13" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J13" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K13" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="M13" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
@@ -4852,13 +5107,13 @@
         <v>30</v>
       </c>
       <c r="P13" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>226</v>
+        <v>136</v>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>243</v>
       </c>
       <c r="R13" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -4873,9 +5128,9 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B14" s="7">
+        <v>245</v>
+      </c>
+      <c r="B14" s="1">
         <v>46398</v>
       </c>
       <c r="C14" s="1" t="str">
@@ -4883,31 +5138,31 @@
         <v>Monday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G14" s="2">
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I14" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J14" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K14" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="M14" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
@@ -4916,13 +5171,13 @@
         <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>231</v>
+        <v>247</v>
+      </c>
+      <c r="Q14" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="R14" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -4937,9 +5192,9 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B15" s="7">
+        <v>250</v>
+      </c>
+      <c r="B15" s="1">
         <v>46400</v>
       </c>
       <c r="C15" s="1" t="str">
@@ -4947,31 +5202,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2">
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I15" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J15" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K15" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="M15" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N15" t="s">
         <v>30</v>
@@ -4980,13 +5235,13 @@
         <v>30</v>
       </c>
       <c r="P15" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>236</v>
+        <v>252</v>
+      </c>
+      <c r="Q15" s="10" t="s">
+        <v>253</v>
       </c>
       <c r="R15" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -5001,9 +5256,9 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="B16" s="7">
+        <v>255</v>
+      </c>
+      <c r="B16" s="1">
         <v>46402</v>
       </c>
       <c r="C16" s="1" t="str">
@@ -5011,31 +5266,31 @@
         <v>Friday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I16" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J16" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K16" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -5044,13 +5299,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>241</v>
+        <v>257</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>258</v>
       </c>
       <c r="R16" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -5065,9 +5320,9 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B17" s="7">
+        <v>260</v>
+      </c>
+      <c r="B17" s="1">
         <v>46405</v>
       </c>
       <c r="C17" s="1" t="str">
@@ -5075,31 +5330,31 @@
         <v>Monday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="G17" s="2">
         <v>6</v>
       </c>
       <c r="H17" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I17" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J17" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K17" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="M17" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
@@ -5107,11 +5362,11 @@
       <c r="O17" t="s">
         <v>30</v>
       </c>
-      <c r="Q17" s="8" t="s">
-        <v>247</v>
+      <c r="Q17" s="10" t="s">
+        <v>264</v>
       </c>
       <c r="R17" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -5126,9 +5381,9 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="B18" s="7">
+        <v>266</v>
+      </c>
+      <c r="B18" s="1">
         <v>46407</v>
       </c>
       <c r="C18" s="1" t="str">
@@ -5136,31 +5391,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="G18" s="2">
         <v>6</v>
       </c>
       <c r="H18" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I18" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J18" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K18" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="M18" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N18" t="s">
         <v>29</v>
@@ -5168,11 +5423,11 @@
       <c r="O18" t="s">
         <v>30</v>
       </c>
-      <c r="Q18" s="8" t="s">
-        <v>250</v>
+      <c r="Q18" s="10" t="s">
+        <v>267</v>
       </c>
       <c r="R18" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -5187,9 +5442,9 @@
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="B19" s="7">
+        <v>268</v>
+      </c>
+      <c r="B19" s="1">
         <v>46407</v>
       </c>
       <c r="C19" s="1" t="str">
@@ -5197,31 +5452,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G19" s="2">
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I19" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J19" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K19" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="N19" t="s">
         <v>29</v>
@@ -5230,13 +5485,13 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>253</v>
+        <v>269</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>270</v>
       </c>
       <c r="R19" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -5251,9 +5506,9 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B20" s="7">
+        <v>272</v>
+      </c>
+      <c r="B20" s="1">
         <v>46408</v>
       </c>
       <c r="C20" s="1" t="str">
@@ -5261,34 +5516,34 @@
         <v>Thursday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G20" s="2">
         <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I20" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J20" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K20" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="M20" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N20" t="s">
         <v>29</v>
@@ -5296,11 +5551,11 @@
       <c r="O20" t="s">
         <v>30</v>
       </c>
-      <c r="Q20" s="8" t="s">
-        <v>257</v>
+      <c r="Q20" s="10" t="s">
+        <v>274</v>
       </c>
       <c r="R20" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -5315,9 +5570,9 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B21" s="7">
+        <v>276</v>
+      </c>
+      <c r="B21" s="1">
         <v>46408</v>
       </c>
       <c r="C21" s="1" t="str">
@@ -5325,31 +5580,31 @@
         <v>Thursday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G21" s="2">
         <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I21" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J21" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K21" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
@@ -5358,13 +5613,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>262</v>
+        <v>277</v>
+      </c>
+      <c r="Q21" s="10" t="s">
+        <v>278</v>
       </c>
       <c r="R21" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -5379,9 +5634,9 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="B22" s="7">
+        <v>280</v>
+      </c>
+      <c r="B22" s="1">
         <v>46414</v>
       </c>
       <c r="C22" s="1" t="str">
@@ -5389,31 +5644,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G22" s="2">
         <v>80</v>
       </c>
       <c r="H22" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I22" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J22" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K22" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="M22" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="N22" t="s">
         <v>30</v>
@@ -5422,13 +5677,13 @@
         <v>30</v>
       </c>
       <c r="P22" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>267</v>
+        <v>282</v>
+      </c>
+      <c r="Q22" s="10" t="s">
+        <v>283</v>
       </c>
       <c r="R22" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -5442,10 +5697,10 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="B23" s="7">
+      <c r="A23" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="B23" s="1">
         <v>46416</v>
       </c>
       <c r="C23" s="1" t="str">
@@ -5453,10 +5708,10 @@
         <v>Friday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>24</v>
@@ -5465,19 +5720,19 @@
         <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I23" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J23" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K23" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="M23" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N23" t="s">
         <v>29</v>
@@ -5485,11 +5740,11 @@
       <c r="O23" t="s">
         <v>30</v>
       </c>
-      <c r="Q23" s="8" t="s">
-        <v>271</v>
+      <c r="Q23" s="10" t="s">
+        <v>287</v>
       </c>
       <c r="R23" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -5504,9 +5759,9 @@
     </row>
     <row r="24" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="B24" s="7">
+        <v>289</v>
+      </c>
+      <c r="B24" s="1">
         <v>46420</v>
       </c>
       <c r="C24" s="1" t="str">
@@ -5514,34 +5769,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G24" s="2">
         <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I24" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J24" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K24" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="L24" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -5550,13 +5805,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>274</v>
+        <v>125</v>
+      </c>
+      <c r="Q24" s="10" t="s">
+        <v>290</v>
       </c>
       <c r="R24" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -5571,9 +5826,9 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="B25" s="7">
+        <v>292</v>
+      </c>
+      <c r="B25" s="1">
         <v>46420</v>
       </c>
       <c r="C25" s="1" t="str">
@@ -5581,31 +5836,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="G25" s="2">
         <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I25" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J25" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K25" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="M25" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N25" t="s">
         <v>29</v>
@@ -5614,13 +5869,13 @@
         <v>30</v>
       </c>
       <c r="P25" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q25" s="8" t="s">
-        <v>279</v>
+        <v>294</v>
+      </c>
+      <c r="Q25" s="10" t="s">
+        <v>295</v>
       </c>
       <c r="R25" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -5635,9 +5890,9 @@
     </row>
     <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="B26" s="7">
+        <v>297</v>
+      </c>
+      <c r="B26" s="1">
         <v>46420</v>
       </c>
       <c r="C26" s="1" t="str">
@@ -5645,28 +5900,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G26" s="2">
         <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I26" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J26" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K26" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="M26" t="s">
         <v>23</v>
@@ -5678,13 +5933,13 @@
         <v>30</v>
       </c>
       <c r="P26" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q26" s="8" t="s">
-        <v>283</v>
+        <v>298</v>
+      </c>
+      <c r="Q26" s="10" t="s">
+        <v>299</v>
       </c>
       <c r="R26" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -5699,9 +5954,9 @@
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B27" s="7">
+        <v>301</v>
+      </c>
+      <c r="B27" s="1">
         <v>46421</v>
       </c>
       <c r="C27" s="1" t="str">
@@ -5709,31 +5964,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="G27" s="2">
         <v>12</v>
       </c>
       <c r="H27" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I27" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J27" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K27" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="M27" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N27" t="s">
         <v>29</v>
@@ -5741,11 +5996,11 @@
       <c r="O27" t="s">
         <v>30</v>
       </c>
-      <c r="Q27" s="8" t="s">
-        <v>286</v>
+      <c r="Q27" s="10" t="s">
+        <v>302</v>
       </c>
       <c r="R27" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -5760,9 +6015,9 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="B28" s="7">
+        <v>303</v>
+      </c>
+      <c r="B28" s="1">
         <v>46421</v>
       </c>
       <c r="C28" s="1" t="str">
@@ -5770,34 +6025,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G28" s="2">
         <v>80</v>
       </c>
       <c r="H28" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I28" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J28" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K28" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="L28" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="M28" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="N28" t="s">
         <v>29</v>
@@ -5805,11 +6060,11 @@
       <c r="O28" t="s">
         <v>30</v>
       </c>
-      <c r="Q28" s="8" t="s">
-        <v>288</v>
+      <c r="Q28" s="10" t="s">
+        <v>304</v>
       </c>
       <c r="R28" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="S28" t="s">
         <v>33</v>
@@ -5824,9 +6079,9 @@
     </row>
     <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="B29" s="7">
+        <v>305</v>
+      </c>
+      <c r="B29" s="1">
         <v>46422</v>
       </c>
       <c r="C29" s="1" t="str">
@@ -5834,31 +6089,31 @@
         <v>Thursday</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="G29" s="2">
         <v>6</v>
       </c>
       <c r="H29" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I29" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J29" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K29" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N29" t="s">
         <v>29</v>
@@ -5867,13 +6122,13 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q29" s="8" t="s">
-        <v>290</v>
+        <v>294</v>
+      </c>
+      <c r="Q29" s="10" t="s">
+        <v>306</v>
       </c>
       <c r="R29" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -5888,9 +6143,9 @@
     </row>
     <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="B30" s="7">
+        <v>307</v>
+      </c>
+      <c r="B30" s="1">
         <v>46422</v>
       </c>
       <c r="C30" s="1" t="str">
@@ -5898,31 +6153,31 @@
         <v>Thursday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G30" s="2">
         <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I30" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J30" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K30" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="M30" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="N30" t="s">
         <v>29</v>
@@ -5931,13 +6186,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q30" s="8" t="s">
-        <v>292</v>
+        <v>277</v>
+      </c>
+      <c r="Q30" s="10" t="s">
+        <v>308</v>
       </c>
       <c r="R30" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -5951,10 +6206,10 @@
       </c>
     </row>
     <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="B31" s="7">
+      <c r="A31" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B31" s="1">
         <v>46423</v>
       </c>
       <c r="C31" s="1" t="str">
@@ -5962,10 +6217,10 @@
         <v>Friday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>24</v>
@@ -5974,19 +6229,19 @@
         <v>24</v>
       </c>
       <c r="H31" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I31" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J31" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K31" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="M31" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N31" t="s">
         <v>29</v>
@@ -5994,11 +6249,11 @@
       <c r="O31" t="s">
         <v>30</v>
       </c>
-      <c r="Q31" s="8" t="s">
-        <v>295</v>
+      <c r="Q31" s="10" t="s">
+        <v>311</v>
       </c>
       <c r="R31" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -6013,9 +6268,9 @@
     </row>
     <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="B32" s="7">
+        <v>312</v>
+      </c>
+      <c r="B32" s="1">
         <v>46426</v>
       </c>
       <c r="C32" s="1" t="str">
@@ -6023,34 +6278,34 @@
         <v>Monday</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G32" s="2">
         <v>80</v>
       </c>
       <c r="H32" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I32" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J32" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K32" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="L32" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="M32" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N32" t="s">
         <v>29</v>
@@ -6058,11 +6313,11 @@
       <c r="O32" t="s">
         <v>30</v>
       </c>
-      <c r="Q32" s="8" t="s">
-        <v>297</v>
+      <c r="Q32" s="10" t="s">
+        <v>313</v>
       </c>
       <c r="R32" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -6077,9 +6332,9 @@
     </row>
     <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="B33" s="7">
+        <v>315</v>
+      </c>
+      <c r="B33" s="1">
         <v>46427</v>
       </c>
       <c r="C33" s="1" t="str">
@@ -6087,31 +6342,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G33" s="2">
         <v>80</v>
       </c>
       <c r="H33" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I33" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J33" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K33" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="M33" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="N33" t="s">
         <v>29</v>
@@ -6120,13 +6375,13 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q33" s="8" t="s">
-        <v>300</v>
+        <v>269</v>
+      </c>
+      <c r="Q33" s="10" t="s">
+        <v>316</v>
       </c>
       <c r="R33" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="S33" t="s">
         <v>33</v>
@@ -6140,10 +6395,10 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="B34" s="7">
+      <c r="A34" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B34" s="1">
         <v>46427</v>
       </c>
       <c r="C34" s="1" t="str">
@@ -6151,34 +6406,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>80</v>
+        <v>111</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>82</v>
+        <v>319</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H34" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I34" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J34" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K34" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="L34" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="M34" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N34" t="s">
         <v>29</v>
@@ -6187,19 +6442,19 @@
         <v>29</v>
       </c>
       <c r="P34" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q34" s="8" t="s">
-        <v>492</v>
+        <v>320</v>
+      </c>
+      <c r="Q34" s="10" t="s">
+        <v>321</v>
       </c>
       <c r="R34" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="S34" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T34" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="U34" t="b">
         <f>FALSE()</f>
@@ -6207,10 +6462,10 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="B35" s="7">
+      <c r="A35" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="B35" s="1">
         <v>46428</v>
       </c>
       <c r="C35" s="1" t="str">
@@ -6218,31 +6473,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G35" s="2">
         <v>80</v>
       </c>
       <c r="H35" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I35" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J35" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K35" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="M35" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="N35" t="s">
         <v>30</v>
@@ -6251,10 +6506,10 @@
         <v>29</v>
       </c>
       <c r="P35" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q35" s="8" t="s">
-        <v>267</v>
+        <v>282</v>
+      </c>
+      <c r="Q35" s="10" t="s">
+        <v>283</v>
       </c>
       <c r="S35" t="s">
         <v>33</v>
@@ -6268,10 +6523,10 @@
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="B36" s="7">
+      <c r="A36" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="B36" s="1">
         <v>46428</v>
       </c>
       <c r="C36" s="1" t="str">
@@ -6279,31 +6534,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G36" s="2">
         <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I36" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J36" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K36" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="M36" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N36" t="s">
         <v>30</v>
@@ -6312,10 +6567,10 @@
         <v>29</v>
       </c>
       <c r="P36" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q36" s="8" t="s">
-        <v>236</v>
+        <v>252</v>
+      </c>
+      <c r="Q36" s="10" t="s">
+        <v>253</v>
       </c>
       <c r="S36" t="s">
         <v>33</v>
@@ -6329,10 +6584,10 @@
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="B37" s="7">
+      <c r="A37" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="B37" s="1">
         <v>46430</v>
       </c>
       <c r="C37" s="1" t="str">
@@ -6340,10 +6595,10 @@
         <v>Friday</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>24</v>
@@ -6352,19 +6607,19 @@
         <v>24</v>
       </c>
       <c r="H37" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I37" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J37" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K37" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="M37" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N37" t="s">
         <v>29</v>
@@ -6372,11 +6627,11 @@
       <c r="O37" t="s">
         <v>30</v>
       </c>
-      <c r="Q37" s="8" t="s">
-        <v>308</v>
+      <c r="Q37" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="R37" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -6391,9 +6646,9 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="B38" s="7">
+        <v>326</v>
+      </c>
+      <c r="B38" s="1">
         <v>46441</v>
       </c>
       <c r="C38" s="1" t="str">
@@ -6401,34 +6656,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G38" s="2">
         <v>80</v>
       </c>
       <c r="H38" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I38" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J38" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K38" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="L38" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="M38" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N38" t="s">
         <v>29</v>
@@ -6437,13 +6692,13 @@
         <v>30</v>
       </c>
       <c r="P38" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>310</v>
+        <v>239</v>
+      </c>
+      <c r="Q38" s="10" t="s">
+        <v>327</v>
       </c>
       <c r="R38" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="S38" t="s">
         <v>33</v>
@@ -6457,10 +6712,10 @@
       </c>
     </row>
     <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="B39" s="7">
+      <c r="A39" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B39" s="1">
         <v>46441</v>
       </c>
       <c r="C39" s="1" t="str">
@@ -6468,34 +6723,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>80</v>
+        <v>231</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>82</v>
+        <v>329</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H39" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I39" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J39" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K39" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="L39" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="M39" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N39" t="s">
         <v>29</v>
@@ -6504,19 +6759,19 @@
         <v>29</v>
       </c>
       <c r="P39" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q39" s="15" t="s">
-        <v>499</v>
+        <v>330</v>
+      </c>
+      <c r="Q39" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="R39" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="S39" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T39" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="U39" t="b">
         <f>FALSE()</f>
@@ -6525,9 +6780,9 @@
     </row>
     <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="B40" s="7">
+        <v>332</v>
+      </c>
+      <c r="B40" s="1">
         <v>46444</v>
       </c>
       <c r="C40" s="1" t="str">
@@ -6535,31 +6790,31 @@
         <v>Friday</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G40" s="2">
         <v>100</v>
       </c>
       <c r="H40" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I40" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J40" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K40" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="L40" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -6570,11 +6825,11 @@
       <c r="O40" t="s">
         <v>30</v>
       </c>
-      <c r="Q40" s="8" t="s">
-        <v>316</v>
+      <c r="Q40" s="10" t="s">
+        <v>334</v>
       </c>
       <c r="R40" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="S40" t="s">
         <v>33</v>
@@ -6601,21 +6856,21 @@
   <hyperlinks>
     <hyperlink ref="Q2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="Q3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="Q5" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="Q6" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="Q19" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="Q23" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="Q24" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="Q28" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="Q31" r:id="rId9" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="Q33" r:id="rId10" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="Q37" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="Q39" r:id="rId12" xr:uid="{C6A1392F-2DEE-417C-927C-B9C444D72EAE}"/>
+    <hyperlink ref="Q5" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="Q6" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="Q19" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="Q23" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="Q24" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="Q28" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="Q31" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="Q33" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="Q37" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="Q39" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId13"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6706,10 +6961,10 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B2" s="1">
         <v>46447</v>
       </c>
       <c r="C2" s="1" t="str">
@@ -6717,34 +6972,34 @@
         <v>Monday</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>80</v>
+        <v>60</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>82</v>
+        <v>337</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I2" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J2" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K2" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="L2" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="M2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -6753,19 +7008,19 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>493</v>
+        <v>343</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>344</v>
       </c>
       <c r="R2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="S2" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T2" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="U2" t="b">
         <f>FALSE()</f>
@@ -6774,9 +7029,9 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B3" s="7">
+        <v>345</v>
+      </c>
+      <c r="B3" s="1">
         <v>46448</v>
       </c>
       <c r="C3" s="1" t="str">
@@ -6784,31 +7039,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G3" s="2">
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I3" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J3" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="K3" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="M3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N3" t="s">
         <v>29</v>
@@ -6816,11 +7071,11 @@
       <c r="O3" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="8" t="s">
-        <v>329</v>
+      <c r="Q3" s="10" t="s">
+        <v>348</v>
       </c>
       <c r="R3" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -6835,9 +7090,9 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="B4" s="7">
+        <v>350</v>
+      </c>
+      <c r="B4" s="1">
         <v>46449</v>
       </c>
       <c r="C4" s="1" t="str">
@@ -6845,31 +7100,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G4" s="2">
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I4" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J4" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K4" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="M4" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
         <v>29</v>
@@ -6878,13 +7133,13 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>334</v>
+        <v>277</v>
+      </c>
+      <c r="Q4" s="10" t="s">
+        <v>353</v>
       </c>
       <c r="R4" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -6899,9 +7154,9 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="B5" s="7">
+        <v>355</v>
+      </c>
+      <c r="B5" s="1">
         <v>46450</v>
       </c>
       <c r="C5" s="1" t="str">
@@ -6909,34 +7164,34 @@
         <v>Thursday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2">
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I5" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J5" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K5" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="L5" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="M5" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N5" t="s">
         <v>29</v>
@@ -6945,13 +7200,13 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>339</v>
+        <v>172</v>
+      </c>
+      <c r="Q5" s="10" t="s">
+        <v>358</v>
       </c>
       <c r="R5" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -6966,9 +7221,9 @@
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="B6" s="7">
+        <v>359</v>
+      </c>
+      <c r="B6" s="1">
         <v>46455</v>
       </c>
       <c r="C6" s="1" t="str">
@@ -6976,31 +7231,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G6" s="2">
         <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I6" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J6" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K6" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="M6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N6" t="s">
         <v>29</v>
@@ -7009,13 +7264,13 @@
         <v>30</v>
       </c>
       <c r="P6" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>342</v>
+        <v>163</v>
+      </c>
+      <c r="Q6" s="10" t="s">
+        <v>361</v>
       </c>
       <c r="R6" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -7029,10 +7284,10 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="B7" s="7">
+      <c r="A7" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B7" s="1">
         <v>46455</v>
       </c>
       <c r="C7" s="1" t="str">
@@ -7040,34 +7295,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>80</v>
+        <v>364</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>82</v>
+        <v>105</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H7" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I7" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J7" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K7" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="L7" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="M7" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
@@ -7076,19 +7331,19 @@
         <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q7" s="15" t="s">
-        <v>500</v>
+        <v>366</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>367</v>
       </c>
       <c r="R7" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="S7" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T7" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="U7" t="b">
         <f>FALSE()</f>
@@ -7096,10 +7351,10 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="B8" s="7">
+      <c r="A8" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="B8" s="1">
         <v>46456</v>
       </c>
       <c r="C8" s="1" t="str">
@@ -7107,31 +7362,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2">
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I8" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J8" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K8" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="M8" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -7140,10 +7395,10 @@
         <v>29</v>
       </c>
       <c r="P8" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>236</v>
+        <v>252</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>253</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -7158,9 +7413,9 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="B9" s="7">
+        <v>369</v>
+      </c>
+      <c r="B9" s="1">
         <v>46456</v>
       </c>
       <c r="C9" s="1" t="str">
@@ -7168,31 +7423,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G9" s="2">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I9" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J9" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K9" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="M9" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -7201,13 +7456,13 @@
         <v>30</v>
       </c>
       <c r="P9" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>350</v>
+        <v>269</v>
+      </c>
+      <c r="Q9" s="10" t="s">
+        <v>370</v>
       </c>
       <c r="R9" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -7222,9 +7477,9 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10" s="7">
+        <v>179</v>
+      </c>
+      <c r="B10" s="1">
         <v>46457</v>
       </c>
       <c r="C10" s="1" t="str">
@@ -7232,31 +7487,31 @@
         <v>Thursday</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G10" s="2">
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I10" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J10" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K10" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
@@ -7264,11 +7519,11 @@
       <c r="O10" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="8" t="s">
-        <v>353</v>
+      <c r="Q10" s="10" t="s">
+        <v>373</v>
       </c>
       <c r="R10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -7283,9 +7538,9 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="B11" s="7">
+        <v>374</v>
+      </c>
+      <c r="B11" s="1">
         <v>46462</v>
       </c>
       <c r="C11" s="1" t="str">
@@ -7293,34 +7548,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2">
         <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I11" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J11" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K11" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="L11" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="M11" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -7328,11 +7583,11 @@
       <c r="O11" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="8" t="s">
-        <v>356</v>
+      <c r="Q11" s="10" t="s">
+        <v>376</v>
       </c>
       <c r="R11" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -7347,9 +7602,9 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="B12" s="7">
+        <v>377</v>
+      </c>
+      <c r="B12" s="1">
         <v>46462</v>
       </c>
       <c r="C12" s="1" t="str">
@@ -7357,31 +7612,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G12" s="2">
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I12" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J12" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K12" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="M12" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
@@ -7390,13 +7645,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>359</v>
+        <v>282</v>
+      </c>
+      <c r="Q12" s="10" t="s">
+        <v>379</v>
       </c>
       <c r="R12" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -7411,9 +7666,9 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="B13" s="7">
+        <v>381</v>
+      </c>
+      <c r="B13" s="1">
         <v>46463</v>
       </c>
       <c r="C13" s="1" t="str">
@@ -7421,34 +7676,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G13" s="2">
         <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I13" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J13" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K13" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="L13" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="M13" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
@@ -7457,13 +7712,13 @@
         <v>30</v>
       </c>
       <c r="P13" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>363</v>
+        <v>64</v>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>383</v>
       </c>
       <c r="R13" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -7478,9 +7733,9 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="B14" s="7">
+        <v>385</v>
+      </c>
+      <c r="B14" s="1">
         <v>46464</v>
       </c>
       <c r="C14" s="1" t="str">
@@ -7488,34 +7743,34 @@
         <v>Thursday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G14" s="2">
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I14" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J14" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K14" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="L14" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="M14" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
@@ -7523,11 +7778,11 @@
       <c r="O14" t="s">
         <v>30</v>
       </c>
-      <c r="Q14" s="8" t="s">
-        <v>368</v>
+      <c r="Q14" s="10" t="s">
+        <v>388</v>
       </c>
       <c r="R14" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -7542,9 +7797,9 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="B15" s="7">
+        <v>390</v>
+      </c>
+      <c r="B15" s="1">
         <v>46468</v>
       </c>
       <c r="C15" s="1" t="str">
@@ -7552,34 +7807,34 @@
         <v>Monday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2">
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I15" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J15" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K15" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="L15" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="M15" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N15" t="s">
         <v>29</v>
@@ -7587,11 +7842,11 @@
       <c r="O15" t="s">
         <v>30</v>
       </c>
-      <c r="Q15" s="8" t="s">
-        <v>371</v>
+      <c r="Q15" s="10" t="s">
+        <v>391</v>
       </c>
       <c r="R15" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -7606,9 +7861,9 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="B16" s="7">
+        <v>393</v>
+      </c>
+      <c r="B16" s="1">
         <v>46469</v>
       </c>
       <c r="C16" s="1" t="str">
@@ -7616,31 +7871,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I16" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J16" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="K16" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="M16" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -7649,13 +7904,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>378</v>
+        <v>397</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>398</v>
       </c>
       <c r="R16" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -7670,9 +7925,9 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="B17" s="7">
+        <v>400</v>
+      </c>
+      <c r="B17" s="1">
         <v>46470</v>
       </c>
       <c r="C17" s="1" t="str">
@@ -7680,34 +7935,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G17" s="2">
         <v>80</v>
       </c>
       <c r="H17" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I17" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J17" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K17" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="L17" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="M17" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
@@ -7715,11 +7970,11 @@
       <c r="O17" t="s">
         <v>30</v>
       </c>
-      <c r="Q17" s="8" t="s">
-        <v>382</v>
+      <c r="Q17" s="10" t="s">
+        <v>402</v>
       </c>
       <c r="R17" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -7734,9 +7989,9 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="B18" s="7">
+        <v>403</v>
+      </c>
+      <c r="B18" s="1">
         <v>46486</v>
       </c>
       <c r="C18" s="1" t="str">
@@ -7744,34 +7999,34 @@
         <v>Friday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G18" s="2">
         <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I18" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J18" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K18" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="L18" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="M18" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N18" t="s">
         <v>29</v>
@@ -7780,13 +8035,13 @@
         <v>30</v>
       </c>
       <c r="P18" t="s">
-        <v>384</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>385</v>
+        <v>404</v>
+      </c>
+      <c r="Q18" s="10" t="s">
+        <v>405</v>
       </c>
       <c r="R18" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -7801,9 +8056,9 @@
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="B19" s="7">
+        <v>407</v>
+      </c>
+      <c r="B19" s="1">
         <v>46492</v>
       </c>
       <c r="C19" s="1" t="str">
@@ -7811,31 +8066,31 @@
         <v>Thursday</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G19" s="2">
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I19" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J19" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K19" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="M19" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N19" t="s">
         <v>30</v>
@@ -7844,13 +8099,13 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>389</v>
+        <v>408</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>409</v>
       </c>
       <c r="R19" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -7865,9 +8120,9 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="B20" s="7">
+        <v>411</v>
+      </c>
+      <c r="B20" s="1">
         <v>46496</v>
       </c>
       <c r="C20" s="1" t="str">
@@ -7875,31 +8130,31 @@
         <v>Monday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G20" s="2">
         <v>100</v>
       </c>
       <c r="H20" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I20" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J20" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K20" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="L20" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="M20" t="s">
         <v>23</v>
@@ -7910,11 +8165,11 @@
       <c r="O20" t="s">
         <v>30</v>
       </c>
-      <c r="Q20" s="8" t="s">
-        <v>393</v>
+      <c r="Q20" s="10" t="s">
+        <v>413</v>
       </c>
       <c r="R20" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -7929,9 +8184,9 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="B21" s="7">
+        <v>414</v>
+      </c>
+      <c r="B21" s="1">
         <v>46500</v>
       </c>
       <c r="C21" s="1" t="str">
@@ -7939,31 +8194,31 @@
         <v>Friday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G21" s="2">
         <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I21" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J21" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="K21" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="M21" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
@@ -7972,13 +8227,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>397</v>
+        <v>416</v>
+      </c>
+      <c r="Q21" s="10" t="s">
+        <v>417</v>
       </c>
       <c r="R21" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -7993,9 +8248,9 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="B22" s="7">
+        <v>419</v>
+      </c>
+      <c r="B22" s="1">
         <v>46505</v>
       </c>
       <c r="C22" s="1" t="str">
@@ -8003,31 +8258,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G22" s="2">
         <v>6</v>
       </c>
       <c r="H22" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I22" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J22" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="K22" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="M22" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N22" t="s">
         <v>29</v>
@@ -8035,11 +8290,11 @@
       <c r="O22" t="s">
         <v>30</v>
       </c>
-      <c r="Q22" s="8" t="s">
-        <v>400</v>
+      <c r="Q22" s="10" t="s">
+        <v>420</v>
       </c>
       <c r="R22" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -8053,10 +8308,10 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="B23" s="7">
+      <c r="A23" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="B23" s="1">
         <v>46506</v>
       </c>
       <c r="C23" s="1" t="str">
@@ -8064,31 +8319,31 @@
         <v>Thursday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G23" s="2">
         <v>80</v>
       </c>
       <c r="H23" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I23" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J23" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K23" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="M23" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N23" t="s">
         <v>30</v>
@@ -8097,13 +8352,13 @@
         <v>29</v>
       </c>
       <c r="P23" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q23" s="8" t="s">
-        <v>389</v>
+        <v>408</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>409</v>
       </c>
       <c r="R23" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -8118,9 +8373,9 @@
     </row>
     <row r="24" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B24" s="7">
+        <v>134</v>
+      </c>
+      <c r="B24" s="1">
         <v>46507</v>
       </c>
       <c r="C24" s="1" t="str">
@@ -8128,31 +8383,31 @@
         <v>Friday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G24" s="2">
         <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I24" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J24" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K24" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="M24" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -8161,13 +8416,13 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>402</v>
+        <v>136</v>
+      </c>
+      <c r="Q24" s="10" t="s">
+        <v>422</v>
       </c>
       <c r="R24" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -8182,9 +8437,9 @@
     </row>
     <row r="25" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="B25" s="7">
+        <v>423</v>
+      </c>
+      <c r="B25" s="1">
         <v>46512</v>
       </c>
       <c r="C25" s="1" t="str">
@@ -8192,34 +8447,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G25" s="2">
         <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I25" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J25" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K25" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="L25" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="M25" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="N25" t="s">
         <v>29</v>
@@ -8227,11 +8482,11 @@
       <c r="O25" t="s">
         <v>30</v>
       </c>
-      <c r="Q25" s="8" t="s">
-        <v>405</v>
+      <c r="Q25" s="10" t="s">
+        <v>425</v>
       </c>
       <c r="R25" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -8246,9 +8501,9 @@
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="B26" s="7">
+        <v>426</v>
+      </c>
+      <c r="B26" s="1">
         <v>46512</v>
       </c>
       <c r="C26" s="1" t="str">
@@ -8256,34 +8511,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G26" s="2">
         <v>80</v>
       </c>
       <c r="H26" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I26" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J26" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K26" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="L26" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="M26" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="N26" t="s">
         <v>29</v>
@@ -8291,11 +8546,11 @@
       <c r="O26" t="s">
         <v>30</v>
       </c>
-      <c r="Q26" s="8" t="s">
-        <v>407</v>
+      <c r="Q26" s="10" t="s">
+        <v>427</v>
       </c>
       <c r="R26" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -8310,9 +8565,9 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B27" s="7">
+        <v>147</v>
+      </c>
+      <c r="B27" s="1">
         <v>46513</v>
       </c>
       <c r="C27" s="1" t="str">
@@ -8320,31 +8575,31 @@
         <v>Thursday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G27" s="2">
         <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I27" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J27" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K27" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="M27" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N27" t="s">
         <v>29</v>
@@ -8352,11 +8607,11 @@
       <c r="O27" t="s">
         <v>30</v>
       </c>
-      <c r="Q27" s="8" t="s">
-        <v>408</v>
+      <c r="Q27" s="10" t="s">
+        <v>428</v>
       </c>
       <c r="R27" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -8370,10 +8625,10 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="B28" s="7">
+      <c r="A28" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B28" s="1">
         <v>46517</v>
       </c>
       <c r="C28" s="1" t="str">
@@ -8381,34 +8636,34 @@
         <v>Monday</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>80</v>
+        <v>46</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>82</v>
+        <v>430</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H28" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I28" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J28" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K28" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="L28" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="M28" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N28" t="s">
         <v>29</v>
@@ -8417,19 +8672,19 @@
         <v>29</v>
       </c>
       <c r="P28" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q28" s="8" t="s">
-        <v>494</v>
+        <v>431</v>
+      </c>
+      <c r="Q28" s="10" t="s">
+        <v>432</v>
       </c>
       <c r="R28" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="S28" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T28" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="U28" t="b">
         <f>FALSE()</f>
@@ -8438,9 +8693,9 @@
     </row>
     <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="B29" s="7">
+        <v>433</v>
+      </c>
+      <c r="B29" s="1">
         <v>46518</v>
       </c>
       <c r="C29" s="1" t="str">
@@ -8448,34 +8703,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G29" s="2">
         <v>80</v>
       </c>
       <c r="H29" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I29" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J29" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K29" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="L29" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="M29" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N29" t="s">
         <v>29</v>
@@ -8484,13 +8739,13 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q29" s="8" t="s">
-        <v>414</v>
+        <v>239</v>
+      </c>
+      <c r="Q29" s="10" t="s">
+        <v>435</v>
       </c>
       <c r="R29" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -8505,9 +8760,9 @@
     </row>
     <row r="30" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="B30" s="7">
+        <v>436</v>
+      </c>
+      <c r="B30" s="1">
         <v>46519</v>
       </c>
       <c r="C30" s="1" t="str">
@@ -8515,31 +8770,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G30" s="2">
         <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I30" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J30" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K30" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="M30" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
@@ -8548,13 +8803,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q30" s="8" t="s">
-        <v>416</v>
+        <v>252</v>
+      </c>
+      <c r="Q30" s="10" t="s">
+        <v>437</v>
       </c>
       <c r="R30" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -8569,9 +8824,9 @@
     </row>
     <row r="31" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="B31" s="7">
+        <v>438</v>
+      </c>
+      <c r="B31" s="1">
         <v>46520</v>
       </c>
       <c r="C31" s="1" t="str">
@@ -8579,31 +8834,31 @@
         <v>Thursday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G31" s="2">
         <v>80</v>
       </c>
       <c r="H31" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I31" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J31" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K31" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="M31" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N31" t="s">
         <v>30</v>
@@ -8611,11 +8866,11 @@
       <c r="O31" t="s">
         <v>30</v>
       </c>
-      <c r="Q31" s="8" t="s">
-        <v>418</v>
+      <c r="Q31" s="10" t="s">
+        <v>439</v>
       </c>
       <c r="R31" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -8630,9 +8885,9 @@
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="B32" s="7">
+        <v>441</v>
+      </c>
+      <c r="B32" s="1">
         <v>46525</v>
       </c>
       <c r="C32" s="1" t="str">
@@ -8640,34 +8895,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G32" s="2">
         <v>80</v>
       </c>
       <c r="H32" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I32" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J32" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K32" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="L32" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="M32" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="N32" t="s">
         <v>29</v>
@@ -8676,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="P32" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q32" s="8" t="s">
-        <v>421</v>
+        <v>64</v>
+      </c>
+      <c r="Q32" s="10" t="s">
+        <v>442</v>
       </c>
       <c r="R32" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -8697,9 +8952,9 @@
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B33" s="7">
+        <v>161</v>
+      </c>
+      <c r="B33" s="1">
         <v>46526</v>
       </c>
       <c r="C33" s="1" t="str">
@@ -8707,31 +8962,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G33" s="2">
         <v>16</v>
       </c>
       <c r="H33" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I33" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J33" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="K33" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="M33" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="N33" t="s">
         <v>29</v>
@@ -8740,13 +8995,13 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q33" s="8" t="s">
-        <v>423</v>
+        <v>163</v>
+      </c>
+      <c r="Q33" s="10" t="s">
+        <v>444</v>
       </c>
       <c r="R33" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="S33" t="s">
         <v>33</v>
@@ -8760,10 +9015,10 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="B34" s="7">
+      <c r="A34" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="B34" s="1">
         <v>46527</v>
       </c>
       <c r="C34" s="1" t="str">
@@ -8771,31 +9026,31 @@
         <v>Thursday</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G34" s="2">
         <v>80</v>
       </c>
       <c r="H34" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I34" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J34" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K34" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="M34" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N34" t="s">
         <v>30</v>
@@ -8804,13 +9059,13 @@
         <v>29</v>
       </c>
       <c r="P34" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q34" s="8" t="s">
-        <v>389</v>
+        <v>408</v>
+      </c>
+      <c r="Q34" s="10" t="s">
+        <v>409</v>
       </c>
       <c r="R34" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="S34" t="s">
         <v>33</v>
@@ -8824,10 +9079,10 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="B35" s="7">
+      <c r="A35" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B35" s="1">
         <v>46527</v>
       </c>
       <c r="C35" s="1" t="str">
@@ -8835,34 +9090,34 @@
         <v>Thursday</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>80</v>
+        <v>447</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>82</v>
+        <v>448</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H35" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I35" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J35" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K35" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="L35" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="M35" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N35" t="s">
         <v>29</v>
@@ -8871,19 +9126,19 @@
         <v>29</v>
       </c>
       <c r="P35" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q35" s="8" t="s">
-        <v>501</v>
+        <v>449</v>
+      </c>
+      <c r="Q35" s="10" t="s">
+        <v>450</v>
       </c>
       <c r="R35" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="S35" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T35" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="U35" t="b">
         <f>FALSE()</f>
@@ -8892,9 +9147,9 @@
     </row>
     <row r="36" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="B36" s="7">
+        <v>451</v>
+      </c>
+      <c r="B36" s="1">
         <v>46533</v>
       </c>
       <c r="C36" s="1" t="str">
@@ -8902,31 +9157,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="G36" s="2">
         <v>12</v>
       </c>
       <c r="H36" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I36" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J36" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="K36" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="M36" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N36" t="s">
         <v>29</v>
@@ -8934,11 +9189,11 @@
       <c r="O36" t="s">
         <v>30</v>
       </c>
-      <c r="Q36" s="8" t="s">
-        <v>430</v>
+      <c r="Q36" s="10" t="s">
+        <v>452</v>
       </c>
       <c r="R36" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="S36" t="s">
         <v>33</v>
@@ -8952,10 +9207,10 @@
       </c>
     </row>
     <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>431</v>
-      </c>
-      <c r="B37" s="7">
+      <c r="A37" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="B37" s="1">
         <v>46534</v>
       </c>
       <c r="C37" s="1" t="str">
@@ -8963,31 +9218,31 @@
         <v>Thursday</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G37" s="2">
         <v>80</v>
       </c>
       <c r="H37" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="I37" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J37" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="K37" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="M37" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N37" t="s">
         <v>30</v>
@@ -8995,8 +9250,8 @@
       <c r="O37" t="s">
         <v>29</v>
       </c>
-      <c r="Q37" s="8" t="s">
-        <v>418</v>
+      <c r="Q37" s="10" t="s">
+        <v>439</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -9021,17 +9276,17 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="Q6" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="Q21" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="Q23" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="Q34" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="Q37" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
-    <hyperlink ref="Q7" r:id="rId6" xr:uid="{F0AD118D-06F4-42C5-A9C0-E95F9538750E}"/>
+    <hyperlink ref="Q6" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="Q7" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="Q21" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="Q23" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="Q34" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="Q37" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9122,10 +9377,10 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>432</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="B2" s="1">
         <v>46546</v>
       </c>
       <c r="C2" s="1" t="str">
@@ -9133,34 +9388,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>80</v>
+        <v>111</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>82</v>
+        <v>455</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I2" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J2" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K2" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="L2" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="M2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -9169,19 +9424,19 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>495</v>
+        <v>461</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>462</v>
       </c>
       <c r="R2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="S2" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T2" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="U2" t="b">
         <f>FALSE()</f>
@@ -9190,9 +9445,9 @@
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="B3" s="7">
+        <v>463</v>
+      </c>
+      <c r="B3" s="1">
         <v>46547</v>
       </c>
       <c r="C3" s="1" t="str">
@@ -9200,34 +9455,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G3" s="2">
         <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I3" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J3" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K3" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="L3" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="M3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s">
         <v>29</v>
@@ -9236,13 +9491,13 @@
         <v>30</v>
       </c>
       <c r="P3" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>443</v>
+        <v>125</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>466</v>
       </c>
       <c r="R3" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -9257,9 +9512,9 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="B4" s="7">
+        <v>468</v>
+      </c>
+      <c r="B4" s="1">
         <v>46548</v>
       </c>
       <c r="C4" s="1" t="str">
@@ -9267,34 +9522,34 @@
         <v>Thursday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G4" s="2">
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I4" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J4" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K4" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="L4" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="M4" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N4" t="s">
         <v>29</v>
@@ -9303,13 +9558,13 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>448</v>
+        <v>172</v>
+      </c>
+      <c r="Q4" s="10" t="s">
+        <v>471</v>
       </c>
       <c r="R4" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -9324,9 +9579,9 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="B5" s="7">
+        <v>472</v>
+      </c>
+      <c r="B5" s="1">
         <v>46552</v>
       </c>
       <c r="C5" s="1" t="str">
@@ -9334,31 +9589,31 @@
         <v>Monday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2">
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I5" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J5" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="K5" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="M5" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s">
         <v>29</v>
@@ -9367,13 +9622,13 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>451</v>
+        <v>247</v>
+      </c>
+      <c r="Q5" s="10" t="s">
+        <v>474</v>
       </c>
       <c r="R5" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -9388,9 +9643,9 @@
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="B6" s="7">
+        <v>476</v>
+      </c>
+      <c r="B6" s="1">
         <v>46553</v>
       </c>
       <c r="C6" s="1" t="str">
@@ -9398,31 +9653,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G6" s="2">
         <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I6" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J6" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K6" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="L6" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
@@ -9433,11 +9688,11 @@
       <c r="O6" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" s="8" t="s">
-        <v>455</v>
+      <c r="Q6" s="10" t="s">
+        <v>478</v>
       </c>
       <c r="R6" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -9451,10 +9706,10 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>456</v>
-      </c>
-      <c r="B7" s="7">
+      <c r="A7" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="B7" s="1">
         <v>46554</v>
       </c>
       <c r="C7" s="1" t="str">
@@ -9462,31 +9717,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G7" s="2">
         <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I7" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J7" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="K7" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="M7" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N7" t="s">
         <v>30</v>
@@ -9495,10 +9750,10 @@
         <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>416</v>
+        <v>252</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>437</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -9513,9 +9768,9 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="B8" s="7">
+        <v>480</v>
+      </c>
+      <c r="B8" s="1">
         <v>46561</v>
       </c>
       <c r="C8" s="1" t="str">
@@ -9523,31 +9778,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2">
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I8" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J8" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="K8" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="M8" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -9556,13 +9811,13 @@
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>458</v>
+        <v>282</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>481</v>
       </c>
       <c r="R8" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -9577,9 +9832,9 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="B9" s="7">
+        <v>483</v>
+      </c>
+      <c r="B9" s="1">
         <v>46562</v>
       </c>
       <c r="C9" s="1" t="str">
@@ -9587,34 +9842,34 @@
         <v>Thursday</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G9" s="2">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I9" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J9" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K9" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="L9" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="M9" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -9622,11 +9877,11 @@
       <c r="O9" t="s">
         <v>30</v>
       </c>
-      <c r="Q9" s="8" t="s">
-        <v>462</v>
+      <c r="Q9" s="10" t="s">
+        <v>485</v>
       </c>
       <c r="R9" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -9641,9 +9896,9 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="B10" s="7">
+        <v>486</v>
+      </c>
+      <c r="B10" s="1">
         <v>46568</v>
       </c>
       <c r="C10" s="1" t="str">
@@ -9651,34 +9906,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G10" s="2">
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I10" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J10" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K10" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="L10" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="M10" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
@@ -9686,11 +9941,11 @@
       <c r="O10" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="8" t="s">
-        <v>465</v>
+      <c r="Q10" s="10" t="s">
+        <v>488</v>
       </c>
       <c r="R10" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -9705,9 +9960,9 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="B11" s="7">
+        <v>489</v>
+      </c>
+      <c r="B11" s="1">
         <v>46569</v>
       </c>
       <c r="C11" s="1" t="str">
@@ -9715,34 +9970,34 @@
         <v>Thursday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2">
         <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I11" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J11" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K11" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="L11" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="M11" t="s">
-        <v>260</v>
+        <v>41</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -9750,11 +10005,11 @@
       <c r="O11" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="8" t="s">
-        <v>468</v>
+      <c r="Q11" s="10" t="s">
+        <v>491</v>
       </c>
       <c r="R11" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -9769,9 +10024,9 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="B12" s="7">
+        <v>492</v>
+      </c>
+      <c r="B12" s="1">
         <v>46570</v>
       </c>
       <c r="C12" s="1" t="str">
@@ -9779,31 +10034,31 @@
         <v>Friday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G12" s="2">
         <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I12" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J12" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="K12" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="M12" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
@@ -9812,13 +10067,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>471</v>
+        <v>136</v>
+      </c>
+      <c r="Q12" s="10" t="s">
+        <v>494</v>
       </c>
       <c r="R12" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -9832,10 +10087,10 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>473</v>
-      </c>
-      <c r="B13" s="7">
+      <c r="A13" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="B13" s="1">
         <v>46574</v>
       </c>
       <c r="C13" s="1" t="str">
@@ -9843,34 +10098,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>80</v>
+        <v>60</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>82</v>
+        <v>497</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I13" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J13" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K13" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="L13" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="M13" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
@@ -9879,19 +10134,19 @@
         <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>496</v>
+        <v>498</v>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>499</v>
       </c>
       <c r="R13" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="S13" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T13" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="U13" t="b">
         <f>FALSE()</f>
@@ -9899,10 +10154,10 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="B14" s="7">
+      <c r="A14" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="B14" s="1">
         <v>46575</v>
       </c>
       <c r="C14" s="1" t="str">
@@ -9910,31 +10165,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G14" s="2">
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I14" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J14" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="K14" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="M14" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="N14" t="s">
         <v>30</v>
@@ -9943,10 +10198,10 @@
         <v>29</v>
       </c>
       <c r="P14" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>458</v>
+        <v>282</v>
+      </c>
+      <c r="Q14" s="10" t="s">
+        <v>481</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -9960,10 +10215,10 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="B15" s="7">
+      <c r="A15" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="B15" s="1">
         <v>46575</v>
       </c>
       <c r="C15" s="1" t="str">
@@ -9971,31 +10226,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2">
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I15" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J15" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="K15" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="M15" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="N15" t="s">
         <v>30</v>
@@ -10004,10 +10259,10 @@
         <v>29</v>
       </c>
       <c r="P15" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>416</v>
+        <v>252</v>
+      </c>
+      <c r="Q15" s="10" t="s">
+        <v>437</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -10022,9 +10277,9 @@
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B16" s="7">
+        <v>242</v>
+      </c>
+      <c r="B16" s="1">
         <v>46576</v>
       </c>
       <c r="C16" s="1" t="str">
@@ -10032,31 +10287,31 @@
         <v>Thursday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G16" s="2">
         <v>80</v>
       </c>
       <c r="H16" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I16" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J16" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="K16" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="M16" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
@@ -10065,13 +10320,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>478</v>
+        <v>136</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>502</v>
       </c>
       <c r="R16" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -10085,10 +10340,10 @@
       </c>
     </row>
     <row r="17" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="B17" s="7">
+      <c r="A17" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="B17" s="1">
         <v>46582</v>
       </c>
       <c r="C17" s="1" t="str">
@@ -10096,98 +10351,98 @@
         <v>Wednesday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>80</v>
+        <v>88</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>82</v>
+        <v>504</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I17" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J17" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K17" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="L17" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="M17" t="s">
+        <v>91</v>
+      </c>
+      <c r="N17" t="s">
+        <v>29</v>
+      </c>
+      <c r="O17" t="s">
+        <v>29</v>
+      </c>
+      <c r="P17" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q17" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="R17" t="s">
+        <v>94</v>
+      </c>
+      <c r="S17" t="s">
+        <v>37</v>
+      </c>
+      <c r="T17" t="s">
+        <v>38</v>
+      </c>
+      <c r="U17" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46589</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="N17" t="s">
-        <v>29</v>
-      </c>
-      <c r="O17" t="s">
-        <v>29</v>
-      </c>
-      <c r="P17" t="s">
-        <v>481</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="R17" t="s">
-        <v>87</v>
-      </c>
-      <c r="S17" t="s">
-        <v>80</v>
-      </c>
-      <c r="T17" t="s">
-        <v>82</v>
-      </c>
-      <c r="U17" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>482</v>
-      </c>
-      <c r="B18" s="7">
-        <v>46589</v>
-      </c>
-      <c r="C18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Wednesday</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G18" s="2">
         <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I18" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J18" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="K18" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="M18" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="N18" t="s">
         <v>30</v>
@@ -10196,10 +10451,10 @@
         <v>29</v>
       </c>
       <c r="P18" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>458</v>
+        <v>282</v>
+      </c>
+      <c r="Q18" s="10" t="s">
+        <v>481</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -10213,10 +10468,10 @@
       </c>
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>483</v>
-      </c>
-      <c r="B19" s="7">
+      <c r="A19" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="B19" s="1">
         <v>46604</v>
       </c>
       <c r="C19" s="1" t="str">
@@ -10224,34 +10479,34 @@
         <v>Thursday</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>82</v>
+        <v>509</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="H19" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I19" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J19" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K19" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="L19" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="M19" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N19" t="s">
         <v>29</v>
@@ -10260,19 +10515,19 @@
         <v>29</v>
       </c>
       <c r="P19" t="s">
-        <v>485</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>497</v>
+        <v>510</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>511</v>
       </c>
       <c r="R19" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="S19" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="T19" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="U19" t="b">
         <f>FALSE()</f>
@@ -10281,9 +10536,9 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="B20" s="7">
+        <v>512</v>
+      </c>
+      <c r="B20" s="1">
         <v>46612</v>
       </c>
       <c r="C20" s="1" t="str">
@@ -10291,34 +10546,34 @@
         <v>Friday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G20" s="2">
         <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I20" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J20" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K20" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="L20" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="M20" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N20" t="s">
         <v>29</v>
@@ -10327,13 +10582,13 @@
         <v>30</v>
       </c>
       <c r="P20" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>488</v>
+        <v>513</v>
+      </c>
+      <c r="Q20" s="10" t="s">
+        <v>514</v>
       </c>
       <c r="R20" t="s">
-        <v>489</v>
+        <v>515</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -10358,12 +10613,12 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="Q9" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="Q9" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF840E23-F1CB-443D-8F45-2E4912C31557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B61B848-660C-4134-BC24-7647A0EF8121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19215" yWindow="240" windowWidth="38370" windowHeight="20505" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="57600" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2169" uniqueCount="525">
   <si>
     <t>Event Name</t>
   </si>
@@ -155,6 +155,9 @@
     <t>Local</t>
   </si>
   <si>
+    <t>St Pauls Nursery Community Room</t>
+  </si>
+  <si>
     <t>External</t>
   </si>
   <si>
@@ -356,9 +359,6 @@
     <t>CPD Programme: Using Evidence to Strengthen Your Early Years Leadership - Session 1</t>
   </si>
   <si>
-    <t>St Pauls Nursery Community Room</t>
-  </si>
-  <si>
     <t>Leadership</t>
   </si>
   <si>
@@ -524,6 +524,18 @@
     <t>CPD Programme: Using Evidence to Strengthen Your Early Years Leadership - Session 2</t>
   </si>
   <si>
+    <t>North Somerset Brilliant Babies Community of Practice Network - November 2026</t>
+  </si>
+  <si>
+    <t>7:00 pm - 8:15 pm</t>
+  </si>
+  <si>
+    <t>Run by North Somerset; booked via their iLearn platform, not through our website.</t>
+  </si>
+  <si>
+    <t>The Brilliant Babies Community of Practice Network is open to anyone working with babies (e.g. nurseries, childminders, PVI settings) in North Somerset. It offers a lively, dynamic opportunity for professional conversation, sharing celebrations, problem-solving as a group, and sharing recent research and articles.</t>
+  </si>
+  <si>
     <t>Exploring an Early Years Curriculum: Open Study Day at St Pauls Nursery</t>
   </si>
   <si>
@@ -1211,6 +1223,9 @@
     <t>Connect, reflect and learn alongside colleagues who share a commitment to equality, diversity and inclusion — discussing current challenges, sharing effective practice, exploring real-life dilemmas and gaining fresh ideas to support your own setting.</t>
   </si>
   <si>
+    <t>North Somerset Brilliant Babies Community of Practice Network - March 2027</t>
+  </si>
+  <si>
     <t>Responsive Communication Strategies for Babies (SALT Network Session)</t>
   </si>
   <si>
@@ -1562,6 +1577,9 @@
     <t>https://beyth.co.uk/course/bristol-terrific-twos-network-sessions-july-2027/</t>
   </si>
   <si>
+    <t>North Somerset Brilliant Babies Community of Practice Network - July 2027</t>
+  </si>
+  <si>
     <t>Getting It Right for Babies CPD Programme - Session 3</t>
   </si>
   <si>
@@ -1587,6 +1605,15 @@
   </si>
   <si>
     <t>Join Specialist Health Visitor Sarah Clarke to explore infant mental health and wellbeing and how it shapes babies' current and lifelong development, sharing ideas to support babies' mental health and development in early years settings — part of the Talking About... series of informal online networking sessions.</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/north-somerset-brilliant-babies-community-of-practice-network-november-2026/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/north-somerset-brilliant-babies-community-of-practice-network-march-2027/</t>
+  </si>
+  <si>
+    <t>https://beyth.co.uk/course/north-somerset-brilliant-babies-community-of-practice-network-july-2027/</t>
   </si>
 </sst>
 </file>
@@ -1616,6 +1643,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -1623,15 +1657,8 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1668,12 +1695,6 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1684,11 +1705,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1700,10 +1720,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1711,17 +1730,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1806,8 +1820,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TableRP12627" displayName="TableRP12627" ref="A1:U33" totalsRowShown="0">
-  <autoFilter ref="A1:U33" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TableRP12627" displayName="TableRP12627" ref="A1:U34" totalsRowShown="0">
+  <autoFilter ref="A1:U34" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Event Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Activity Date"/>
@@ -1866,8 +1880,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="TableRP32627" displayName="TableRP32627" ref="A1:U37" totalsRowShown="0">
-  <autoFilter ref="A1:U37" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="TableRP32627" displayName="TableRP32627" ref="A1:U38" totalsRowShown="0">
+  <autoFilter ref="A1:U38" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Event Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Activity Date"/>
@@ -1896,8 +1910,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="TableRP42627" displayName="TableRP42627" ref="A1:U20" totalsRowShown="0">
-  <autoFilter ref="A1:U20" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="TableRP42627" displayName="TableRP42627" ref="A1:U21" totalsRowShown="0">
+  <autoFilter ref="A1:U21" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Event Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Activity Date"/>
@@ -2101,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.85546875" customWidth="1"/>
@@ -2192,7 +2206,7 @@
         <v>46288</v>
       </c>
       <c r="C2" s="1" t="str">
-        <f t="shared" ref="C2:C33" si="0">IF(B2="","",TEXT(B2,"dddd"))</f>
+        <f t="shared" ref="C2:C34" si="0">IF(B2="","",TEXT(B2,"dddd"))</f>
         <v>Wednesday</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -2246,7 +2260,7 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B3" s="7">
@@ -2259,14 +2273,14 @@
       <c r="D3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="19" t="s">
+      <c r="F3" s="1" t="s">
         <v>38</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H3" t="s">
         <v>25</v>
@@ -2275,16 +2289,16 @@
         <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
         <v>28</v>
       </c>
       <c r="L3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N3" t="s">
         <v>29</v>
@@ -2293,19 +2307,19 @@
         <v>29</v>
       </c>
       <c r="P3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="Q3" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="R3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S3" t="s">
         <v>37</v>
       </c>
       <c r="T3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U3" t="b">
         <f>FALSE()</f>
@@ -2314,7 +2328,7 @@
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="7">
         <v>46300</v>
@@ -2324,13 +2338,13 @@
         <v>Monday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" s="2">
         <v>80</v>
@@ -2342,16 +2356,16 @@
         <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N4" t="s">
         <v>29</v>
@@ -2360,10 +2374,10 @@
         <v>30</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -2378,7 +2392,7 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="7">
         <v>46302</v>
@@ -2388,13 +2402,13 @@
         <v>Wednesday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" s="2">
         <v>80</v>
@@ -2406,17 +2420,17 @@
         <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" t="s">
         <v>28</v>
       </c>
       <c r="L5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" t="s">
         <v>56</v>
       </c>
-      <c r="M5" t="s">
-        <v>55</v>
-      </c>
       <c r="N5" t="s">
         <v>29</v>
       </c>
@@ -2424,10 +2438,10 @@
         <v>30</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -2442,7 +2456,7 @@
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B6" s="7">
         <v>46302</v>
@@ -2452,13 +2466,13 @@
         <v>Wednesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2">
         <v>80</v>
@@ -2470,17 +2484,17 @@
         <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6" t="s">
         <v>62</v>
       </c>
-      <c r="L6" t="s">
-        <v>63</v>
-      </c>
-      <c r="M6" t="s">
-        <v>61</v>
-      </c>
       <c r="N6" t="s">
         <v>29</v>
       </c>
@@ -2488,13 +2502,13 @@
         <v>30</v>
       </c>
       <c r="P6" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" s="10" t="s">
         <v>65</v>
       </c>
+      <c r="Q6" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="R6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -2509,7 +2523,7 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" s="7">
         <v>46303</v>
@@ -2525,7 +2539,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2">
         <v>10</v>
@@ -2552,7 +2566,7 @@
         <v>30</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R7" t="s">
         <v>32</v>
@@ -2570,7 +2584,7 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B8" s="7">
         <v>46307</v>
@@ -2580,13 +2594,13 @@
         <v>Monday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2">
         <v>80</v>
@@ -2598,13 +2612,13 @@
         <v>26</v>
       </c>
       <c r="J8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K8" t="s">
         <v>28</v>
       </c>
       <c r="M8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N8" t="s">
         <v>29</v>
@@ -2613,13 +2627,13 @@
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q8" s="10" t="s">
         <v>75</v>
       </c>
+      <c r="Q8" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="R8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -2634,7 +2648,7 @@
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9" s="7">
         <v>46308</v>
@@ -2644,13 +2658,13 @@
         <v>Tuesday</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9" s="2">
         <v>100</v>
@@ -2662,13 +2676,13 @@
         <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K9" t="s">
         <v>28</v>
       </c>
       <c r="L9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M9" t="s">
         <v>23</v>
@@ -2680,10 +2694,10 @@
         <v>30</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -2698,7 +2712,7 @@
     </row>
     <row r="10" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" s="7">
         <v>46309</v>
@@ -2708,15 +2722,15 @@
         <v>Wednesday</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="21">
+      <c r="E10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="2">
         <v>80</v>
       </c>
       <c r="H10" t="s">
@@ -2726,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K10" t="s">
         <v>28</v>
       </c>
       <c r="M10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
@@ -2741,10 +2755,10 @@
         <v>30</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -2759,7 +2773,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B11" s="7">
         <v>46309</v>
@@ -2769,16 +2783,16 @@
         <v>Wednesday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>38</v>
+        <v>90</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H11" t="s">
         <v>25</v>
@@ -2787,16 +2801,16 @@
         <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K11" t="s">
         <v>28</v>
       </c>
       <c r="L11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -2805,19 +2819,19 @@
         <v>29</v>
       </c>
       <c r="P11" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q11" s="8" t="s">
         <v>93</v>
       </c>
+      <c r="Q11" s="11" t="s">
+        <v>94</v>
+      </c>
       <c r="R11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S11" t="s">
         <v>37</v>
       </c>
       <c r="T11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U11" t="b">
         <f>FALSE()</f>
@@ -2825,8 +2839,8 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>95</v>
+      <c r="A12" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="B12" s="7">
         <v>46311</v>
@@ -2838,14 +2852,14 @@
       <c r="D12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="19" t="s">
-        <v>38</v>
+      <c r="G12" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H12" t="s">
         <v>25</v>
@@ -2854,16 +2868,16 @@
         <v>26</v>
       </c>
       <c r="J12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K12" t="s">
         <v>28</v>
       </c>
       <c r="L12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
@@ -2872,19 +2886,19 @@
         <v>29</v>
       </c>
       <c r="P12" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q12" s="9" t="s">
         <v>97</v>
       </c>
+      <c r="Q12" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="R12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S12" t="s">
         <v>37</v>
       </c>
       <c r="T12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U12" t="b">
         <f>FALSE()</f>
@@ -2893,7 +2907,7 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" s="7">
         <v>46315</v>
@@ -2903,15 +2917,15 @@
         <v>Tuesday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="21">
+      <c r="F13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="2">
         <v>80</v>
       </c>
       <c r="H13" t="s">
@@ -2921,10 +2935,10 @@
         <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M13" t="s">
         <v>23</v>
@@ -2936,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="P13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -2957,7 +2971,7 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B14" s="7">
         <v>46315</v>
@@ -2970,10 +2984,10 @@
         <v>36</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G14" s="2">
         <v>16</v>
@@ -3002,7 +3016,7 @@
       <c r="P14" t="s">
         <v>107</v>
       </c>
-      <c r="Q14" s="10" t="s">
+      <c r="Q14" s="8" t="s">
         <v>108</v>
       </c>
       <c r="R14" t="s">
@@ -3033,14 +3047,14 @@
       <c r="D15" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G15" s="12" t="s">
-        <v>38</v>
+      <c r="G15" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H15" t="s">
         <v>25</v>
@@ -3049,7 +3063,7 @@
         <v>26</v>
       </c>
       <c r="J15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K15" t="s">
         <v>28</v>
@@ -3058,7 +3072,7 @@
         <v>113</v>
       </c>
       <c r="M15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N15" t="s">
         <v>29</v>
@@ -3069,7 +3083,7 @@
       <c r="P15" t="s">
         <v>114</v>
       </c>
-      <c r="Q15" s="10" t="s">
+      <c r="Q15" s="8" t="s">
         <v>115</v>
       </c>
       <c r="R15" t="s">
@@ -3079,7 +3093,7 @@
         <v>37</v>
       </c>
       <c r="T15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U15" t="b">
         <f>FALSE()</f>
@@ -3098,13 +3112,13 @@
         <v>Wednesday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>118</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G16" s="2">
         <v>80</v>
@@ -3116,7 +3130,7 @@
         <v>26</v>
       </c>
       <c r="J16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K16" t="s">
         <v>119</v>
@@ -3165,10 +3179,10 @@
         <v>124</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G17" s="2">
         <v>80</v>
@@ -3180,16 +3194,16 @@
         <v>26</v>
       </c>
       <c r="J17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
@@ -3200,7 +3214,7 @@
       <c r="P17" t="s">
         <v>125</v>
       </c>
-      <c r="Q17" s="10" t="s">
+      <c r="Q17" s="8" t="s">
         <v>126</v>
       </c>
       <c r="R17" t="s">
@@ -3231,13 +3245,13 @@
       <c r="D18" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="21">
+      <c r="F18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="2">
         <v>500</v>
       </c>
       <c r="H18" t="s">
@@ -3247,10 +3261,10 @@
         <v>26</v>
       </c>
       <c r="J18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M18" t="s">
         <v>130</v>
@@ -3264,7 +3278,7 @@
       <c r="P18" t="s">
         <v>131</v>
       </c>
-      <c r="Q18" s="10" t="s">
+      <c r="Q18" s="8" t="s">
         <v>132</v>
       </c>
       <c r="R18" t="s">
@@ -3296,10 +3310,10 @@
         <v>135</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G19" s="2">
         <v>80</v>
@@ -3311,7 +3325,7 @@
         <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>
@@ -3328,7 +3342,7 @@
       <c r="P19" t="s">
         <v>136</v>
       </c>
-      <c r="Q19" s="10" t="s">
+      <c r="Q19" s="8" t="s">
         <v>137</v>
       </c>
       <c r="R19" t="s">
@@ -3359,14 +3373,14 @@
       <c r="D20" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G20" s="12" t="s">
-        <v>38</v>
+      <c r="G20" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H20" t="s">
         <v>25</v>
@@ -3375,7 +3389,7 @@
         <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K20" t="s">
         <v>28</v>
@@ -3384,7 +3398,7 @@
         <v>113</v>
       </c>
       <c r="M20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N20" t="s">
         <v>29</v>
@@ -3395,7 +3409,7 @@
       <c r="P20" t="s">
         <v>142</v>
       </c>
-      <c r="Q20" s="10" t="s">
+      <c r="Q20" s="8" t="s">
         <v>143</v>
       </c>
       <c r="R20" t="s">
@@ -3405,7 +3419,7 @@
         <v>37</v>
       </c>
       <c r="T20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U20" t="b">
         <f>FALSE()</f>
@@ -3424,13 +3438,13 @@
         <v>Wednesday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" s="2">
         <v>80</v>
@@ -3442,13 +3456,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N21" t="s">
         <v>30</v>
@@ -3485,13 +3499,13 @@
         <v>Thursday</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G22" s="2">
         <v>80</v>
@@ -3503,13 +3517,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N22" t="s">
         <v>29</v>
@@ -3517,7 +3531,7 @@
       <c r="O22" t="s">
         <v>30</v>
       </c>
-      <c r="Q22" s="10" t="s">
+      <c r="Q22" s="8" t="s">
         <v>148</v>
       </c>
       <c r="R22" t="s">
@@ -3552,7 +3566,7 @@
         <v>118</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2">
         <v>12</v>
@@ -3610,13 +3624,13 @@
         <v>Monday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2">
         <v>80</v>
@@ -3628,10 +3642,10 @@
         <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L24" t="s">
         <v>157</v>
@@ -3645,7 +3659,7 @@
       <c r="O24" t="s">
         <v>30</v>
       </c>
-      <c r="Q24" s="10" t="s">
+      <c r="Q24" s="8" t="s">
         <v>158</v>
       </c>
       <c r="R24" t="s">
@@ -3663,7 +3677,7 @@
       </c>
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>160</v>
       </c>
       <c r="B25" s="7">
@@ -3677,10 +3691,10 @@
         <v>36</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G25" s="2">
         <v>16</v>
@@ -3727,27 +3741,24 @@
       </c>
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="16" t="s">
         <v>161</v>
       </c>
       <c r="B26" s="7">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="C26" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>162</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G26" s="2">
-        <v>16</v>
+        <v>37</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H26" t="s">
         <v>25</v>
@@ -3756,34 +3767,37 @@
         <v>26</v>
       </c>
       <c r="J26" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="K26" t="s">
         <v>28</v>
       </c>
+      <c r="L26" t="s">
+        <v>113</v>
+      </c>
       <c r="M26" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="N26" t="s">
         <v>29</v>
       </c>
       <c r="O26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P26" t="s">
         <v>163</v>
       </c>
-      <c r="Q26" s="10" t="s">
+      <c r="Q26" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="R26" t="s">
         <v>164</v>
       </c>
-      <c r="R26" t="s">
-        <v>165</v>
-      </c>
       <c r="S26" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T26" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="U26" t="b">
         <f>FALSE()</f>
@@ -3792,23 +3806,26 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46337</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B27" s="7">
-        <v>46338</v>
-      </c>
-      <c r="C27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Thursday</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="G27" s="2">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="H27" t="s">
         <v>25</v>
@@ -3817,13 +3834,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="K27" t="s">
         <v>28</v>
       </c>
-      <c r="L27" t="s">
-        <v>113</v>
+      <c r="M27" t="s">
+        <v>106</v>
       </c>
       <c r="N27" t="s">
         <v>29</v>
@@ -3831,14 +3848,17 @@
       <c r="O27" t="s">
         <v>30</v>
       </c>
-      <c r="Q27" s="8" t="s">
+      <c r="P27" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q27" s="11" t="s">
         <v>168</v>
       </c>
       <c r="R27" t="s">
         <v>169</v>
       </c>
       <c r="S27" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="T27" t="s">
         <v>34</v>
@@ -3849,27 +3869,24 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="6" t="s">
         <v>170</v>
       </c>
       <c r="B28" s="7">
-        <v>46344</v>
+        <v>46338</v>
       </c>
       <c r="C28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Thursday</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G28" s="2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H28" t="s">
         <v>25</v>
@@ -3878,25 +3895,28 @@
         <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="K28" t="s">
-        <v>100</v>
-      </c>
-      <c r="M28" t="s">
-        <v>91</v>
+        <v>28</v>
+      </c>
+      <c r="L28" t="s">
+        <v>113</v>
       </c>
       <c r="N28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>145</v>
+        <v>172</v>
+      </c>
+      <c r="R28" t="s">
+        <v>173</v>
       </c>
       <c r="S28" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T28" t="s">
         <v>34</v>
@@ -3907,24 +3927,24 @@
       </c>
     </row>
     <row r="29" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>171</v>
+      <c r="A29" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="B29" s="7">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="C29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G29" s="2">
         <v>80</v>
@@ -3936,31 +3956,22 @@
         <v>26</v>
       </c>
       <c r="J29" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="K29" t="s">
-        <v>49</v>
-      </c>
-      <c r="L29" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="M29" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="N29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O29" t="s">
-        <v>30</v>
-      </c>
-      <c r="P29" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q29" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="R29" t="s">
-        <v>174</v>
+        <v>29</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -3978,20 +3989,20 @@
         <v>175</v>
       </c>
       <c r="B30" s="7">
-        <v>46351</v>
+        <v>46345</v>
       </c>
       <c r="C30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Thursday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G30" s="2">
         <v>80</v>
@@ -4003,13 +4014,16 @@
         <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="K30" t="s">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="L30" t="s">
+        <v>51</v>
       </c>
       <c r="M30" t="s">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="N30" t="s">
         <v>29</v>
@@ -4020,7 +4034,7 @@
       <c r="P30" t="s">
         <v>176</v>
       </c>
-      <c r="Q30" s="8" t="s">
+      <c r="Q30" s="11" t="s">
         <v>177</v>
       </c>
       <c r="R30" t="s">
@@ -4038,24 +4052,24 @@
       </c>
     </row>
     <row r="31" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="13" t="s">
         <v>179</v>
       </c>
       <c r="B31" s="7">
-        <v>46352</v>
+        <v>46351</v>
       </c>
       <c r="C31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G31" s="2">
         <v>80</v>
@@ -4067,19 +4081,22 @@
         <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K31" t="s">
+        <v>101</v>
+      </c>
+      <c r="M31" t="s">
+        <v>156</v>
+      </c>
+      <c r="N31" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31" t="s">
+        <v>30</v>
+      </c>
+      <c r="P31" t="s">
         <v>180</v>
-      </c>
-      <c r="M31" t="s">
-        <v>47</v>
-      </c>
-      <c r="N31" t="s">
-        <v>29</v>
-      </c>
-      <c r="O31" t="s">
-        <v>30</v>
       </c>
       <c r="Q31" s="8" t="s">
         <v>181</v>
@@ -4099,7 +4116,7 @@
       </c>
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="13" t="s">
         <v>183</v>
       </c>
       <c r="B32" s="7">
@@ -4110,13 +4127,13 @@
         <v>Thursday</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G32" s="2">
         <v>80</v>
@@ -4128,16 +4145,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="K32" t="s">
-        <v>62</v>
-      </c>
-      <c r="L32" t="s">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="M32" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="N32" t="s">
         <v>29</v>
@@ -4145,14 +4159,11 @@
       <c r="O32" t="s">
         <v>30</v>
       </c>
-      <c r="P32" t="s">
-        <v>64</v>
-      </c>
       <c r="Q32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -4166,27 +4177,27 @@
       </c>
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
-        <v>186</v>
+      <c r="A33" s="13" t="s">
+        <v>187</v>
       </c>
       <c r="B33" s="7">
-        <v>46353</v>
+        <v>46352</v>
       </c>
       <c r="C33" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Friday</v>
+        <v>Thursday</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>37</v>
+        <v>61</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>38</v>
+        <v>49</v>
+      </c>
+      <c r="G33" s="10">
+        <v>80</v>
       </c>
       <c r="H33" t="s">
         <v>25</v>
@@ -4195,50 +4206,117 @@
         <v>26</v>
       </c>
       <c r="J33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K33" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="L33" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="M33" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="N33" t="s">
         <v>29</v>
       </c>
       <c r="O33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q33" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q33" s="8" t="s">
         <v>188</v>
       </c>
       <c r="R33" t="s">
         <v>189</v>
       </c>
       <c r="S33" t="s">
+        <v>33</v>
+      </c>
+      <c r="T33" t="s">
+        <v>34</v>
+      </c>
+      <c r="U33" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46353</v>
+      </c>
+      <c r="C34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Friday</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="T33" t="s">
-        <v>38</v>
-      </c>
-      <c r="U33" t="b">
+      <c r="F34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H34" t="s">
+        <v>25</v>
+      </c>
+      <c r="I34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" t="s">
+        <v>40</v>
+      </c>
+      <c r="K34" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" t="s">
+        <v>41</v>
+      </c>
+      <c r="M34" t="s">
+        <v>42</v>
+      </c>
+      <c r="N34" t="s">
+        <v>29</v>
+      </c>
+      <c r="O34" t="s">
+        <v>29</v>
+      </c>
+      <c r="P34" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q34" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="R34" t="s">
+        <v>193</v>
+      </c>
+      <c r="S34" t="s">
+        <v>37</v>
+      </c>
+      <c r="T34" t="s">
+        <v>39</v>
+      </c>
+      <c r="U34" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="S2:S33" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="S2:S34" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Regional,Local"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T2:T33" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="T2:T34" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Website,External"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4257,10 +4335,10 @@
     <hyperlink ref="Q21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
     <hyperlink ref="Q23" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="Q25" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="Q27" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="Q28" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="Q30" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="Q33" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="Q28" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="Q29" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="Q31" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="Q34" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4357,9 +4435,9 @@
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B2" s="1">
+        <v>194</v>
+      </c>
+      <c r="B2" s="7">
         <v>46357</v>
       </c>
       <c r="C2" s="1" t="str">
@@ -4367,31 +4445,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G2" s="2">
         <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>
@@ -4402,11 +4480,11 @@
       <c r="O2" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="10" t="s">
-        <v>196</v>
+      <c r="Q2" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="R2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="S2" t="s">
         <v>33</v>
@@ -4420,10 +4498,10 @@
       </c>
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="B3" s="1">
+      <c r="A3" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" s="7">
         <v>46357</v>
       </c>
       <c r="C3" s="1" t="str">
@@ -4434,25 +4512,25 @@
         <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G3" s="2">
         <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="M3" t="s">
         <v>106</v>
@@ -4466,7 +4544,7 @@
       <c r="P3" t="s">
         <v>107</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="Q3" s="8" t="s">
         <v>108</v>
       </c>
       <c r="R3" t="s">
@@ -4485,9 +4563,9 @@
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B4" s="1">
+        <v>204</v>
+      </c>
+      <c r="B4" s="7">
         <v>46357</v>
       </c>
       <c r="C4" s="1" t="str">
@@ -4497,32 +4575,32 @@
       <c r="D4" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="12" t="s">
         <v>38</v>
       </c>
+      <c r="G4" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="H4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="M4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" t="s">
         <v>29</v>
@@ -4531,10 +4609,10 @@
         <v>29</v>
       </c>
       <c r="P4" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>203</v>
+        <v>206</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>207</v>
       </c>
       <c r="R4" t="s">
         <v>116</v>
@@ -4543,7 +4621,7 @@
         <v>37</v>
       </c>
       <c r="T4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U4" t="b">
         <f>FALSE()</f>
@@ -4552,9 +4630,9 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B5" s="1">
+        <v>208</v>
+      </c>
+      <c r="B5" s="7">
         <v>46358</v>
       </c>
       <c r="C5" s="1" t="str">
@@ -4562,34 +4640,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" s="2">
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L5" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="M5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N5" t="s">
         <v>29</v>
@@ -4597,11 +4675,11 @@
       <c r="O5" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="10" t="s">
-        <v>206</v>
+      <c r="Q5" s="8" t="s">
+        <v>210</v>
       </c>
       <c r="R5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -4615,10 +4693,10 @@
       </c>
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="A6" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="7">
         <v>46358</v>
       </c>
       <c r="C6" s="1" t="str">
@@ -4626,31 +4704,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2">
         <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J6" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K6" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N6" t="s">
         <v>30</v>
@@ -4658,7 +4736,7 @@
       <c r="O6" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="Q6" s="8" t="s">
         <v>145</v>
       </c>
       <c r="S6" t="s">
@@ -4674,9 +4752,9 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="B7" s="1">
+        <v>214</v>
+      </c>
+      <c r="B7" s="7">
         <v>46358</v>
       </c>
       <c r="C7" s="1" t="str">
@@ -4684,28 +4762,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G7" s="2">
         <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J7" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M7" t="s">
         <v>156</v>
@@ -4716,11 +4794,11 @@
       <c r="O7" t="s">
         <v>30</v>
       </c>
-      <c r="Q7" s="10" t="s">
-        <v>213</v>
+      <c r="Q7" s="8" t="s">
+        <v>217</v>
       </c>
       <c r="R7" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -4735,9 +4813,9 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B8" s="1">
+        <v>219</v>
+      </c>
+      <c r="B8" s="7">
         <v>46360</v>
       </c>
       <c r="C8" s="1" t="str">
@@ -4745,34 +4823,34 @@
         <v>Friday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>130</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2">
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J8" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K8" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="L8" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="M8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N8" t="s">
         <v>29</v>
@@ -4783,11 +4861,11 @@
       <c r="P8" t="s">
         <v>125</v>
       </c>
-      <c r="Q8" s="10" t="s">
-        <v>217</v>
+      <c r="Q8" s="8" t="s">
+        <v>221</v>
       </c>
       <c r="R8" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -4802,9 +4880,9 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B9" s="1">
+        <v>223</v>
+      </c>
+      <c r="B9" s="7">
         <v>46363</v>
       </c>
       <c r="C9" s="1" t="str">
@@ -4812,34 +4890,34 @@
         <v>Monday</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9" s="2">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J9" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="L9" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
@@ -4847,11 +4925,11 @@
       <c r="O9" t="s">
         <v>30</v>
       </c>
-      <c r="Q9" s="10" t="s">
-        <v>222</v>
+      <c r="Q9" s="8" t="s">
+        <v>226</v>
       </c>
       <c r="R9" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -4866,9 +4944,9 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="B10" s="1">
+        <v>228</v>
+      </c>
+      <c r="B10" s="7">
         <v>46364</v>
       </c>
       <c r="C10" s="1" t="str">
@@ -4876,31 +4954,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2">
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
@@ -4909,13 +4987,13 @@
         <v>30</v>
       </c>
       <c r="P10" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q10" s="10" t="s">
-        <v>228</v>
+        <v>231</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>232</v>
       </c>
       <c r="R10" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -4930,9 +5008,9 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B11" s="1">
+        <v>234</v>
+      </c>
+      <c r="B11" s="7">
         <v>46365</v>
       </c>
       <c r="C11" s="1" t="str">
@@ -4940,34 +5018,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E11" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>38</v>
+        <v>236</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H11" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J11" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K11" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L11" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="M11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -4976,19 +5054,19 @@
         <v>29</v>
       </c>
       <c r="P11" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q11" s="10" t="s">
-        <v>235</v>
+        <v>238</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>239</v>
       </c>
       <c r="R11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S11" t="s">
         <v>37</v>
       </c>
       <c r="T11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U11" t="b">
         <f>FALSE()</f>
@@ -4997,9 +5075,9 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="B12" s="1">
+        <v>240</v>
+      </c>
+      <c r="B12" s="7">
         <v>46366</v>
       </c>
       <c r="C12" s="1" t="str">
@@ -5007,31 +5085,31 @@
         <v>Thursday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>118</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G12" s="2">
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J12" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K12" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="L12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="M12" t="s">
         <v>118</v>
@@ -5043,13 +5121,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q12" s="10" t="s">
-        <v>240</v>
+        <v>243</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>244</v>
       </c>
       <c r="R12" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -5064,9 +5142,9 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B13" s="1">
+        <v>246</v>
+      </c>
+      <c r="B13" s="7">
         <v>46394</v>
       </c>
       <c r="C13" s="1" t="str">
@@ -5074,28 +5152,28 @@
         <v>Thursday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" s="2">
         <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I13" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J13" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K13" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="M13" t="s">
         <v>106</v>
@@ -5109,11 +5187,11 @@
       <c r="P13" t="s">
         <v>136</v>
       </c>
-      <c r="Q13" s="10" t="s">
-        <v>243</v>
+      <c r="Q13" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="R13" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -5128,9 +5206,9 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="B14" s="1">
+        <v>249</v>
+      </c>
+      <c r="B14" s="7">
         <v>46398</v>
       </c>
       <c r="C14" s="1" t="str">
@@ -5138,31 +5216,31 @@
         <v>Monday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G14" s="2">
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J14" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M14" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
@@ -5171,13 +5249,13 @@
         <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q14" s="10" t="s">
-        <v>248</v>
+        <v>251</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>252</v>
       </c>
       <c r="R14" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -5192,9 +5270,9 @@
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B15" s="1">
+        <v>254</v>
+      </c>
+      <c r="B15" s="7">
         <v>46400</v>
       </c>
       <c r="C15" s="1" t="str">
@@ -5202,28 +5280,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" s="2">
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I15" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J15" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K15" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M15" t="s">
         <v>156</v>
@@ -5235,13 +5313,13 @@
         <v>30</v>
       </c>
       <c r="P15" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>253</v>
+        <v>256</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="R15" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -5256,9 +5334,9 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B16" s="1">
+        <v>259</v>
+      </c>
+      <c r="B16" s="7">
         <v>46402</v>
       </c>
       <c r="C16" s="1" t="str">
@@ -5266,28 +5344,28 @@
         <v>Friday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>118</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I16" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J16" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K16" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="M16" t="s">
         <v>118</v>
@@ -5299,13 +5377,13 @@
         <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q16" s="10" t="s">
-        <v>258</v>
+        <v>261</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>262</v>
       </c>
       <c r="R16" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -5320,9 +5398,9 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="B17" s="1">
+        <v>264</v>
+      </c>
+      <c r="B17" s="7">
         <v>46405</v>
       </c>
       <c r="C17" s="1" t="str">
@@ -5330,31 +5408,31 @@
         <v>Monday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G17" s="2">
         <v>6</v>
       </c>
       <c r="H17" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I17" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J17" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K17" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
@@ -5362,11 +5440,11 @@
       <c r="O17" t="s">
         <v>30</v>
       </c>
-      <c r="Q17" s="10" t="s">
-        <v>264</v>
+      <c r="Q17" s="8" t="s">
+        <v>268</v>
       </c>
       <c r="R17" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -5381,41 +5459,41 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B18" s="7">
+        <v>46407</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B18" s="1">
-        <v>46407</v>
-      </c>
-      <c r="C18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Wednesday</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="G18" s="2">
         <v>6</v>
       </c>
       <c r="H18" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I18" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J18" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K18" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N18" t="s">
         <v>29</v>
@@ -5423,11 +5501,11 @@
       <c r="O18" t="s">
         <v>30</v>
       </c>
-      <c r="Q18" s="10" t="s">
-        <v>267</v>
+      <c r="Q18" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="R18" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -5442,9 +5520,9 @@
     </row>
     <row r="19" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="B19" s="1">
+        <v>272</v>
+      </c>
+      <c r="B19" s="7">
         <v>46407</v>
       </c>
       <c r="C19" s="1" t="str">
@@ -5452,28 +5530,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G19" s="2">
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I19" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J19" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K19" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s">
         <v>106</v>
@@ -5485,13 +5563,13 @@
         <v>30</v>
       </c>
       <c r="P19" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q19" s="10" t="s">
-        <v>270</v>
+        <v>273</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>274</v>
       </c>
       <c r="R19" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -5506,9 +5584,9 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="B20" s="1">
+        <v>276</v>
+      </c>
+      <c r="B20" s="7">
         <v>46408</v>
       </c>
       <c r="C20" s="1" t="str">
@@ -5516,31 +5594,31 @@
         <v>Thursday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G20" s="2">
         <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I20" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J20" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K20" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="L20" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="M20" t="s">
         <v>156</v>
@@ -5551,11 +5629,11 @@
       <c r="O20" t="s">
         <v>30</v>
       </c>
-      <c r="Q20" s="10" t="s">
-        <v>274</v>
+      <c r="Q20" s="8" t="s">
+        <v>278</v>
       </c>
       <c r="R20" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -5570,9 +5648,9 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="B21" s="1">
+        <v>280</v>
+      </c>
+      <c r="B21" s="7">
         <v>46408</v>
       </c>
       <c r="C21" s="1" t="str">
@@ -5583,28 +5661,28 @@
         <v>111</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" s="2">
         <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I21" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J21" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K21" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
@@ -5613,13 +5691,13 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q21" s="10" t="s">
-        <v>278</v>
+        <v>281</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>282</v>
       </c>
       <c r="R21" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -5634,9 +5712,9 @@
     </row>
     <row r="22" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B22" s="1">
+        <v>284</v>
+      </c>
+      <c r="B22" s="7">
         <v>46414</v>
       </c>
       <c r="C22" s="1" t="str">
@@ -5644,31 +5722,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G22" s="2">
         <v>80</v>
       </c>
       <c r="H22" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I22" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J22" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K22" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M22" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="N22" t="s">
         <v>30</v>
@@ -5677,13 +5755,13 @@
         <v>30</v>
       </c>
       <c r="P22" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q22" s="10" t="s">
-        <v>283</v>
+        <v>286</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>287</v>
       </c>
       <c r="R22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -5697,10 +5775,10 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="B23" s="1">
+      <c r="A23" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="B23" s="7">
         <v>46416</v>
       </c>
       <c r="C23" s="1" t="str">
@@ -5708,10 +5786,10 @@
         <v>Friday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>24</v>
@@ -5720,19 +5798,19 @@
         <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I23" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J23" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K23" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N23" t="s">
         <v>29</v>
@@ -5740,11 +5818,11 @@
       <c r="O23" t="s">
         <v>30</v>
       </c>
-      <c r="Q23" s="10" t="s">
-        <v>287</v>
+      <c r="Q23" s="8" t="s">
+        <v>291</v>
       </c>
       <c r="R23" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -5759,9 +5837,9 @@
     </row>
     <row r="24" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="B24" s="1">
+        <v>293</v>
+      </c>
+      <c r="B24" s="7">
         <v>46420</v>
       </c>
       <c r="C24" s="1" t="str">
@@ -5772,31 +5850,31 @@
         <v>124</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2">
         <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I24" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J24" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K24" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="L24" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
@@ -5807,11 +5885,11 @@
       <c r="P24" t="s">
         <v>125</v>
       </c>
-      <c r="Q24" s="10" t="s">
-        <v>290</v>
+      <c r="Q24" s="8" t="s">
+        <v>294</v>
       </c>
       <c r="R24" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -5826,9 +5904,9 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="B25" s="1">
+        <v>296</v>
+      </c>
+      <c r="B25" s="7">
         <v>46420</v>
       </c>
       <c r="C25" s="1" t="str">
@@ -5836,31 +5914,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G25" s="2">
         <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I25" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J25" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K25" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N25" t="s">
         <v>29</v>
@@ -5869,13 +5947,13 @@
         <v>30</v>
       </c>
       <c r="P25" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q25" s="10" t="s">
-        <v>295</v>
+        <v>298</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>299</v>
       </c>
       <c r="R25" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -5890,9 +5968,9 @@
     </row>
     <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="B26" s="1">
+        <v>301</v>
+      </c>
+      <c r="B26" s="7">
         <v>46420</v>
       </c>
       <c r="C26" s="1" t="str">
@@ -5900,28 +5978,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G26" s="2">
         <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I26" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J26" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="M26" t="s">
         <v>23</v>
@@ -5933,13 +6011,13 @@
         <v>30</v>
       </c>
       <c r="P26" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q26" s="10" t="s">
-        <v>299</v>
+        <v>302</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>303</v>
       </c>
       <c r="R26" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -5954,9 +6032,9 @@
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="B27" s="1">
+        <v>305</v>
+      </c>
+      <c r="B27" s="7">
         <v>46421</v>
       </c>
       <c r="C27" s="1" t="str">
@@ -5964,28 +6042,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G27" s="2">
         <v>12</v>
       </c>
       <c r="H27" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I27" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J27" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K27" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M27" t="s">
         <v>156</v>
@@ -5996,11 +6074,11 @@
       <c r="O27" t="s">
         <v>30</v>
       </c>
-      <c r="Q27" s="10" t="s">
-        <v>302</v>
+      <c r="Q27" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="R27" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -6015,9 +6093,9 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="B28" s="1">
+        <v>307</v>
+      </c>
+      <c r="B28" s="7">
         <v>46421</v>
       </c>
       <c r="C28" s="1" t="str">
@@ -6025,34 +6103,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G28" s="2">
         <v>80</v>
       </c>
       <c r="H28" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I28" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J28" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K28" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L28" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="M28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N28" t="s">
         <v>29</v>
@@ -6060,11 +6138,11 @@
       <c r="O28" t="s">
         <v>30</v>
       </c>
-      <c r="Q28" s="10" t="s">
-        <v>304</v>
+      <c r="Q28" s="8" t="s">
+        <v>308</v>
       </c>
       <c r="R28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S28" t="s">
         <v>33</v>
@@ -6079,9 +6157,9 @@
     </row>
     <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="B29" s="1">
+        <v>309</v>
+      </c>
+      <c r="B29" s="7">
         <v>46422</v>
       </c>
       <c r="C29" s="1" t="str">
@@ -6089,31 +6167,31 @@
         <v>Thursday</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G29" s="2">
         <v>6</v>
       </c>
       <c r="H29" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I29" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J29" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K29" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N29" t="s">
         <v>29</v>
@@ -6122,13 +6200,13 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q29" s="10" t="s">
-        <v>306</v>
+        <v>298</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>310</v>
       </c>
       <c r="R29" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="S29" t="s">
         <v>33</v>
@@ -6143,9 +6221,9 @@
     </row>
     <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B30" s="1">
+        <v>311</v>
+      </c>
+      <c r="B30" s="7">
         <v>46422</v>
       </c>
       <c r="C30" s="1" t="str">
@@ -6156,28 +6234,28 @@
         <v>111</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G30" s="2">
         <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I30" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J30" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K30" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N30" t="s">
         <v>29</v>
@@ -6186,13 +6264,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q30" s="10" t="s">
-        <v>308</v>
+        <v>281</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>312</v>
       </c>
       <c r="R30" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -6206,10 +6284,10 @@
       </c>
     </row>
     <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="B31" s="1">
+      <c r="A31" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B31" s="7">
         <v>46423</v>
       </c>
       <c r="C31" s="1" t="str">
@@ -6217,10 +6295,10 @@
         <v>Friday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>24</v>
@@ -6229,19 +6307,19 @@
         <v>24</v>
       </c>
       <c r="H31" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I31" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J31" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K31" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="M31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N31" t="s">
         <v>29</v>
@@ -6249,11 +6327,11 @@
       <c r="O31" t="s">
         <v>30</v>
       </c>
-      <c r="Q31" s="10" t="s">
-        <v>311</v>
+      <c r="Q31" s="8" t="s">
+        <v>315</v>
       </c>
       <c r="R31" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -6268,9 +6346,9 @@
     </row>
     <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="B32" s="1">
+        <v>316</v>
+      </c>
+      <c r="B32" s="7">
         <v>46426</v>
       </c>
       <c r="C32" s="1" t="str">
@@ -6278,34 +6356,34 @@
         <v>Monday</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G32" s="2">
         <v>80</v>
       </c>
       <c r="H32" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I32" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J32" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K32" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="L32" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N32" t="s">
         <v>29</v>
@@ -6313,11 +6391,11 @@
       <c r="O32" t="s">
         <v>30</v>
       </c>
-      <c r="Q32" s="10" t="s">
-        <v>313</v>
+      <c r="Q32" s="8" t="s">
+        <v>317</v>
       </c>
       <c r="R32" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -6332,9 +6410,9 @@
     </row>
     <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="B33" s="1">
+        <v>319</v>
+      </c>
+      <c r="B33" s="7">
         <v>46427</v>
       </c>
       <c r="C33" s="1" t="str">
@@ -6342,28 +6420,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2">
         <v>80</v>
       </c>
       <c r="H33" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I33" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J33" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K33" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="M33" t="s">
         <v>106</v>
@@ -6375,13 +6453,13 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q33" s="10" t="s">
-        <v>316</v>
+        <v>273</v>
+      </c>
+      <c r="Q33" s="8" t="s">
+        <v>320</v>
       </c>
       <c r="R33" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="S33" t="s">
         <v>33</v>
@@ -6396,9 +6474,9 @@
     </row>
     <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B34" s="1">
+        <v>322</v>
+      </c>
+      <c r="B34" s="7">
         <v>46427</v>
       </c>
       <c r="C34" s="1" t="str">
@@ -6408,32 +6486,32 @@
       <c r="D34" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>38</v>
+        <v>323</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H34" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I34" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J34" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K34" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L34" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="M34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N34" t="s">
         <v>29</v>
@@ -6442,10 +6520,10 @@
         <v>29</v>
       </c>
       <c r="P34" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q34" s="10" t="s">
-        <v>321</v>
+        <v>324</v>
+      </c>
+      <c r="Q34" s="8" t="s">
+        <v>325</v>
       </c>
       <c r="R34" t="s">
         <v>116</v>
@@ -6454,7 +6532,7 @@
         <v>37</v>
       </c>
       <c r="T34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U34" t="b">
         <f>FALSE()</f>
@@ -6462,10 +6540,10 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="B35" s="1">
+      <c r="A35" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="B35" s="7">
         <v>46428</v>
       </c>
       <c r="C35" s="1" t="str">
@@ -6473,31 +6551,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G35" s="2">
         <v>80</v>
       </c>
       <c r="H35" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I35" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J35" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K35" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M35" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="N35" t="s">
         <v>30</v>
@@ -6506,10 +6584,10 @@
         <v>29</v>
       </c>
       <c r="P35" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q35" s="10" t="s">
-        <v>283</v>
+        <v>286</v>
+      </c>
+      <c r="Q35" s="8" t="s">
+        <v>287</v>
       </c>
       <c r="S35" t="s">
         <v>33</v>
@@ -6523,10 +6601,10 @@
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="B36" s="1">
+      <c r="A36" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="B36" s="7">
         <v>46428</v>
       </c>
       <c r="C36" s="1" t="str">
@@ -6534,28 +6612,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G36" s="2">
         <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I36" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J36" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K36" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M36" t="s">
         <v>156</v>
@@ -6567,10 +6645,10 @@
         <v>29</v>
       </c>
       <c r="P36" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q36" s="10" t="s">
-        <v>253</v>
+        <v>256</v>
+      </c>
+      <c r="Q36" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="S36" t="s">
         <v>33</v>
@@ -6584,10 +6662,10 @@
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="B37" s="1">
+      <c r="A37" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="B37" s="7">
         <v>46430</v>
       </c>
       <c r="C37" s="1" t="str">
@@ -6595,10 +6673,10 @@
         <v>Friday</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>24</v>
@@ -6607,19 +6685,19 @@
         <v>24</v>
       </c>
       <c r="H37" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I37" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J37" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K37" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="M37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N37" t="s">
         <v>29</v>
@@ -6627,11 +6705,11 @@
       <c r="O37" t="s">
         <v>30</v>
       </c>
-      <c r="Q37" s="10" t="s">
-        <v>325</v>
+      <c r="Q37" s="8" t="s">
+        <v>329</v>
       </c>
       <c r="R37" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -6646,9 +6724,9 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B38" s="1">
+        <v>330</v>
+      </c>
+      <c r="B38" s="7">
         <v>46441</v>
       </c>
       <c r="C38" s="1" t="str">
@@ -6656,31 +6734,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>118</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G38" s="2">
         <v>80</v>
       </c>
       <c r="H38" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I38" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J38" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K38" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="L38" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="M38" t="s">
         <v>118</v>
@@ -6692,13 +6770,13 @@
         <v>30</v>
       </c>
       <c r="P38" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q38" s="10" t="s">
-        <v>327</v>
+        <v>243</v>
+      </c>
+      <c r="Q38" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="R38" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="S38" t="s">
         <v>33</v>
@@ -6713,9 +6791,9 @@
     </row>
     <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B39" s="1">
+        <v>332</v>
+      </c>
+      <c r="B39" s="7">
         <v>46441</v>
       </c>
       <c r="C39" s="1" t="str">
@@ -6723,34 +6801,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E39" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>38</v>
+        <v>333</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H39" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I39" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J39" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K39" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L39" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="M39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N39" t="s">
         <v>29</v>
@@ -6759,19 +6837,19 @@
         <v>29</v>
       </c>
       <c r="P39" t="s">
-        <v>330</v>
-      </c>
-      <c r="Q39" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
+      </c>
+      <c r="Q39" s="11" t="s">
+        <v>335</v>
       </c>
       <c r="R39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S39" t="s">
         <v>37</v>
       </c>
       <c r="T39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U39" t="b">
         <f>FALSE()</f>
@@ -6780,9 +6858,9 @@
     </row>
     <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="B40" s="1">
+        <v>336</v>
+      </c>
+      <c r="B40" s="7">
         <v>46444</v>
       </c>
       <c r="C40" s="1" t="str">
@@ -6790,31 +6868,31 @@
         <v>Friday</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G40" s="2">
         <v>100</v>
       </c>
       <c r="H40" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I40" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J40" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K40" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L40" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -6825,11 +6903,11 @@
       <c r="O40" t="s">
         <v>30</v>
       </c>
-      <c r="Q40" s="10" t="s">
-        <v>334</v>
+      <c r="Q40" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="R40" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="S40" t="s">
         <v>33</v>
@@ -6877,7 +6955,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.85546875" customWidth="1"/>
@@ -6962,44 +7040,44 @@
     </row>
     <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="B2" s="1">
+        <v>340</v>
+      </c>
+      <c r="B2" s="7">
         <v>46447</v>
       </c>
       <c r="C2" s="1" t="str">
-        <f t="shared" ref="C2:C37" si="0">IF(B2="","",TEXT(B2,"dddd"))</f>
+        <f t="shared" ref="C2:C38" si="0">IF(B2="","",TEXT(B2,"dddd"))</f>
         <v>Monday</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>38</v>
+        <v>341</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="L2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="M2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -7008,10 +7086,10 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>344</v>
+        <v>347</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="R2" t="s">
         <v>116</v>
@@ -7020,7 +7098,7 @@
         <v>37</v>
       </c>
       <c r="T2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U2" t="b">
         <f>FALSE()</f>
@@ -7029,9 +7107,9 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="B3" s="1">
+        <v>349</v>
+      </c>
+      <c r="B3" s="7">
         <v>46448</v>
       </c>
       <c r="C3" s="1" t="str">
@@ -7039,31 +7117,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G3" s="2">
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="K3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="M3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N3" t="s">
         <v>29</v>
@@ -7071,11 +7149,11 @@
       <c r="O3" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="10" t="s">
-        <v>348</v>
+      <c r="Q3" s="8" t="s">
+        <v>352</v>
       </c>
       <c r="R3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -7090,9 +7168,9 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="B4" s="1">
+        <v>354</v>
+      </c>
+      <c r="B4" s="7">
         <v>46449</v>
       </c>
       <c r="C4" s="1" t="str">
@@ -7103,28 +7181,28 @@
         <v>111</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" s="2">
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N4" t="s">
         <v>29</v>
@@ -7133,13 +7211,13 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>353</v>
+        <v>281</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>357</v>
       </c>
       <c r="R4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -7154,9 +7232,9 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="B5" s="1">
+        <v>359</v>
+      </c>
+      <c r="B5" s="7">
         <v>46450</v>
       </c>
       <c r="C5" s="1" t="str">
@@ -7164,34 +7242,34 @@
         <v>Thursday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" s="2">
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J5" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="L5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="M5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N5" t="s">
         <v>29</v>
@@ -7200,13 +7278,13 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q5" s="10" t="s">
-        <v>358</v>
+        <v>176</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>362</v>
       </c>
       <c r="R5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -7221,9 +7299,9 @@
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="B6" s="1">
+        <v>363</v>
+      </c>
+      <c r="B6" s="7">
         <v>46455</v>
       </c>
       <c r="C6" s="1" t="str">
@@ -7231,28 +7309,28 @@
         <v>Tuesday</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>118</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2">
         <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I6" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J6" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K6" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="M6" t="s">
         <v>118</v>
@@ -7264,13 +7342,13 @@
         <v>30</v>
       </c>
       <c r="P6" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q6" s="10" t="s">
-        <v>361</v>
+        <v>167</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>365</v>
       </c>
       <c r="R6" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -7285,9 +7363,9 @@
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="B7" s="1">
+        <v>367</v>
+      </c>
+      <c r="B7" s="7">
         <v>46455</v>
       </c>
       <c r="C7" s="1" t="str">
@@ -7295,34 +7373,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="E7" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G7" s="12" t="s">
         <v>38</v>
       </c>
+      <c r="G7" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="H7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I7" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J7" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K7" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="L7" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="M7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
@@ -7331,19 +7409,19 @@
         <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="R7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S7" t="s">
         <v>37</v>
       </c>
       <c r="T7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U7" t="b">
         <f>FALSE()</f>
@@ -7351,10 +7429,10 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="B8" s="1">
+      <c r="A8" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B8" s="7">
         <v>46456</v>
       </c>
       <c r="C8" s="1" t="str">
@@ -7362,28 +7440,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2">
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I8" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J8" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K8" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M8" t="s">
         <v>156</v>
@@ -7395,10 +7473,10 @@
         <v>29</v>
       </c>
       <c r="P8" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>253</v>
+        <v>256</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -7413,9 +7491,9 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="B9" s="1">
+        <v>373</v>
+      </c>
+      <c r="B9" s="7">
         <v>46456</v>
       </c>
       <c r="C9" s="1" t="str">
@@ -7423,28 +7501,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9" s="2">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I9" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J9" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K9" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="M9" t="s">
         <v>106</v>
@@ -7456,13 +7534,13 @@
         <v>30</v>
       </c>
       <c r="P9" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q9" s="10" t="s">
-        <v>370</v>
+        <v>273</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>374</v>
       </c>
       <c r="R9" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -7477,9 +7555,9 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B10" s="1">
+        <v>183</v>
+      </c>
+      <c r="B10" s="7">
         <v>46457</v>
       </c>
       <c r="C10" s="1" t="str">
@@ -7487,31 +7565,31 @@
         <v>Thursday</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2">
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I10" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J10" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="M10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
@@ -7519,11 +7597,11 @@
       <c r="O10" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="10" t="s">
-        <v>373</v>
+      <c r="Q10" s="8" t="s">
+        <v>377</v>
       </c>
       <c r="R10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -7538,9 +7616,9 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="B11" s="1">
+        <v>378</v>
+      </c>
+      <c r="B11" s="7">
         <v>46462</v>
       </c>
       <c r="C11" s="1" t="str">
@@ -7548,31 +7626,31 @@
         <v>Tuesday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G11" s="2">
         <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I11" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J11" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K11" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="L11" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="M11" t="s">
         <v>156</v>
@@ -7583,11 +7661,11 @@
       <c r="O11" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="10" t="s">
-        <v>376</v>
+      <c r="Q11" s="8" t="s">
+        <v>380</v>
       </c>
       <c r="R11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -7602,9 +7680,9 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="B12" s="1">
+        <v>381</v>
+      </c>
+      <c r="B12" s="7">
         <v>46462</v>
       </c>
       <c r="C12" s="1" t="str">
@@ -7615,28 +7693,28 @@
         <v>111</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G12" s="2">
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I12" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J12" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K12" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="M12" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
@@ -7645,13 +7723,13 @@
         <v>30</v>
       </c>
       <c r="P12" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q12" s="10" t="s">
-        <v>379</v>
+        <v>286</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>383</v>
       </c>
       <c r="R12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -7666,9 +7744,9 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="B13" s="1">
+        <v>385</v>
+      </c>
+      <c r="B13" s="7">
         <v>46463</v>
       </c>
       <c r="C13" s="1" t="str">
@@ -7676,34 +7754,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" s="2">
         <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I13" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K13" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="L13" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="M13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
@@ -7712,13 +7790,13 @@
         <v>30</v>
       </c>
       <c r="P13" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q13" s="10" t="s">
-        <v>383</v>
+        <v>65</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>387</v>
       </c>
       <c r="R13" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="S13" t="s">
         <v>33</v>
@@ -7733,9 +7811,9 @@
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="B14" s="1">
+        <v>389</v>
+      </c>
+      <c r="B14" s="7">
         <v>46464</v>
       </c>
       <c r="C14" s="1" t="str">
@@ -7743,34 +7821,34 @@
         <v>Thursday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G14" s="2">
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I14" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J14" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K14" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="L14" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="M14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
@@ -7778,11 +7856,11 @@
       <c r="O14" t="s">
         <v>30</v>
       </c>
-      <c r="Q14" s="10" t="s">
-        <v>388</v>
+      <c r="Q14" s="8" t="s">
+        <v>392</v>
       </c>
       <c r="R14" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -7796,63 +7874,63 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="B15" s="1">
-        <v>46468</v>
+      <c r="A15" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="B15" s="7">
+        <v>46464</v>
       </c>
       <c r="C15" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Monday</v>
+        <v>Thursday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>46</v>
+        <v>162</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="2">
-        <v>80</v>
+        <v>37</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H15" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I15" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J15" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K15" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="L15" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="M15" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="N15" t="s">
         <v>29</v>
       </c>
       <c r="O15" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>391</v>
+        <v>29</v>
+      </c>
+      <c r="P15" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>523</v>
       </c>
       <c r="R15" t="s">
-        <v>392</v>
+        <v>164</v>
       </c>
       <c r="S15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T15" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="U15" t="b">
         <f>FALSE()</f>
@@ -7861,56 +7939,56 @@
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="B16" s="1">
-        <v>46469</v>
+        <v>395</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46468</v>
       </c>
       <c r="C16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Tuesday</v>
+        <v>Monday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>394</v>
+        <v>47</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>395</v>
+        <v>49</v>
       </c>
       <c r="G16" s="2">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I16" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J16" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K16" t="s">
+        <v>360</v>
+      </c>
+      <c r="L16" t="s">
+        <v>361</v>
+      </c>
+      <c r="M16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N16" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q16" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="M16" t="s">
-        <v>130</v>
-      </c>
-      <c r="N16" t="s">
-        <v>29</v>
-      </c>
-      <c r="O16" t="s">
-        <v>30</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="R16" t="s">
         <v>397</v>
-      </c>
-      <c r="Q16" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="R16" t="s">
-        <v>399</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -7925,44 +8003,41 @@
     </row>
     <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46469</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B17" s="1">
-        <v>46470</v>
-      </c>
-      <c r="C17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Wednesday</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G17" s="2">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I17" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J17" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="K17" t="s">
-        <v>341</v>
-      </c>
-      <c r="L17" t="s">
         <v>401</v>
       </c>
       <c r="M17" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
@@ -7970,11 +8045,14 @@
       <c r="O17" t="s">
         <v>30</v>
       </c>
-      <c r="Q17" s="10" t="s">
+      <c r="P17" t="s">
         <v>402</v>
       </c>
+      <c r="Q17" s="8" t="s">
+        <v>403</v>
+      </c>
       <c r="R17" t="s">
-        <v>58</v>
+        <v>404</v>
       </c>
       <c r="S17" t="s">
         <v>33</v>
@@ -7989,44 +8067,44 @@
     </row>
     <row r="18" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="B18" s="1">
-        <v>46486</v>
+        <v>405</v>
+      </c>
+      <c r="B18" s="7">
+        <v>46470</v>
       </c>
       <c r="C18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Friday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>216</v>
+        <v>55</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G18" s="2">
         <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I18" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J18" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K18" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="L18" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
       <c r="M18" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="N18" t="s">
         <v>29</v>
@@ -8034,14 +8112,11 @@
       <c r="O18" t="s">
         <v>30</v>
       </c>
-      <c r="P18" t="s">
-        <v>404</v>
-      </c>
-      <c r="Q18" s="10" t="s">
-        <v>405</v>
+      <c r="Q18" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="R18" t="s">
-        <v>406</v>
+        <v>59</v>
       </c>
       <c r="S18" t="s">
         <v>33</v>
@@ -8056,56 +8131,59 @@
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="B19" s="1">
-        <v>46492</v>
+        <v>408</v>
+      </c>
+      <c r="B19" s="7">
+        <v>46486</v>
       </c>
       <c r="C19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Friday</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>88</v>
+        <v>220</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G19" s="2">
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I19" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J19" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="K19" t="s">
-        <v>356</v>
+        <v>360</v>
+      </c>
+      <c r="L19" t="s">
+        <v>346</v>
       </c>
       <c r="M19" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="N19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O19" t="s">
         <v>30</v>
       </c>
       <c r="P19" t="s">
-        <v>408</v>
-      </c>
-      <c r="Q19" s="10" t="s">
         <v>409</v>
       </c>
+      <c r="Q19" s="8" t="s">
+        <v>410</v>
+      </c>
       <c r="R19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="S19" t="s">
         <v>33</v>
@@ -8120,56 +8198,56 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="B20" s="1">
-        <v>46496</v>
+        <v>412</v>
+      </c>
+      <c r="B20" s="7">
+        <v>46492</v>
       </c>
       <c r="C20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Monday</v>
+        <v>Thursday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="2">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s">
+        <v>342</v>
+      </c>
+      <c r="I20" t="s">
+        <v>343</v>
+      </c>
+      <c r="J20" t="s">
+        <v>355</v>
+      </c>
+      <c r="K20" t="s">
+        <v>360</v>
+      </c>
+      <c r="M20" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="2">
-        <v>100</v>
-      </c>
-      <c r="H20" t="s">
-        <v>338</v>
-      </c>
-      <c r="I20" t="s">
-        <v>339</v>
-      </c>
-      <c r="J20" t="s">
-        <v>340</v>
-      </c>
-      <c r="K20" t="s">
-        <v>341</v>
-      </c>
-      <c r="L20" t="s">
-        <v>412</v>
-      </c>
-      <c r="M20" t="s">
-        <v>23</v>
-      </c>
       <c r="N20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O20" t="s">
         <v>30</v>
       </c>
-      <c r="Q20" s="10" t="s">
+      <c r="P20" t="s">
         <v>413</v>
       </c>
+      <c r="Q20" s="8" t="s">
+        <v>414</v>
+      </c>
       <c r="R20" t="s">
-        <v>335</v>
+        <v>415</v>
       </c>
       <c r="S20" t="s">
         <v>33</v>
@@ -8184,56 +8262,56 @@
     </row>
     <row r="21" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="B21" s="1">
-        <v>46500</v>
+        <v>416</v>
+      </c>
+      <c r="B21" s="7">
+        <v>46496</v>
       </c>
       <c r="C21" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Friday</v>
+        <v>Monday</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>415</v>
+        <v>129</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="G21" s="2">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="H21" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I21" t="s">
+        <v>343</v>
+      </c>
+      <c r="J21" t="s">
+        <v>344</v>
+      </c>
+      <c r="K21" t="s">
+        <v>345</v>
+      </c>
+      <c r="L21" t="s">
+        <v>417</v>
+      </c>
+      <c r="M21" t="s">
+        <v>23</v>
+      </c>
+      <c r="N21" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="R21" t="s">
         <v>339</v>
-      </c>
-      <c r="J21" t="s">
-        <v>346</v>
-      </c>
-      <c r="K21" t="s">
-        <v>360</v>
-      </c>
-      <c r="M21" t="s">
-        <v>118</v>
-      </c>
-      <c r="N21" t="s">
-        <v>29</v>
-      </c>
-      <c r="O21" t="s">
-        <v>30</v>
-      </c>
-      <c r="P21" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q21" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="R21" t="s">
-        <v>418</v>
       </c>
       <c r="S21" t="s">
         <v>33</v>
@@ -8250,39 +8328,39 @@
       <c r="A22" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="B22" s="1">
-        <v>46505</v>
+      <c r="B22" s="7">
+        <v>46500</v>
       </c>
       <c r="C22" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Friday</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>261</v>
+        <v>420</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G22" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I22" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J22" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="K22" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="M22" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="N22" t="s">
         <v>29</v>
@@ -8290,11 +8368,14 @@
       <c r="O22" t="s">
         <v>30</v>
       </c>
-      <c r="Q22" s="10" t="s">
-        <v>420</v>
+      <c r="P22" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>422</v>
       </c>
       <c r="R22" t="s">
-        <v>349</v>
+        <v>423</v>
       </c>
       <c r="S22" t="s">
         <v>33</v>
@@ -8308,57 +8389,54 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="B23" s="1">
-        <v>46506</v>
+      <c r="A23" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46505</v>
       </c>
       <c r="C23" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>88</v>
+        <v>265</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G23" s="2">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="H23" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I23" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J23" t="s">
+        <v>350</v>
+      </c>
+      <c r="K23" t="s">
         <v>351</v>
       </c>
-      <c r="K23" t="s">
-        <v>356</v>
-      </c>
       <c r="M23" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="N23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O23" t="s">
-        <v>29</v>
-      </c>
-      <c r="P23" t="s">
-        <v>408</v>
-      </c>
-      <c r="Q23" s="10" t="s">
-        <v>409</v>
+        <v>30</v>
+      </c>
+      <c r="Q23" s="8" t="s">
+        <v>425</v>
       </c>
       <c r="R23" t="s">
-        <v>410</v>
+        <v>353</v>
       </c>
       <c r="S23" t="s">
         <v>33</v>
@@ -8372,57 +8450,57 @@
       </c>
     </row>
     <row r="24" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B24" s="1">
-        <v>46507</v>
+      <c r="A24" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46506</v>
       </c>
       <c r="C24" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Friday</v>
+        <v>Thursday</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2">
         <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I24" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J24" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K24" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="M24" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="N24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P24" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q24" s="10" t="s">
-        <v>422</v>
+        <v>413</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>414</v>
       </c>
       <c r="R24" t="s">
-        <v>138</v>
+        <v>415</v>
       </c>
       <c r="S24" t="s">
         <v>33</v>
@@ -8437,44 +8515,41 @@
     </row>
     <row r="25" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>423</v>
-      </c>
-      <c r="B25" s="1">
-        <v>46512</v>
+        <v>134</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46507</v>
       </c>
       <c r="C25" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Friday</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>424</v>
+        <v>135</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" s="2">
         <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I25" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J25" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="K25" t="s">
-        <v>352</v>
-      </c>
-      <c r="L25" t="s">
-        <v>387</v>
+        <v>345</v>
       </c>
       <c r="M25" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="N25" t="s">
         <v>29</v>
@@ -8482,11 +8557,14 @@
       <c r="O25" t="s">
         <v>30</v>
       </c>
-      <c r="Q25" s="10" t="s">
-        <v>425</v>
+      <c r="P25" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>427</v>
       </c>
       <c r="R25" t="s">
-        <v>389</v>
+        <v>138</v>
       </c>
       <c r="S25" t="s">
         <v>33</v>
@@ -8501,9 +8579,9 @@
     </row>
     <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="B26" s="1">
+        <v>428</v>
+      </c>
+      <c r="B26" s="7">
         <v>46512</v>
       </c>
       <c r="C26" s="1" t="str">
@@ -8511,34 +8589,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>54</v>
+        <v>429</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G26" s="2">
         <v>80</v>
       </c>
       <c r="H26" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I26" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J26" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K26" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="L26" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="M26" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="N26" t="s">
         <v>29</v>
@@ -8546,11 +8624,11 @@
       <c r="O26" t="s">
         <v>30</v>
       </c>
-      <c r="Q26" s="10" t="s">
-        <v>427</v>
+      <c r="Q26" s="8" t="s">
+        <v>430</v>
       </c>
       <c r="R26" t="s">
-        <v>58</v>
+        <v>393</v>
       </c>
       <c r="S26" t="s">
         <v>33</v>
@@ -8565,41 +8643,44 @@
     </row>
     <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B27" s="1">
-        <v>46513</v>
+        <v>431</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46512</v>
       </c>
       <c r="C27" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>231</v>
+        <v>55</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G27" s="2">
         <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I27" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J27" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="K27" t="s">
-        <v>356</v>
+        <v>345</v>
+      </c>
+      <c r="L27" t="s">
+        <v>406</v>
       </c>
       <c r="M27" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="N27" t="s">
         <v>29</v>
@@ -8607,11 +8688,11 @@
       <c r="O27" t="s">
         <v>30</v>
       </c>
-      <c r="Q27" s="10" t="s">
-        <v>428</v>
+      <c r="Q27" s="8" t="s">
+        <v>432</v>
       </c>
       <c r="R27" t="s">
-        <v>149</v>
+        <v>59</v>
       </c>
       <c r="S27" t="s">
         <v>33</v>
@@ -8626,65 +8707,59 @@
     </row>
     <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="B28" s="1">
-        <v>46517</v>
+        <v>147</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46513</v>
       </c>
       <c r="C28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Monday</v>
+        <v>Thursday</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>37</v>
+        <v>235</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>38</v>
+        <v>49</v>
+      </c>
+      <c r="G28" s="10">
+        <v>80</v>
       </c>
       <c r="H28" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I28" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J28" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="K28" t="s">
-        <v>341</v>
-      </c>
-      <c r="L28" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="M28" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="N28" t="s">
         <v>29</v>
       </c>
       <c r="O28" t="s">
-        <v>29</v>
-      </c>
-      <c r="P28" t="s">
-        <v>431</v>
-      </c>
-      <c r="Q28" s="10" t="s">
-        <v>432</v>
+        <v>30</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>433</v>
       </c>
       <c r="R28" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="S28" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="T28" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="U28" t="b">
         <f>FALSE()</f>
@@ -8693,65 +8768,65 @@
     </row>
     <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="B29" s="1">
-        <v>46518</v>
+        <v>434</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46517</v>
       </c>
       <c r="C29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Tuesday</v>
+        <v>Monday</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>118</v>
+        <v>47</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G29" s="2">
-        <v>80</v>
+        <v>435</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H29" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I29" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J29" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K29" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="L29" t="s">
-        <v>434</v>
+        <v>346</v>
       </c>
       <c r="M29" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="N29" t="s">
         <v>29</v>
       </c>
       <c r="O29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P29" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q29" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>437</v>
       </c>
       <c r="R29" t="s">
-        <v>241</v>
+        <v>116</v>
       </c>
       <c r="S29" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T29" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="U29" t="b">
         <f>FALSE()</f>
@@ -8760,56 +8835,59 @@
     </row>
     <row r="30" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="B30" s="1">
-        <v>46519</v>
+        <v>438</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46518</v>
       </c>
       <c r="C30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>251</v>
+        <v>47</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G30" s="2">
         <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I30" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J30" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="K30" t="s">
-        <v>352</v>
+        <v>364</v>
+      </c>
+      <c r="L30" t="s">
+        <v>439</v>
       </c>
       <c r="M30" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="N30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O30" t="s">
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q30" s="10" t="s">
-        <v>437</v>
+        <v>243</v>
+      </c>
+      <c r="Q30" s="8" t="s">
+        <v>440</v>
       </c>
       <c r="R30" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="S30" t="s">
         <v>33</v>
@@ -8824,41 +8902,41 @@
     </row>
     <row r="31" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="B31" s="1">
-        <v>46520</v>
+        <v>441</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46519</v>
       </c>
       <c r="C31" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>364</v>
+        <v>255</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G31" s="2">
         <v>80</v>
       </c>
       <c r="H31" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I31" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J31" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K31" t="s">
         <v>356</v>
       </c>
       <c r="M31" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="N31" t="s">
         <v>30</v>
@@ -8866,11 +8944,14 @@
       <c r="O31" t="s">
         <v>30</v>
       </c>
-      <c r="Q31" s="10" t="s">
-        <v>439</v>
+      <c r="P31" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q31" s="8" t="s">
+        <v>442</v>
       </c>
       <c r="R31" t="s">
-        <v>440</v>
+        <v>258</v>
       </c>
       <c r="S31" t="s">
         <v>33</v>
@@ -8885,59 +8966,53 @@
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="B32" s="1">
-        <v>46525</v>
+        <v>443</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46520</v>
       </c>
       <c r="C32" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Tuesday</v>
+        <v>Thursday</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>60</v>
+        <v>368</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G32" s="2">
         <v>80</v>
       </c>
       <c r="H32" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I32" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J32" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="K32" t="s">
-        <v>347</v>
-      </c>
-      <c r="L32" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="M32" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="N32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O32" t="s">
         <v>30</v>
       </c>
-      <c r="P32" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q32" s="10" t="s">
-        <v>442</v>
+      <c r="Q32" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="R32" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="S32" t="s">
         <v>33</v>
@@ -8952,41 +9027,44 @@
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B33" s="1">
-        <v>46526</v>
+        <v>446</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46525</v>
       </c>
       <c r="C33" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I33" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J33" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K33" t="s">
-        <v>341</v>
+        <v>351</v>
+      </c>
+      <c r="L33" t="s">
+        <v>386</v>
       </c>
       <c r="M33" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="N33" t="s">
         <v>29</v>
@@ -8995,13 +9073,13 @@
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q33" s="10" t="s">
-        <v>444</v>
+        <v>65</v>
+      </c>
+      <c r="Q33" s="8" t="s">
+        <v>447</v>
       </c>
       <c r="R33" t="s">
-        <v>165</v>
+        <v>448</v>
       </c>
       <c r="S33" t="s">
         <v>33</v>
@@ -9015,57 +9093,57 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="B34" s="1">
-        <v>46527</v>
+      <c r="A34" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46526</v>
       </c>
       <c r="C34" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Thursday</v>
+        <v>Wednesday</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G34" s="2">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="H34" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I34" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J34" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K34" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="M34" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="N34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P34" t="s">
-        <v>408</v>
-      </c>
-      <c r="Q34" s="10" t="s">
-        <v>409</v>
+        <v>167</v>
+      </c>
+      <c r="Q34" s="8" t="s">
+        <v>449</v>
       </c>
       <c r="R34" t="s">
-        <v>410</v>
+        <v>169</v>
       </c>
       <c r="S34" t="s">
         <v>33</v>
@@ -9079,10 +9157,10 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="B35" s="1">
+      <c r="A35" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="B35" s="7">
         <v>46527</v>
       </c>
       <c r="C35" s="1" t="str">
@@ -9090,55 +9168,52 @@
         <v>Thursday</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>37</v>
+        <v>89</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>38</v>
+        <v>49</v>
+      </c>
+      <c r="G35" s="10">
+        <v>80</v>
       </c>
       <c r="H35" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I35" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J35" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="K35" t="s">
-        <v>341</v>
-      </c>
-      <c r="L35" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="M35" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="N35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O35" t="s">
         <v>29</v>
       </c>
       <c r="P35" t="s">
-        <v>449</v>
-      </c>
-      <c r="Q35" s="10" t="s">
-        <v>450</v>
+        <v>413</v>
+      </c>
+      <c r="Q35" s="8" t="s">
+        <v>414</v>
       </c>
       <c r="R35" t="s">
-        <v>94</v>
+        <v>415</v>
       </c>
       <c r="S35" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="T35" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="U35" t="b">
         <f>FALSE()</f>
@@ -9149,109 +9224,118 @@
       <c r="A36" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="7">
+        <v>46527</v>
+      </c>
+      <c r="C36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Thursday</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H36" t="s">
+        <v>342</v>
+      </c>
+      <c r="I36" t="s">
+        <v>343</v>
+      </c>
+      <c r="J36" t="s">
+        <v>344</v>
+      </c>
+      <c r="K36" t="s">
+        <v>345</v>
+      </c>
+      <c r="L36" t="s">
+        <v>369</v>
+      </c>
+      <c r="M36" t="s">
+        <v>92</v>
+      </c>
+      <c r="N36" t="s">
+        <v>29</v>
+      </c>
+      <c r="O36" t="s">
+        <v>29</v>
+      </c>
+      <c r="P36" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q36" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="R36" t="s">
+        <v>95</v>
+      </c>
+      <c r="S36" t="s">
+        <v>37</v>
+      </c>
+      <c r="T36" t="s">
+        <v>39</v>
+      </c>
+      <c r="U36" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="B37" s="7">
         <v>46533</v>
       </c>
-      <c r="C36" s="1" t="str">
+      <c r="C37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Wednesday</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="D37" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G36" s="2">
+      <c r="F37" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G37" s="2">
         <v>12</v>
       </c>
-      <c r="H36" t="s">
-        <v>338</v>
-      </c>
-      <c r="I36" t="s">
-        <v>339</v>
-      </c>
-      <c r="J36" t="s">
-        <v>346</v>
-      </c>
-      <c r="K36" t="s">
-        <v>352</v>
-      </c>
-      <c r="M36" t="s">
-        <v>156</v>
-      </c>
-      <c r="N36" t="s">
-        <v>29</v>
-      </c>
-      <c r="O36" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q36" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="R36" t="s">
-        <v>214</v>
-      </c>
-      <c r="S36" t="s">
-        <v>33</v>
-      </c>
-      <c r="T36" t="s">
-        <v>34</v>
-      </c>
-      <c r="U36" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="B37" s="1">
-        <v>46534</v>
-      </c>
-      <c r="C37" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Thursday</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G37" s="2">
-        <v>80</v>
-      </c>
       <c r="H37" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I37" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J37" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K37" t="s">
         <v>356</v>
       </c>
       <c r="M37" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="N37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O37" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q37" s="10" t="s">
-        <v>439</v>
+        <v>30</v>
+      </c>
+      <c r="Q37" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="R37" t="s">
+        <v>218</v>
       </c>
       <c r="S37" t="s">
         <v>33</v>
@@ -9264,13 +9348,71 @@
         <v>0</v>
       </c>
     </row>
+    <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="B38" s="7">
+        <v>46534</v>
+      </c>
+      <c r="C38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Thursday</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G38" s="2">
+        <v>80</v>
+      </c>
+      <c r="H38" t="s">
+        <v>342</v>
+      </c>
+      <c r="I38" t="s">
+        <v>343</v>
+      </c>
+      <c r="J38" t="s">
+        <v>355</v>
+      </c>
+      <c r="K38" t="s">
+        <v>360</v>
+      </c>
+      <c r="M38" t="s">
+        <v>92</v>
+      </c>
+      <c r="N38" t="s">
+        <v>30</v>
+      </c>
+      <c r="O38" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q38" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="S38" t="s">
+        <v>33</v>
+      </c>
+      <c r="T38" t="s">
+        <v>34</v>
+      </c>
+      <c r="U38" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="S2:S37" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="S2:S38" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Regional,Local"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T2:T37" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="T2:T38" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Website,External"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9278,10 +9420,10 @@
   <hyperlinks>
     <hyperlink ref="Q6" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
     <hyperlink ref="Q7" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="Q21" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="Q23" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="Q34" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="Q37" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="Q22" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="Q24" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="Q35" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="Q38" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9293,7 +9435,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.85546875" customWidth="1"/>
@@ -9378,44 +9520,44 @@
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="B2" s="1">
+        <v>459</v>
+      </c>
+      <c r="B2" s="7">
         <v>46546</v>
       </c>
       <c r="C2" s="1" t="str">
-        <f t="shared" ref="C2:C20" si="0">IF(B2="","",TEXT(B2,"dddd"))</f>
+        <f t="shared" ref="C2:C21" si="0">IF(B2="","",TEXT(B2,"dddd"))</f>
         <v>Tuesday</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>38</v>
+        <v>460</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I2" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="L2" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="M2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
@@ -9424,10 +9566,10 @@
         <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>462</v>
+        <v>466</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>467</v>
       </c>
       <c r="R2" t="s">
         <v>116</v>
@@ -9436,7 +9578,7 @@
         <v>37</v>
       </c>
       <c r="T2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U2" t="b">
         <f>FALSE()</f>
@@ -9445,9 +9587,9 @@
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="B3" s="1">
+        <v>468</v>
+      </c>
+      <c r="B3" s="7">
         <v>46547</v>
       </c>
       <c r="C3" s="1" t="str">
@@ -9458,31 +9600,31 @@
         <v>124</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G3" s="2">
         <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L3" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="M3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s">
         <v>29</v>
@@ -9493,11 +9635,11 @@
       <c r="P3" t="s">
         <v>125</v>
       </c>
-      <c r="Q3" s="10" t="s">
-        <v>466</v>
+      <c r="Q3" s="8" t="s">
+        <v>471</v>
       </c>
       <c r="R3" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="S3" t="s">
         <v>33</v>
@@ -9512,9 +9654,9 @@
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="B4" s="1">
+        <v>473</v>
+      </c>
+      <c r="B4" s="7">
         <v>46548</v>
       </c>
       <c r="C4" s="1" t="str">
@@ -9522,34 +9664,34 @@
         <v>Thursday</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" s="2">
         <v>80</v>
       </c>
       <c r="H4" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I4" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J4" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K4" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="L4" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N4" t="s">
         <v>29</v>
@@ -9558,13 +9700,13 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>471</v>
+        <v>176</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>476</v>
       </c>
       <c r="R4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="S4" t="s">
         <v>33</v>
@@ -9579,9 +9721,9 @@
     </row>
     <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="B5" s="1">
+        <v>477</v>
+      </c>
+      <c r="B5" s="7">
         <v>46552</v>
       </c>
       <c r="C5" s="1" t="str">
@@ -9589,28 +9731,28 @@
         <v>Monday</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" s="2">
         <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I5" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J5" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="M5" t="s">
         <v>106</v>
@@ -9622,13 +9764,13 @@
         <v>30</v>
       </c>
       <c r="P5" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q5" s="10" t="s">
-        <v>474</v>
+        <v>251</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>479</v>
       </c>
       <c r="R5" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="S5" t="s">
         <v>33</v>
@@ -9643,9 +9785,9 @@
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="B6" s="1">
+        <v>481</v>
+      </c>
+      <c r="B6" s="7">
         <v>46553</v>
       </c>
       <c r="C6" s="1" t="str">
@@ -9659,25 +9801,25 @@
         <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2">
         <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I6" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J6" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K6" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="L6" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
@@ -9688,11 +9830,11 @@
       <c r="O6" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" s="10" t="s">
-        <v>478</v>
+      <c r="Q6" s="8" t="s">
+        <v>483</v>
       </c>
       <c r="R6" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="S6" t="s">
         <v>33</v>
@@ -9706,10 +9848,10 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="B7" s="1">
+      <c r="A7" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="B7" s="7">
         <v>46554</v>
       </c>
       <c r="C7" s="1" t="str">
@@ -9717,28 +9859,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2">
         <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I7" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J7" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K7" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="M7" t="s">
         <v>156</v>
@@ -9750,10 +9892,10 @@
         <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q7" s="10" t="s">
-        <v>437</v>
+        <v>256</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>442</v>
       </c>
       <c r="S7" t="s">
         <v>33</v>
@@ -9768,9 +9910,9 @@
     </row>
     <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="B8" s="1">
+        <v>485</v>
+      </c>
+      <c r="B8" s="7">
         <v>46561</v>
       </c>
       <c r="C8" s="1" t="str">
@@ -9778,31 +9920,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2">
         <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I8" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J8" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K8" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="M8" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -9811,13 +9953,13 @@
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>481</v>
+        <v>286</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>486</v>
       </c>
       <c r="R8" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="S8" t="s">
         <v>33</v>
@@ -9832,9 +9974,9 @@
     </row>
     <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B9" s="1">
+        <v>488</v>
+      </c>
+      <c r="B9" s="7">
         <v>46562</v>
       </c>
       <c r="C9" s="1" t="str">
@@ -9842,31 +9984,31 @@
         <v>Thursday</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9" s="2">
         <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I9" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J9" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K9" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L9" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="M9" t="s">
         <v>156</v>
@@ -9877,11 +10019,11 @@
       <c r="O9" t="s">
         <v>30</v>
       </c>
-      <c r="Q9" s="10" t="s">
-        <v>485</v>
+      <c r="Q9" s="8" t="s">
+        <v>490</v>
       </c>
       <c r="R9" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="S9" t="s">
         <v>33</v>
@@ -9896,9 +10038,9 @@
     </row>
     <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="B10" s="1">
+        <v>491</v>
+      </c>
+      <c r="B10" s="7">
         <v>46568</v>
       </c>
       <c r="C10" s="1" t="str">
@@ -9906,34 +10048,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2">
         <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I10" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J10" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K10" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="L10" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="M10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
@@ -9941,11 +10083,11 @@
       <c r="O10" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="10" t="s">
-        <v>488</v>
+      <c r="Q10" s="8" t="s">
+        <v>493</v>
       </c>
       <c r="R10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S10" t="s">
         <v>33</v>
@@ -9960,9 +10102,9 @@
     </row>
     <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="B11" s="1">
+        <v>494</v>
+      </c>
+      <c r="B11" s="7">
         <v>46569</v>
       </c>
       <c r="C11" s="1" t="str">
@@ -9970,34 +10112,34 @@
         <v>Thursday</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G11" s="2">
         <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I11" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J11" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K11" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L11" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="M11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -10005,11 +10147,11 @@
       <c r="O11" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="10" t="s">
-        <v>491</v>
+      <c r="Q11" s="8" t="s">
+        <v>496</v>
       </c>
       <c r="R11" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="S11" t="s">
         <v>33</v>
@@ -10024,9 +10166,9 @@
     </row>
     <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="B12" s="1">
+        <v>497</v>
+      </c>
+      <c r="B12" s="7">
         <v>46570</v>
       </c>
       <c r="C12" s="1" t="str">
@@ -10034,31 +10176,31 @@
         <v>Friday</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G12" s="2">
         <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I12" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J12" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K12" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="M12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
@@ -10069,11 +10211,11 @@
       <c r="P12" t="s">
         <v>136</v>
       </c>
-      <c r="Q12" s="10" t="s">
-        <v>494</v>
+      <c r="Q12" s="8" t="s">
+        <v>499</v>
       </c>
       <c r="R12" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="S12" t="s">
         <v>33</v>
@@ -10088,9 +10230,9 @@
     </row>
     <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="B13" s="1">
+        <v>501</v>
+      </c>
+      <c r="B13" s="7">
         <v>46574</v>
       </c>
       <c r="C13" s="1" t="str">
@@ -10098,34 +10240,34 @@
         <v>Tuesday</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>38</v>
+        <v>502</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H13" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I13" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J13" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K13" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="L13" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="M13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
@@ -10134,10 +10276,10 @@
         <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>498</v>
-      </c>
-      <c r="Q13" s="10" t="s">
-        <v>499</v>
+        <v>503</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>504</v>
       </c>
       <c r="R13" t="s">
         <v>116</v>
@@ -10146,7 +10288,7 @@
         <v>37</v>
       </c>
       <c r="T13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U13" t="b">
         <f>FALSE()</f>
@@ -10154,10 +10296,10 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>500</v>
-      </c>
-      <c r="B14" s="1">
+      <c r="A14" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="B14" s="7">
         <v>46575</v>
       </c>
       <c r="C14" s="1" t="str">
@@ -10165,31 +10307,31 @@
         <v>Wednesday</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G14" s="2">
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I14" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J14" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K14" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="M14" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="N14" t="s">
         <v>30</v>
@@ -10198,10 +10340,10 @@
         <v>29</v>
       </c>
       <c r="P14" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q14" s="10" t="s">
-        <v>481</v>
+        <v>286</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>486</v>
       </c>
       <c r="S14" t="s">
         <v>33</v>
@@ -10215,10 +10357,10 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>501</v>
-      </c>
-      <c r="B15" s="1">
+      <c r="A15" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="B15" s="7">
         <v>46575</v>
       </c>
       <c r="C15" s="1" t="str">
@@ -10226,28 +10368,28 @@
         <v>Wednesday</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" s="2">
         <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I15" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J15" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K15" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="M15" t="s">
         <v>156</v>
@@ -10259,10 +10401,10 @@
         <v>29</v>
       </c>
       <c r="P15" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>437</v>
+        <v>256</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>442</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -10277,9 +10419,9 @@
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B16" s="1">
+        <v>246</v>
+      </c>
+      <c r="B16" s="7">
         <v>46576</v>
       </c>
       <c r="C16" s="1" t="str">
@@ -10287,28 +10429,28 @@
         <v>Thursday</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G16" s="2">
         <v>80</v>
       </c>
       <c r="H16" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I16" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J16" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="K16" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="M16" t="s">
         <v>106</v>
@@ -10322,11 +10464,11 @@
       <c r="P16" t="s">
         <v>136</v>
       </c>
-      <c r="Q16" s="10" t="s">
-        <v>502</v>
+      <c r="Q16" s="8" t="s">
+        <v>507</v>
       </c>
       <c r="R16" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="S16" t="s">
         <v>33</v>
@@ -10341,9 +10483,9 @@
     </row>
     <row r="17" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="B17" s="1">
+        <v>508</v>
+      </c>
+      <c r="B17" s="7">
         <v>46582</v>
       </c>
       <c r="C17" s="1" t="str">
@@ -10351,34 +10493,34 @@
         <v>Wednesday</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>38</v>
+        <v>509</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H17" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I17" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J17" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K17" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="L17" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="M17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
@@ -10387,19 +10529,19 @@
         <v>29</v>
       </c>
       <c r="P17" t="s">
-        <v>505</v>
-      </c>
-      <c r="Q17" s="10" t="s">
-        <v>506</v>
+        <v>510</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>511</v>
       </c>
       <c r="R17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S17" t="s">
         <v>37</v>
       </c>
       <c r="T17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U17" t="b">
         <f>FALSE()</f>
@@ -10407,127 +10549,124 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>507</v>
-      </c>
-      <c r="B18" s="1">
-        <v>46589</v>
+      <c r="A18" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="B18" s="7">
+        <v>46583</v>
       </c>
       <c r="C18" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Wednesday</v>
+        <v>Thursday</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="2">
-        <v>80</v>
+        <v>37</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H18" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I18" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J18" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="K18" t="s">
         <v>464</v>
       </c>
+      <c r="L18" t="s">
+        <v>465</v>
+      </c>
       <c r="M18" t="s">
-        <v>281</v>
+        <v>85</v>
       </c>
       <c r="N18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O18" t="s">
         <v>29</v>
       </c>
       <c r="P18" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q18" s="10" t="s">
-        <v>481</v>
+        <v>163</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="R18" t="s">
+        <v>164</v>
       </c>
       <c r="S18" t="s">
+        <v>37</v>
+      </c>
+      <c r="T18" t="s">
+        <v>39</v>
+      </c>
+      <c r="U18" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="B19" s="7">
+        <v>46589</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="10">
+        <v>80</v>
+      </c>
+      <c r="H19" t="s">
+        <v>461</v>
+      </c>
+      <c r="I19" t="s">
+        <v>462</v>
+      </c>
+      <c r="J19" t="s">
+        <v>478</v>
+      </c>
+      <c r="K19" t="s">
+        <v>469</v>
+      </c>
+      <c r="M19" t="s">
+        <v>285</v>
+      </c>
+      <c r="N19" t="s">
+        <v>30</v>
+      </c>
+      <c r="O19" t="s">
+        <v>29</v>
+      </c>
+      <c r="P19" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="S19" t="s">
         <v>33</v>
       </c>
-      <c r="T18" t="s">
+      <c r="T19" t="s">
         <v>34</v>
-      </c>
-      <c r="U18" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>508</v>
-      </c>
-      <c r="B19" s="1">
-        <v>46604</v>
-      </c>
-      <c r="C19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Thursday</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="H19" t="s">
-        <v>456</v>
-      </c>
-      <c r="I19" t="s">
-        <v>457</v>
-      </c>
-      <c r="J19" t="s">
-        <v>458</v>
-      </c>
-      <c r="K19" t="s">
-        <v>459</v>
-      </c>
-      <c r="L19" t="s">
-        <v>460</v>
-      </c>
-      <c r="M19" t="s">
-        <v>84</v>
-      </c>
-      <c r="N19" t="s">
-        <v>29</v>
-      </c>
-      <c r="O19" t="s">
-        <v>29</v>
-      </c>
-      <c r="P19" t="s">
-        <v>510</v>
-      </c>
-      <c r="Q19" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="R19" t="s">
-        <v>116</v>
-      </c>
-      <c r="S19" t="s">
-        <v>37</v>
-      </c>
-      <c r="T19" t="s">
-        <v>38</v>
       </c>
       <c r="U19" t="b">
         <f>FALSE()</f>
@@ -10536,78 +10675,145 @@
     </row>
     <row r="20" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="B20" s="1">
-        <v>46612</v>
+        <v>514</v>
+      </c>
+      <c r="B20" s="7">
+        <v>46604</v>
       </c>
       <c r="C20" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>Friday</v>
+        <v>Thursday</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>130</v>
+        <v>79</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G20" s="2">
-        <v>80</v>
+        <v>515</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="H20" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="I20" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J20" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="K20" t="s">
         <v>464</v>
       </c>
       <c r="L20" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="M20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N20" t="s">
         <v>29</v>
       </c>
       <c r="O20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P20" t="s">
-        <v>513</v>
-      </c>
-      <c r="Q20" s="10" t="s">
-        <v>514</v>
+        <v>516</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>517</v>
       </c>
       <c r="R20" t="s">
-        <v>515</v>
+        <v>116</v>
       </c>
       <c r="S20" t="s">
+        <v>37</v>
+      </c>
+      <c r="T20" t="s">
+        <v>39</v>
+      </c>
+      <c r="U20" t="b">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="B21" s="7">
+        <v>46612</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Friday</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="2">
+        <v>80</v>
+      </c>
+      <c r="H21" t="s">
+        <v>461</v>
+      </c>
+      <c r="I21" t="s">
+        <v>462</v>
+      </c>
+      <c r="J21" t="s">
+        <v>463</v>
+      </c>
+      <c r="K21" t="s">
+        <v>469</v>
+      </c>
+      <c r="L21" t="s">
+        <v>465</v>
+      </c>
+      <c r="M21" t="s">
+        <v>85</v>
+      </c>
+      <c r="N21" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" t="s">
+        <v>30</v>
+      </c>
+      <c r="P21" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="R21" t="s">
+        <v>521</v>
+      </c>
+      <c r="S21" t="s">
         <v>33</v>
       </c>
-      <c r="T20" t="s">
+      <c r="T21" t="s">
         <v>34</v>
       </c>
-      <c r="U20" t="b">
+      <c r="U21" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="S2:S20" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="S2:S21" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Regional,Local"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="T2:T20" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="T2:T21" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"Website,External"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Data/2026-2027 SPH Activity Master List.xlsx
+++ b/Data/2026-2027 SPH Activity Master List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude Working Folder\HubSpot Events - RP1 - RP4 - 2026-2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B61B848-660C-4134-BC24-7647A0EF8121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30DB7D3-E2E6-44BF-9EB7-0BC1DECFCC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="57600" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="57600" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2169" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="525">
   <si>
     <t>Event Name</t>
   </si>
@@ -1658,7 +1658,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1695,6 +1695,12 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1708,7 +1714,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1734,6 +1740,8 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3754,10 +3762,13 @@
       <c r="D26" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="F26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="18" t="s">
         <v>39</v>
       </c>
       <c r="H26" t="s">
@@ -7887,10 +7898,13 @@
       <c r="D15" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="F15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="18" t="s">
         <v>39</v>
       </c>
       <c r="H15" t="s">
@@ -10562,10 +10576,13 @@
       <c r="D18" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="F18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>39</v>
       </c>
       <c r="H18" t="s">
